--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -805,6 +805,131 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>114920743</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57252</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>523996</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6713290</v>
+      </c>
+      <c r="S3" t="n">
+        <v>75</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-02-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-02-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska och gammla spår vad jag kan se.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kalle Ericson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kalle Ericson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -1447,7 +1447,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118680241</v>
+        <v>118680065</v>
       </c>
       <c r="B8" t="n">
         <v>97846</v>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1490,11 +1490,6 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1506,10 +1501,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524096</v>
+        <v>524085</v>
       </c>
       <c r="R8" t="n">
-        <v>6714118</v>
+        <v>6714124</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1541,7 +1536,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1551,12 +1546,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Några i blom.</t>
+          <t>Under mindre gran intill större tall, i blom och minst 20 rosetter.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1583,7 +1578,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118680271</v>
+        <v>118680431</v>
       </c>
       <c r="B9" t="n">
         <v>97846</v>
@@ -1618,12 +1613,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1642,10 +1637,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524098</v>
+        <v>524105</v>
       </c>
       <c r="R9" t="n">
-        <v>6714108</v>
+        <v>6714054</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1677,7 +1672,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1687,12 +1682,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ca 10 rosetter några i blom</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1719,7 +1709,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118680340</v>
+        <v>118680271</v>
       </c>
       <c r="B10" t="n">
         <v>97846</v>
@@ -1759,7 +1749,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1778,10 +1768,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524081</v>
+        <v>524098</v>
       </c>
       <c r="R10" t="n">
-        <v>6714116</v>
+        <v>6714108</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1813,7 +1803,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1823,12 +1813,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Mycket i blom och rosetter.</t>
+          <t>Ca 10 rosetter några i blom</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1855,7 +1845,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118680431</v>
+        <v>118680590</v>
       </c>
       <c r="B11" t="n">
         <v>97846</v>
@@ -1890,7 +1880,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1914,10 +1904,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524105</v>
+        <v>524083</v>
       </c>
       <c r="R11" t="n">
-        <v>6714054</v>
+        <v>6714083</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1949,7 +1939,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1959,7 +1949,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1986,7 +1976,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118680590</v>
+        <v>118680966</v>
       </c>
       <c r="B12" t="n">
         <v>97846</v>
@@ -2021,12 +2011,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2045,10 +2035,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524083</v>
+        <v>524064</v>
       </c>
       <c r="R12" t="n">
-        <v>6714083</v>
+        <v>6714092</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -2080,7 +2070,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2090,7 +2080,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>I blom och fler rosetter på fler fläckar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2117,7 +2112,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118680966</v>
+        <v>118680340</v>
       </c>
       <c r="B13" t="n">
         <v>97846</v>
@@ -2152,7 +2147,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2176,10 +2171,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524064</v>
+        <v>524081</v>
       </c>
       <c r="R13" t="n">
-        <v>6714092</v>
+        <v>6714116</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2211,7 +2206,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2221,12 +2216,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>I blom och fler rosetter på fler fläckar.</t>
+          <t>Mycket i blom och rosetter.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2253,7 +2248,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118680065</v>
+        <v>118680241</v>
       </c>
       <c r="B14" t="n">
         <v>97846</v>
@@ -2288,7 +2283,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2296,6 +2291,11 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524085</v>
+        <v>524096</v>
       </c>
       <c r="R14" t="n">
-        <v>6714124</v>
+        <v>6714118</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Under mindre gran intill större tall, i blom och minst 20 rosetter.</t>
+          <t>Några i blom.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -1447,7 +1447,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118680065</v>
+        <v>118680340</v>
       </c>
       <c r="B8" t="n">
         <v>97846</v>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1490,6 +1490,11 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1501,10 +1506,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524085</v>
+        <v>524081</v>
       </c>
       <c r="R8" t="n">
-        <v>6714124</v>
+        <v>6714116</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1536,7 +1541,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1546,12 +1551,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Under mindre gran intill större tall, i blom och minst 20 rosetter.</t>
+          <t>Mycket i blom och rosetter.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1578,7 +1583,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118680431</v>
+        <v>118680966</v>
       </c>
       <c r="B9" t="n">
         <v>97846</v>
@@ -1613,12 +1618,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1637,10 +1642,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524105</v>
+        <v>524064</v>
       </c>
       <c r="R9" t="n">
-        <v>6714054</v>
+        <v>6714092</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1672,7 +1677,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1682,7 +1687,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I blom och fler rosetter på fler fläckar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1709,7 +1719,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118680271</v>
+        <v>118680431</v>
       </c>
       <c r="B10" t="n">
         <v>97846</v>
@@ -1744,12 +1754,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1768,10 +1778,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524098</v>
+        <v>524105</v>
       </c>
       <c r="R10" t="n">
-        <v>6714108</v>
+        <v>6714054</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1803,7 +1813,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1813,12 +1823,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ca 10 rosetter några i blom</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1845,7 +1850,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118680590</v>
+        <v>118680065</v>
       </c>
       <c r="B11" t="n">
         <v>97846</v>
@@ -1880,17 +1885,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524083</v>
+        <v>524085</v>
       </c>
       <c r="R11" t="n">
-        <v>6714083</v>
+        <v>6714124</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1949,7 +1949,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Under mindre gran intill större tall, i blom och minst 20 rosetter.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1976,7 +1981,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118680966</v>
+        <v>118680241</v>
       </c>
       <c r="B12" t="n">
         <v>97846</v>
@@ -2011,7 +2016,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2035,10 +2040,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524064</v>
+        <v>524096</v>
       </c>
       <c r="R12" t="n">
-        <v>6714092</v>
+        <v>6714118</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -2070,7 +2075,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2080,12 +2085,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>I blom och fler rosetter på fler fläckar.</t>
+          <t>Några i blom.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2112,7 +2117,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118680340</v>
+        <v>118680271</v>
       </c>
       <c r="B13" t="n">
         <v>97846</v>
@@ -2152,7 +2157,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2171,10 +2176,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524081</v>
+        <v>524098</v>
       </c>
       <c r="R13" t="n">
-        <v>6714116</v>
+        <v>6714108</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2206,7 +2211,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2216,12 +2221,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Mycket i blom och rosetter.</t>
+          <t>Ca 10 rosetter några i blom</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2248,7 +2253,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118680241</v>
+        <v>118680590</v>
       </c>
       <c r="B14" t="n">
         <v>97846</v>
@@ -2288,7 +2293,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2307,10 +2312,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524096</v>
+        <v>524083</v>
       </c>
       <c r="R14" t="n">
-        <v>6714118</v>
+        <v>6714083</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2342,7 +2347,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2352,12 +2357,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Några i blom.</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -1447,10 +1447,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118680340</v>
+        <v>118680966</v>
       </c>
       <c r="B8" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524081</v>
+        <v>524064</v>
       </c>
       <c r="R8" t="n">
-        <v>6714116</v>
+        <v>6714092</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Mycket i blom och rosetter.</t>
+          <t>I blom och fler rosetter på fler fläckar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1583,10 +1583,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118680966</v>
+        <v>118680065</v>
       </c>
       <c r="B9" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1626,11 +1626,6 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1642,10 +1637,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524064</v>
+        <v>524085</v>
       </c>
       <c r="R9" t="n">
-        <v>6714092</v>
+        <v>6714124</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1677,7 +1672,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1687,12 +1682,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I blom och fler rosetter på fler fläckar.</t>
+          <t>Under mindre gran intill större tall, i blom och minst 20 rosetter.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1719,10 +1714,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118680431</v>
+        <v>118680340</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1754,12 +1749,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1778,10 +1773,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524105</v>
+        <v>524081</v>
       </c>
       <c r="R10" t="n">
-        <v>6714054</v>
+        <v>6714116</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1813,7 +1808,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1823,7 +1818,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Mycket i blom och rosetter.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1850,10 +1850,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118680065</v>
+        <v>118680590</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1885,12 +1885,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1904,10 +1909,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524085</v>
+        <v>524083</v>
       </c>
       <c r="R11" t="n">
-        <v>6714124</v>
+        <v>6714083</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1939,7 +1944,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1949,12 +1954,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Under mindre gran intill större tall, i blom och minst 20 rosetter.</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1981,10 +1981,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118680241</v>
+        <v>118680431</v>
       </c>
       <c r="B12" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2016,12 +2016,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524096</v>
+        <v>524105</v>
       </c>
       <c r="R12" t="n">
-        <v>6714118</v>
+        <v>6714054</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2085,12 +2085,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Några i blom.</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2117,10 +2112,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118680271</v>
+        <v>118680241</v>
       </c>
       <c r="B13" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2152,12 +2147,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2176,10 +2171,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524098</v>
+        <v>524096</v>
       </c>
       <c r="R13" t="n">
-        <v>6714108</v>
+        <v>6714118</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2226,7 +2221,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ca 10 rosetter några i blom</t>
+          <t>Några i blom.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2253,10 +2248,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118680590</v>
+        <v>118680271</v>
       </c>
       <c r="B14" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2288,12 +2283,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2312,10 +2307,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524083</v>
+        <v>524098</v>
       </c>
       <c r="R14" t="n">
-        <v>6714083</v>
+        <v>6714108</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2347,7 +2342,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2357,7 +2352,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ca 10 rosetter några i blom</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -1447,7 +1447,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118680966</v>
+        <v>118680271</v>
       </c>
       <c r="B8" t="n">
         <v>97853</v>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524064</v>
+        <v>524098</v>
       </c>
       <c r="R8" t="n">
-        <v>6714092</v>
+        <v>6714108</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>I blom och fler rosetter på fler fläckar.</t>
+          <t>Ca 10 rosetter några i blom</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1583,7 +1583,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118680065</v>
+        <v>118680431</v>
       </c>
       <c r="B9" t="n">
         <v>97853</v>
@@ -1623,7 +1623,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1637,10 +1642,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524085</v>
+        <v>524105</v>
       </c>
       <c r="R9" t="n">
-        <v>6714124</v>
+        <v>6714054</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1672,7 +1677,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1682,12 +1687,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Under mindre gran intill större tall, i blom och minst 20 rosetter.</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1714,7 +1714,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118680340</v>
+        <v>118680241</v>
       </c>
       <c r="B10" t="n">
         <v>97853</v>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524081</v>
+        <v>524096</v>
       </c>
       <c r="R10" t="n">
-        <v>6714116</v>
+        <v>6714118</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Mycket i blom och rosetter.</t>
+          <t>Några i blom.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1850,7 +1850,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118680590</v>
+        <v>118680966</v>
       </c>
       <c r="B11" t="n">
         <v>97853</v>
@@ -1885,12 +1885,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524083</v>
+        <v>524064</v>
       </c>
       <c r="R11" t="n">
-        <v>6714083</v>
+        <v>6714092</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1954,7 +1954,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>I blom och fler rosetter på fler fläckar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1981,7 +1986,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118680431</v>
+        <v>118680065</v>
       </c>
       <c r="B12" t="n">
         <v>97853</v>
@@ -2021,12 +2026,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524105</v>
+        <v>524085</v>
       </c>
       <c r="R12" t="n">
-        <v>6714054</v>
+        <v>6714124</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2085,7 +2085,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Under mindre gran intill större tall, i blom och minst 20 rosetter.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2112,7 +2117,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118680241</v>
+        <v>118680340</v>
       </c>
       <c r="B13" t="n">
         <v>97853</v>
@@ -2147,7 +2152,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2171,10 +2176,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524096</v>
+        <v>524081</v>
       </c>
       <c r="R13" t="n">
-        <v>6714118</v>
+        <v>6714116</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2206,7 +2211,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2216,12 +2221,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Några i blom.</t>
+          <t>Mycket i blom och rosetter.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2248,7 +2253,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118680271</v>
+        <v>118680590</v>
       </c>
       <c r="B14" t="n">
         <v>97853</v>
@@ -2283,12 +2288,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2307,10 +2312,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524098</v>
+        <v>524083</v>
       </c>
       <c r="R14" t="n">
-        <v>6714108</v>
+        <v>6714083</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2342,7 +2347,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2352,12 +2357,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ca 10 rosetter några i blom</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -2387,7 +2387,7 @@
         <v>122821104</v>
       </c>
       <c r="B15" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>122817980</v>
       </c>
       <c r="B16" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2656,10 +2656,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122821729</v>
+        <v>122821824</v>
       </c>
       <c r="B17" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2691,12 +2691,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524077</v>
+        <v>524055</v>
       </c>
       <c r="R17" t="n">
-        <v>6714076</v>
+        <v>6714048</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2760,12 +2760,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2792,10 +2787,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122821198</v>
+        <v>122821729</v>
       </c>
       <c r="B18" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2827,12 +2822,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2840,7 +2835,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2852,10 +2846,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524049</v>
+        <v>524077</v>
       </c>
       <c r="R18" t="n">
-        <v>6714097</v>
+        <v>6714076</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2867,7 +2861,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Falun</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2887,7 +2881,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2897,12 +2891,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Under klen gran. En överblommad.</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2911,7 +2905,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2933,7 +2926,7 @@
         <v>122821745</v>
       </c>
       <c r="B19" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3061,10 +3054,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122821824</v>
+        <v>122821198</v>
       </c>
       <c r="B20" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3109,6 +3102,7 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3120,10 +3114,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524055</v>
+        <v>524049</v>
       </c>
       <c r="R20" t="n">
-        <v>6714048</v>
+        <v>6714097</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3135,7 +3129,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Borlänge</t>
+          <t>Falun</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -3155,7 +3149,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3165,7 +3159,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Under klen gran. En överblommad.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3174,6 +3173,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -2384,7 +2384,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122821104</v>
+        <v>122821824</v>
       </c>
       <c r="B15" t="n">
         <v>98355</v>
@@ -2419,12 +2419,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524057</v>
+        <v>524055</v>
       </c>
       <c r="R15" t="n">
-        <v>6714094</v>
+        <v>6714048</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2488,12 +2488,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2656,7 +2651,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122821824</v>
+        <v>122821729</v>
       </c>
       <c r="B17" t="n">
         <v>98355</v>
@@ -2691,12 +2686,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2715,10 +2710,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524055</v>
+        <v>524077</v>
       </c>
       <c r="R17" t="n">
-        <v>6714048</v>
+        <v>6714076</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2750,7 +2745,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2760,7 +2755,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2787,7 +2787,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122821729</v>
+        <v>122821198</v>
       </c>
       <c r="B18" t="n">
         <v>98355</v>
@@ -2822,12 +2822,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2835,6 +2835,7 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2846,10 +2847,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524077</v>
+        <v>524049</v>
       </c>
       <c r="R18" t="n">
-        <v>6714076</v>
+        <v>6714097</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2861,7 +2862,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Borlänge</t>
+          <t>Falun</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2881,7 +2882,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2891,12 +2892,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>Under klen gran. En överblommad.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2905,6 +2906,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -3054,7 +3056,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122821198</v>
+        <v>122821104</v>
       </c>
       <c r="B20" t="n">
         <v>98355</v>
@@ -3089,12 +3091,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3102,7 +3104,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3114,10 +3115,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524049</v>
+        <v>524057</v>
       </c>
       <c r="R20" t="n">
-        <v>6714097</v>
+        <v>6714094</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3129,7 +3130,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Falun</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -3164,7 +3165,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Under klen gran. En överblommad.</t>
+          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3173,7 +3174,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2384,10 +2384,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122821824</v>
+        <v>122821104</v>
       </c>
       <c r="B15" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2419,12 +2419,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524055</v>
+        <v>524057</v>
       </c>
       <c r="R15" t="n">
-        <v>6714048</v>
+        <v>6714094</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2488,7 +2488,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2518,7 +2523,7 @@
         <v>122817980</v>
       </c>
       <c r="B16" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2651,10 +2656,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122821729</v>
+        <v>122821198</v>
       </c>
       <c r="B17" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2686,12 +2691,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2699,6 +2704,7 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2710,10 +2716,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524077</v>
+        <v>524049</v>
       </c>
       <c r="R17" t="n">
-        <v>6714076</v>
+        <v>6714097</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2725,7 +2731,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Borlänge</t>
+          <t>Falun</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2745,7 +2751,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2755,12 +2761,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>Under klen gran. En överblommad.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2769,6 +2775,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2787,10 +2794,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122821198</v>
+        <v>122821824</v>
       </c>
       <c r="B18" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2835,7 +2842,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2847,10 +2853,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524049</v>
+        <v>524055</v>
       </c>
       <c r="R18" t="n">
-        <v>6714097</v>
+        <v>6714048</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2862,7 +2868,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Falun</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2882,7 +2888,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2892,12 +2898,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Under klen gran. En överblommad.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2906,7 +2907,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2925,10 +2925,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122821745</v>
+        <v>122821729</v>
       </c>
       <c r="B19" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524080</v>
+        <v>524077</v>
       </c>
       <c r="R19" t="n">
-        <v>6714074</v>
+        <v>6714076</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3029,7 +3029,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3056,10 +3061,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122821104</v>
+        <v>122821745</v>
       </c>
       <c r="B20" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3091,12 +3096,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3115,10 +3120,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524057</v>
+        <v>524080</v>
       </c>
       <c r="R20" t="n">
-        <v>6714094</v>
+        <v>6714074</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3150,7 +3155,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3160,12 +3165,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3189,6 +3189,395 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122916997</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>524142</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6713729</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122915863</v>
+      </c>
+      <c r="B22" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>524025</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6713544</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>122917069</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>524154</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6713729</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3579,6 +3579,1409 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>122958064</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>524144</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6713722</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>122959354</v>
+      </c>
+      <c r="B25" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>524122</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6713710</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122957710</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>524145</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6713733</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Under klena granar.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>122958842</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57848</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Banvallen, Smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>524149</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6713704</v>
+      </c>
+      <c r="S27" t="n">
+        <v>50</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>122958244</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>524143</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6713721</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter. Kanske fler.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>122959503</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>524145</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6713672</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>122961337</v>
+      </c>
+      <c r="B30" t="n">
+        <v>90944</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>524040</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6713957</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>122958631</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>524136</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6713723</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Bladrosetter och en överblommad.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>122958484</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>524142</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6713723</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>122959453</v>
+      </c>
+      <c r="B33" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>524128</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6713669</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>122958550</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>524147</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6713728</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -2384,7 +2384,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122821104</v>
+        <v>122817980</v>
       </c>
       <c r="B15" t="n">
         <v>98357</v>
@@ -2419,12 +2419,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2439,14 +2439,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524057</v>
+        <v>524038</v>
       </c>
       <c r="R15" t="n">
-        <v>6714094</v>
+        <v>6713288</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2488,12 +2488,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
+          <t>10-15 bladrosetter under klen senvuxen gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2520,7 +2520,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122817980</v>
+        <v>122821824</v>
       </c>
       <c r="B16" t="n">
         <v>98357</v>
@@ -2575,14 +2575,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524038</v>
+        <v>524055</v>
       </c>
       <c r="R16" t="n">
-        <v>6713288</v>
+        <v>6714048</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2624,12 +2624,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>10-15 bladrosetter under klen senvuxen gran.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2794,7 +2789,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122821824</v>
+        <v>122821729</v>
       </c>
       <c r="B18" t="n">
         <v>98357</v>
@@ -2829,12 +2824,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2853,10 +2848,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524055</v>
+        <v>524077</v>
       </c>
       <c r="R18" t="n">
-        <v>6714048</v>
+        <v>6714076</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2888,7 +2883,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2898,7 +2893,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2925,7 +2925,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122821729</v>
+        <v>122821104</v>
       </c>
       <c r="B19" t="n">
         <v>98357</v>
@@ -2960,12 +2960,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524077</v>
+        <v>524057</v>
       </c>
       <c r="R19" t="n">
-        <v>6714076</v>
+        <v>6714094</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3192,7 +3192,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122916997</v>
+        <v>122917069</v>
       </c>
       <c r="B21" t="n">
         <v>98357</v>
@@ -3227,12 +3227,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524142</v>
+        <v>524154</v>
       </c>
       <c r="R21" t="n">
         <v>6713729</v>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3445,7 +3445,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122917069</v>
+        <v>122916997</v>
       </c>
       <c r="B23" t="n">
         <v>98357</v>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3504,7 +3504,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524154</v>
+        <v>524142</v>
       </c>
       <c r="R23" t="n">
         <v>6713729</v>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>En överblommad.</t>
+          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3581,10 +3581,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122958064</v>
+        <v>122959354</v>
       </c>
       <c r="B24" t="n">
-        <v>98357</v>
+        <v>8441</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3593,45 +3593,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3640,10 +3626,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524144</v>
+        <v>524122</v>
       </c>
       <c r="R24" t="n">
-        <v>6713722</v>
+        <v>6713710</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3675,7 +3661,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3685,12 +3671,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3717,10 +3698,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122959354</v>
+        <v>122958064</v>
       </c>
       <c r="B25" t="n">
-        <v>8441</v>
+        <v>98357</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3729,31 +3710,45 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3762,10 +3757,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524122</v>
+        <v>524144</v>
       </c>
       <c r="R25" t="n">
-        <v>6713710</v>
+        <v>6713722</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3797,7 +3792,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3807,7 +3802,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3965,10 +3965,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122958842</v>
+        <v>122959503</v>
       </c>
       <c r="B27" t="n">
-        <v>57848</v>
+        <v>98357</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3977,25 +3977,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -4003,24 +4003,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Banvallen, Smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524149</v>
+        <v>524145</v>
       </c>
       <c r="R27" t="n">
-        <v>6713704</v>
+        <v>6713672</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4049,7 +4054,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4059,7 +4064,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4086,10 +4091,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122958244</v>
+        <v>122961337</v>
       </c>
       <c r="B28" t="n">
-        <v>98357</v>
+        <v>90944</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4098,57 +4103,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524143</v>
+        <v>524040</v>
       </c>
       <c r="R28" t="n">
-        <v>6713721</v>
+        <v>6713957</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4180,7 +4169,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4190,12 +4179,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter. Kanske fler.</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4204,6 +4188,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4222,10 +4207,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122959503</v>
+        <v>122958842</v>
       </c>
       <c r="B29" t="n">
-        <v>98357</v>
+        <v>57848</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4234,25 +4219,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4260,29 +4245,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvallen, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524145</v>
+        <v>524149</v>
       </c>
       <c r="R29" t="n">
-        <v>6713672</v>
+        <v>6713704</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4311,7 +4291,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4321,7 +4301,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4348,10 +4328,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122961337</v>
+        <v>122958484</v>
       </c>
       <c r="B30" t="n">
-        <v>90944</v>
+        <v>98357</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4360,41 +4340,57 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524040</v>
+        <v>524142</v>
       </c>
       <c r="R30" t="n">
-        <v>6713957</v>
+        <v>6713723</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4426,7 +4422,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4436,7 +4432,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4445,7 +4441,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4464,10 +4459,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122958631</v>
+        <v>122959453</v>
       </c>
       <c r="B31" t="n">
-        <v>98357</v>
+        <v>8441</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4476,45 +4471,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4523,10 +4504,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524136</v>
+        <v>524128</v>
       </c>
       <c r="R31" t="n">
-        <v>6713723</v>
+        <v>6713669</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4558,7 +4539,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4568,12 +4549,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Bladrosetter och en överblommad.</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4600,7 +4576,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122958484</v>
+        <v>122958631</v>
       </c>
       <c r="B32" t="n">
         <v>98357</v>
@@ -4635,7 +4611,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4659,7 +4635,7 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524142</v>
+        <v>524136</v>
       </c>
       <c r="R32" t="n">
         <v>6713723</v>
@@ -4694,7 +4670,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4704,7 +4680,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Bladrosetter och en överblommad.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4731,10 +4712,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122959453</v>
+        <v>122958244</v>
       </c>
       <c r="B33" t="n">
-        <v>8441</v>
+        <v>98357</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4743,31 +4724,45 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4776,10 +4771,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524128</v>
+        <v>524143</v>
       </c>
       <c r="R33" t="n">
-        <v>6713669</v>
+        <v>6713721</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4811,7 +4806,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4821,7 +4816,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter. Kanske fler.</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -2384,10 +2384,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122817980</v>
+        <v>122821198</v>
       </c>
       <c r="B15" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2432,6 +2432,7 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2439,14 +2440,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524038</v>
+        <v>524049</v>
       </c>
       <c r="R15" t="n">
-        <v>6713288</v>
+        <v>6714097</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2458,7 +2459,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Borlänge</t>
+          <t>Falun</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2478,7 +2479,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2488,12 +2489,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>10-15 bladrosetter under klen senvuxen gran.</t>
+          <t>Under klen gran. En överblommad.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2502,6 +2503,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2520,10 +2522,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122821824</v>
+        <v>122821745</v>
       </c>
       <c r="B16" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2560,7 +2562,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2579,10 +2581,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524055</v>
+        <v>524080</v>
       </c>
       <c r="R16" t="n">
-        <v>6714048</v>
+        <v>6714074</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2614,7 +2616,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2624,7 +2626,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2651,10 +2653,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122821198</v>
+        <v>122821104</v>
       </c>
       <c r="B17" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2686,12 +2688,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2699,7 +2701,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2711,10 +2712,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524049</v>
+        <v>524057</v>
       </c>
       <c r="R17" t="n">
-        <v>6714097</v>
+        <v>6714094</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2726,7 +2727,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Falun</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2761,7 +2762,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Under klen gran. En överblommad.</t>
+          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2770,7 +2771,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2789,10 +2789,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122821729</v>
+        <v>122817980</v>
       </c>
       <c r="B18" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2824,12 +2824,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2844,14 +2844,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524077</v>
+        <v>524038</v>
       </c>
       <c r="R18" t="n">
-        <v>6714076</v>
+        <v>6713288</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2893,12 +2893,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>10-15 bladrosetter under klen senvuxen gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2925,10 +2925,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122821104</v>
+        <v>122821824</v>
       </c>
       <c r="B19" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2960,12 +2960,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524057</v>
+        <v>524055</v>
       </c>
       <c r="R19" t="n">
-        <v>6714094</v>
+        <v>6714048</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3029,12 +3029,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3061,10 +3056,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122821745</v>
+        <v>122821729</v>
       </c>
       <c r="B20" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3096,7 +3091,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3120,10 +3115,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524080</v>
+        <v>524077</v>
       </c>
       <c r="R20" t="n">
-        <v>6714074</v>
+        <v>6714076</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3155,7 +3150,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3165,7 +3160,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3192,10 +3192,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122917069</v>
+        <v>122916997</v>
       </c>
       <c r="B21" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3227,12 +3227,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524154</v>
+        <v>524142</v>
       </c>
       <c r="R21" t="n">
         <v>6713729</v>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>En överblommad.</t>
+          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3328,10 +3328,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122915863</v>
+        <v>122917069</v>
       </c>
       <c r="B22" t="n">
-        <v>8441</v>
+        <v>98365</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3340,43 +3340,57 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524025</v>
+        <v>524154</v>
       </c>
       <c r="R22" t="n">
-        <v>6713544</v>
+        <v>6713729</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3408,7 +3422,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3418,7 +3432,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3445,10 +3464,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122916997</v>
+        <v>122915863</v>
       </c>
       <c r="B23" t="n">
-        <v>98357</v>
+        <v>8441</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3457,57 +3476,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524142</v>
+        <v>524025</v>
       </c>
       <c r="R23" t="n">
-        <v>6713729</v>
+        <v>6713544</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3539,7 +3544,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3549,12 +3554,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:33</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3581,10 +3581,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122959354</v>
+        <v>122959503</v>
       </c>
       <c r="B24" t="n">
-        <v>8441</v>
+        <v>98365</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3593,31 +3593,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3626,10 +3635,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524122</v>
+        <v>524145</v>
       </c>
       <c r="R24" t="n">
-        <v>6713710</v>
+        <v>6713672</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3661,7 +3670,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3671,7 +3680,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3698,10 +3707,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122958064</v>
+        <v>122958484</v>
       </c>
       <c r="B25" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3733,12 +3742,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3757,10 +3766,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524144</v>
+        <v>524142</v>
       </c>
       <c r="R25" t="n">
-        <v>6713722</v>
+        <v>6713723</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3792,7 +3801,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3802,12 +3811,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3834,10 +3838,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122957710</v>
+        <v>122958244</v>
       </c>
       <c r="B26" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3882,16 +3886,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524145</v>
+        <v>524143</v>
       </c>
       <c r="R26" t="n">
-        <v>6713733</v>
+        <v>6713721</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3923,7 +3932,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3933,12 +3942,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Under klena granar.</t>
+          <t>Ca 20 bladrosetter. Kanske fler.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3965,10 +3974,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122959503</v>
+        <v>122957710</v>
       </c>
       <c r="B27" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4000,12 +4009,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -4022,7 +4031,7 @@
         <v>524145</v>
       </c>
       <c r="R27" t="n">
-        <v>6713672</v>
+        <v>6713733</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4054,7 +4063,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4064,7 +4073,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Under klena granar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4091,10 +4105,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122961337</v>
+        <v>122958631</v>
       </c>
       <c r="B28" t="n">
-        <v>90944</v>
+        <v>98365</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4103,41 +4117,57 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524040</v>
+        <v>524136</v>
       </c>
       <c r="R28" t="n">
-        <v>6713957</v>
+        <v>6713723</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4169,7 +4199,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4179,7 +4209,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Bladrosetter och en överblommad.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4188,7 +4223,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4207,10 +4241,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122958842</v>
+        <v>122961337</v>
       </c>
       <c r="B29" t="n">
-        <v>57848</v>
+        <v>90952</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4219,50 +4253,44 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Banvallen, Smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524149</v>
+        <v>524040</v>
       </c>
       <c r="R29" t="n">
-        <v>6713704</v>
+        <v>6713957</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4291,7 +4319,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4301,7 +4329,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4310,6 +4338,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4328,10 +4357,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122958484</v>
+        <v>122959354</v>
       </c>
       <c r="B30" t="n">
-        <v>98357</v>
+        <v>8441</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4340,45 +4369,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4387,10 +4402,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524142</v>
+        <v>524122</v>
       </c>
       <c r="R30" t="n">
-        <v>6713723</v>
+        <v>6713710</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4422,7 +4437,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4432,7 +4447,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4459,10 +4474,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122959453</v>
+        <v>122958842</v>
       </c>
       <c r="B31" t="n">
-        <v>8441</v>
+        <v>57848</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4475,42 +4490,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvallen, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524128</v>
+        <v>524149</v>
       </c>
       <c r="R31" t="n">
-        <v>6713669</v>
+        <v>6713704</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4539,7 +4558,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4549,7 +4568,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4576,10 +4595,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122958631</v>
+        <v>122958064</v>
       </c>
       <c r="B32" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4611,12 +4630,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4635,10 +4654,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524136</v>
+        <v>524144</v>
       </c>
       <c r="R32" t="n">
-        <v>6713723</v>
+        <v>6713722</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4670,7 +4689,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4680,12 +4699,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Bladrosetter och en överblommad.</t>
+          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4712,10 +4731,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122958244</v>
+        <v>122959453</v>
       </c>
       <c r="B33" t="n">
-        <v>98357</v>
+        <v>8441</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4724,45 +4743,31 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4771,10 +4776,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524143</v>
+        <v>524128</v>
       </c>
       <c r="R33" t="n">
-        <v>6713721</v>
+        <v>6713669</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4806,7 +4811,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4816,12 +4821,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter. Kanske fler.</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4851,7 +4851,7 @@
         <v>122958550</v>
       </c>
       <c r="B34" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -2384,7 +2384,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122821198</v>
+        <v>122821745</v>
       </c>
       <c r="B15" t="n">
         <v>98365</v>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2432,7 +2432,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2444,10 +2443,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524049</v>
+        <v>524080</v>
       </c>
       <c r="R15" t="n">
-        <v>6714097</v>
+        <v>6714074</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2459,7 +2458,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Falun</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2479,7 +2478,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2489,12 +2488,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Under klen gran. En överblommad.</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2503,7 +2497,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2522,7 +2515,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122821745</v>
+        <v>122821824</v>
       </c>
       <c r="B16" t="n">
         <v>98365</v>
@@ -2562,7 +2555,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2581,10 +2574,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524080</v>
+        <v>524055</v>
       </c>
       <c r="R16" t="n">
-        <v>6714074</v>
+        <v>6714048</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2616,7 +2609,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2626,7 +2619,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2653,7 +2646,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122821104</v>
+        <v>122821729</v>
       </c>
       <c r="B17" t="n">
         <v>98365</v>
@@ -2688,12 +2681,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2712,10 +2705,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524057</v>
+        <v>524077</v>
       </c>
       <c r="R17" t="n">
-        <v>6714094</v>
+        <v>6714076</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2747,7 +2740,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2757,12 +2750,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2789,7 +2782,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122817980</v>
+        <v>122821104</v>
       </c>
       <c r="B18" t="n">
         <v>98365</v>
@@ -2824,12 +2817,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2844,14 +2837,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524038</v>
+        <v>524057</v>
       </c>
       <c r="R18" t="n">
-        <v>6713288</v>
+        <v>6714094</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2883,7 +2876,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2893,12 +2886,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>10-15 bladrosetter under klen senvuxen gran.</t>
+          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2925,7 +2918,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122821824</v>
+        <v>122821198</v>
       </c>
       <c r="B19" t="n">
         <v>98365</v>
@@ -2973,6 +2966,7 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2984,10 +2978,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524055</v>
+        <v>524049</v>
       </c>
       <c r="R19" t="n">
-        <v>6714048</v>
+        <v>6714097</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2999,7 +2993,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Borlänge</t>
+          <t>Falun</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -3019,7 +3013,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3029,7 +3023,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Under klen gran. En överblommad.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3038,6 +3037,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3056,7 +3056,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122821729</v>
+        <v>122817980</v>
       </c>
       <c r="B20" t="n">
         <v>98365</v>
@@ -3091,12 +3091,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3111,14 +3111,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524077</v>
+        <v>524038</v>
       </c>
       <c r="R20" t="n">
-        <v>6714076</v>
+        <v>6713288</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>10-15 bladrosetter under klen senvuxen gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3192,10 +3192,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122916997</v>
+        <v>122915863</v>
       </c>
       <c r="B21" t="n">
-        <v>98365</v>
+        <v>8441</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3204,57 +3204,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524142</v>
+        <v>524025</v>
       </c>
       <c r="R21" t="n">
-        <v>6713729</v>
+        <v>6713544</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3286,7 +3272,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3296,12 +3282,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:33</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3464,10 +3445,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122915863</v>
+        <v>122916997</v>
       </c>
       <c r="B23" t="n">
-        <v>8441</v>
+        <v>98365</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3476,43 +3457,57 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524025</v>
+        <v>524142</v>
       </c>
       <c r="R23" t="n">
-        <v>6713544</v>
+        <v>6713729</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3544,7 +3539,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3554,7 +3549,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3581,7 +3581,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122959503</v>
+        <v>122958631</v>
       </c>
       <c r="B24" t="n">
         <v>98365</v>
@@ -3616,12 +3616,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3629,16 +3629,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524145</v>
+        <v>524136</v>
       </c>
       <c r="R24" t="n">
-        <v>6713672</v>
+        <v>6713723</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3670,7 +3675,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3680,7 +3685,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Bladrosetter och en överblommad.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3838,10 +3848,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122958244</v>
+        <v>122961337</v>
       </c>
       <c r="B26" t="n">
-        <v>98365</v>
+        <v>90952</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3850,57 +3860,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524143</v>
+        <v>524040</v>
       </c>
       <c r="R26" t="n">
-        <v>6713721</v>
+        <v>6713957</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3932,7 +3926,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3942,12 +3936,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter. Kanske fler.</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3956,6 +3945,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -4105,10 +4095,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122958631</v>
+        <v>122959453</v>
       </c>
       <c r="B28" t="n">
-        <v>98365</v>
+        <v>8441</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4117,45 +4107,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -4164,10 +4140,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524136</v>
+        <v>524128</v>
       </c>
       <c r="R28" t="n">
-        <v>6713723</v>
+        <v>6713669</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4199,7 +4175,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4209,12 +4185,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Bladrosetter och en överblommad.</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4241,10 +4212,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122961337</v>
+        <v>122958064</v>
       </c>
       <c r="B29" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4253,41 +4224,57 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524040</v>
+        <v>524144</v>
       </c>
       <c r="R29" t="n">
-        <v>6713957</v>
+        <v>6713722</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4319,7 +4306,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4329,7 +4316,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4338,7 +4330,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4474,10 +4465,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122958842</v>
+        <v>122958550</v>
       </c>
       <c r="B31" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4486,25 +4477,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4512,24 +4503,34 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Banvallen, Smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524149</v>
+        <v>524147</v>
       </c>
       <c r="R31" t="n">
-        <v>6713704</v>
+        <v>6713728</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4558,7 +4559,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4568,7 +4569,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4595,7 +4601,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122958064</v>
+        <v>122959503</v>
       </c>
       <c r="B32" t="n">
         <v>98365</v>
@@ -4635,7 +4641,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4643,21 +4649,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524144</v>
+        <v>524145</v>
       </c>
       <c r="R32" t="n">
-        <v>6713722</v>
+        <v>6713672</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4689,7 +4690,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4699,12 +4700,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4731,10 +4727,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122959453</v>
+        <v>122958842</v>
       </c>
       <c r="B33" t="n">
-        <v>8441</v>
+        <v>57848</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4747,42 +4743,46 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvallen, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524128</v>
+        <v>524149</v>
       </c>
       <c r="R33" t="n">
-        <v>6713669</v>
+        <v>6713704</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4848,7 +4848,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122958550</v>
+        <v>122958244</v>
       </c>
       <c r="B34" t="n">
         <v>98365</v>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4907,10 +4907,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524147</v>
+        <v>524143</v>
       </c>
       <c r="R34" t="n">
-        <v>6713728</v>
+        <v>6713721</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4942,7 +4942,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>Ca 20 bladrosetter. Kanske fler.</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -3581,10 +3581,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122958631</v>
+        <v>122961337</v>
       </c>
       <c r="B24" t="n">
-        <v>98365</v>
+        <v>90952</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3593,57 +3593,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524136</v>
+        <v>524040</v>
       </c>
       <c r="R24" t="n">
-        <v>6713723</v>
+        <v>6713957</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3675,7 +3659,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3685,12 +3669,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Bladrosetter och en överblommad.</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3699,6 +3678,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3717,7 +3697,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122958484</v>
+        <v>122958631</v>
       </c>
       <c r="B25" t="n">
         <v>98365</v>
@@ -3752,7 +3732,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3776,7 +3756,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524142</v>
+        <v>524136</v>
       </c>
       <c r="R25" t="n">
         <v>6713723</v>
@@ -3811,7 +3791,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3821,7 +3801,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Bladrosetter och en överblommad.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3848,10 +3833,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122961337</v>
+        <v>122958484</v>
       </c>
       <c r="B26" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3860,41 +3845,57 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524040</v>
+        <v>524142</v>
       </c>
       <c r="R26" t="n">
-        <v>6713957</v>
+        <v>6713723</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3926,7 +3927,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3936,7 +3937,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3945,7 +3946,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -2515,7 +2515,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122821824</v>
+        <v>122821104</v>
       </c>
       <c r="B16" t="n">
         <v>98365</v>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524055</v>
+        <v>524057</v>
       </c>
       <c r="R16" t="n">
-        <v>6714048</v>
+        <v>6714094</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2619,7 +2619,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2646,7 +2651,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122821729</v>
+        <v>122821824</v>
       </c>
       <c r="B17" t="n">
         <v>98365</v>
@@ -2681,12 +2686,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2705,10 +2710,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524077</v>
+        <v>524055</v>
       </c>
       <c r="R17" t="n">
-        <v>6714076</v>
+        <v>6714048</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2740,7 +2745,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2750,12 +2755,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2782,7 +2782,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122821104</v>
+        <v>122821729</v>
       </c>
       <c r="B18" t="n">
         <v>98365</v>
@@ -2817,12 +2817,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2841,10 +2841,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524057</v>
+        <v>524077</v>
       </c>
       <c r="R18" t="n">
-        <v>6714094</v>
+        <v>6714076</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2886,12 +2886,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2918,7 +2918,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122821198</v>
+        <v>122817980</v>
       </c>
       <c r="B19" t="n">
         <v>98365</v>
@@ -2966,7 +2966,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2974,14 +2973,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524049</v>
+        <v>524038</v>
       </c>
       <c r="R19" t="n">
-        <v>6714097</v>
+        <v>6713288</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2993,7 +2992,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Falun</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -3013,7 +3012,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3023,12 +3022,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Under klen gran. En överblommad.</t>
+          <t>10-15 bladrosetter under klen senvuxen gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3037,7 +3036,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3056,7 +3054,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122817980</v>
+        <v>122821198</v>
       </c>
       <c r="B20" t="n">
         <v>98365</v>
@@ -3104,6 +3102,7 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3111,14 +3110,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524038</v>
+        <v>524049</v>
       </c>
       <c r="R20" t="n">
-        <v>6713288</v>
+        <v>6714097</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3130,7 +3129,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Borlänge</t>
+          <t>Falun</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -3150,7 +3149,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3160,12 +3159,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>10-15 bladrosetter under klen senvuxen gran.</t>
+          <t>Under klen gran. En överblommad.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3174,6 +3173,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3192,10 +3192,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122915863</v>
+        <v>122916997</v>
       </c>
       <c r="B21" t="n">
-        <v>8441</v>
+        <v>98365</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3204,43 +3204,57 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524025</v>
+        <v>524142</v>
       </c>
       <c r="R21" t="n">
-        <v>6713544</v>
+        <v>6713729</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3272,7 +3286,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3282,7 +3296,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3445,10 +3464,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122916997</v>
+        <v>122915863</v>
       </c>
       <c r="B23" t="n">
-        <v>98365</v>
+        <v>8441</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3457,57 +3476,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524142</v>
+        <v>524025</v>
       </c>
       <c r="R23" t="n">
-        <v>6713729</v>
+        <v>6713544</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3539,7 +3544,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3549,12 +3554,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:33</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3581,10 +3581,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122961337</v>
+        <v>122958484</v>
       </c>
       <c r="B24" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3593,41 +3593,57 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524040</v>
+        <v>524142</v>
       </c>
       <c r="R24" t="n">
-        <v>6713957</v>
+        <v>6713723</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3659,7 +3675,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3669,7 +3685,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3678,7 +3694,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3697,7 +3712,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122958631</v>
+        <v>122958550</v>
       </c>
       <c r="B25" t="n">
         <v>98365</v>
@@ -3732,7 +3747,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3756,10 +3771,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524136</v>
+        <v>524147</v>
       </c>
       <c r="R25" t="n">
-        <v>6713723</v>
+        <v>6713728</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3791,7 +3806,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3801,12 +3816,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Bladrosetter och en överblommad.</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3833,10 +3848,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122958484</v>
+        <v>122959354</v>
       </c>
       <c r="B26" t="n">
-        <v>98365</v>
+        <v>8441</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3845,45 +3860,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3892,10 +3893,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524142</v>
+        <v>524122</v>
       </c>
       <c r="R26" t="n">
-        <v>6713723</v>
+        <v>6713710</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3927,7 +3928,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3937,7 +3938,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3964,7 +3965,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122957710</v>
+        <v>122958064</v>
       </c>
       <c r="B27" t="n">
         <v>98365</v>
@@ -3999,12 +4000,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -4012,16 +4013,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524145</v>
+        <v>524144</v>
       </c>
       <c r="R27" t="n">
-        <v>6713733</v>
+        <v>6713722</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4053,7 +4059,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4063,12 +4069,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Under klena granar.</t>
+          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4095,10 +4101,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122959453</v>
+        <v>122958842</v>
       </c>
       <c r="B28" t="n">
-        <v>8441</v>
+        <v>57848</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4111,42 +4117,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvallen, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524128</v>
+        <v>524149</v>
       </c>
       <c r="R28" t="n">
-        <v>6713669</v>
+        <v>6713704</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4175,7 +4185,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4185,7 +4195,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4212,10 +4222,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122958064</v>
+        <v>122959453</v>
       </c>
       <c r="B29" t="n">
-        <v>98365</v>
+        <v>8441</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4224,45 +4234,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4271,10 +4267,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524144</v>
+        <v>524128</v>
       </c>
       <c r="R29" t="n">
-        <v>6713722</v>
+        <v>6713669</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4306,7 +4302,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4316,12 +4312,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4348,10 +4339,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122959354</v>
+        <v>122959503</v>
       </c>
       <c r="B30" t="n">
-        <v>8441</v>
+        <v>98365</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4360,31 +4351,40 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4393,10 +4393,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524122</v>
+        <v>524145</v>
       </c>
       <c r="R30" t="n">
-        <v>6713710</v>
+        <v>6713672</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4465,7 +4465,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122958550</v>
+        <v>122958244</v>
       </c>
       <c r="B31" t="n">
         <v>98365</v>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4524,10 +4524,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524147</v>
+        <v>524143</v>
       </c>
       <c r="R31" t="n">
-        <v>6713728</v>
+        <v>6713721</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>Ca 20 bladrosetter. Kanske fler.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4601,10 +4601,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122959503</v>
+        <v>122961337</v>
       </c>
       <c r="B32" t="n">
-        <v>98365</v>
+        <v>90952</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4613,52 +4613,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524145</v>
+        <v>524040</v>
       </c>
       <c r="R32" t="n">
-        <v>6713672</v>
+        <v>6713957</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4690,7 +4679,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4700,7 +4689,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4709,6 +4698,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4727,10 +4717,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122958842</v>
+        <v>122957710</v>
       </c>
       <c r="B33" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4739,50 +4729,55 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Banvallen, Smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524149</v>
+        <v>524145</v>
       </c>
       <c r="R33" t="n">
-        <v>6713704</v>
+        <v>6713733</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4811,7 +4806,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4821,7 +4816,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Under klena granar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4848,7 +4848,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122958244</v>
+        <v>122958631</v>
       </c>
       <c r="B34" t="n">
         <v>98365</v>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4907,10 +4907,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524143</v>
+        <v>524136</v>
       </c>
       <c r="R34" t="n">
-        <v>6713721</v>
+        <v>6713723</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4942,7 +4942,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ca 20 bladrosetter. Kanske fler.</t>
+          <t>Bladrosetter och en överblommad.</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -2515,7 +2515,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122821104</v>
+        <v>122821198</v>
       </c>
       <c r="B16" t="n">
         <v>98365</v>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2563,6 +2563,7 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2574,10 +2575,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524057</v>
+        <v>524049</v>
       </c>
       <c r="R16" t="n">
-        <v>6714094</v>
+        <v>6714097</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2589,7 +2590,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Borlänge</t>
+          <t>Falun</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2624,7 +2625,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
+          <t>Under klen gran. En överblommad.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2633,6 +2634,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2651,7 +2653,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122821824</v>
+        <v>122821104</v>
       </c>
       <c r="B17" t="n">
         <v>98365</v>
@@ -2686,12 +2688,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2710,10 +2712,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524055</v>
+        <v>524057</v>
       </c>
       <c r="R17" t="n">
-        <v>6714048</v>
+        <v>6714094</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2745,7 +2747,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2755,7 +2757,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3054,7 +3061,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122821198</v>
+        <v>122821824</v>
       </c>
       <c r="B20" t="n">
         <v>98365</v>
@@ -3102,7 +3109,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3114,10 +3120,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524049</v>
+        <v>524055</v>
       </c>
       <c r="R20" t="n">
-        <v>6714097</v>
+        <v>6714048</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3129,7 +3135,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Falun</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -3149,7 +3155,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3159,12 +3165,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Under klen gran. En överblommad.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3173,7 +3174,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3328,10 +3328,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122917069</v>
+        <v>122915863</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>8441</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3340,57 +3340,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524154</v>
+        <v>524025</v>
       </c>
       <c r="R22" t="n">
-        <v>6713729</v>
+        <v>6713544</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3422,7 +3408,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3432,12 +3418,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:36</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3464,10 +3445,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122915863</v>
+        <v>122917069</v>
       </c>
       <c r="B23" t="n">
-        <v>8441</v>
+        <v>98365</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3476,43 +3457,57 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524025</v>
+        <v>524154</v>
       </c>
       <c r="R23" t="n">
-        <v>6713544</v>
+        <v>6713729</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3544,7 +3539,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3554,7 +3549,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3581,10 +3581,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122958484</v>
+        <v>122961337</v>
       </c>
       <c r="B24" t="n">
-        <v>98365</v>
+        <v>90952</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3593,57 +3593,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524142</v>
+        <v>524040</v>
       </c>
       <c r="R24" t="n">
-        <v>6713723</v>
+        <v>6713957</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3675,7 +3659,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3685,7 +3669,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3694,6 +3678,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3712,7 +3697,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122958550</v>
+        <v>122959503</v>
       </c>
       <c r="B25" t="n">
         <v>98365</v>
@@ -3752,7 +3737,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3760,21 +3745,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524147</v>
+        <v>524145</v>
       </c>
       <c r="R25" t="n">
-        <v>6713728</v>
+        <v>6713672</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3806,7 +3786,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3816,12 +3796,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3848,7 +3823,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122959354</v>
+        <v>122959453</v>
       </c>
       <c r="B26" t="n">
         <v>8441</v>
@@ -3893,10 +3868,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524122</v>
+        <v>524128</v>
       </c>
       <c r="R26" t="n">
-        <v>6713710</v>
+        <v>6713669</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3928,7 +3903,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3938,7 +3913,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3965,7 +3940,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122958064</v>
+        <v>122958550</v>
       </c>
       <c r="B27" t="n">
         <v>98365</v>
@@ -4005,7 +3980,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -4024,10 +3999,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524144</v>
+        <v>524147</v>
       </c>
       <c r="R27" t="n">
-        <v>6713722</v>
+        <v>6713728</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4059,7 +4034,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4069,12 +4044,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4101,10 +4076,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122958842</v>
+        <v>122959354</v>
       </c>
       <c r="B28" t="n">
-        <v>57848</v>
+        <v>8441</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4117,46 +4092,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Banvallen, Smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524149</v>
+        <v>524122</v>
       </c>
       <c r="R28" t="n">
-        <v>6713704</v>
+        <v>6713710</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4185,7 +4156,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4195,7 +4166,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4222,10 +4193,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122959453</v>
+        <v>122957710</v>
       </c>
       <c r="B29" t="n">
-        <v>8441</v>
+        <v>98365</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4234,31 +4205,40 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4267,10 +4247,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524128</v>
+        <v>524145</v>
       </c>
       <c r="R29" t="n">
-        <v>6713669</v>
+        <v>6713733</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4302,7 +4282,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4312,7 +4292,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Under klena granar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4339,7 +4324,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122959503</v>
+        <v>122958244</v>
       </c>
       <c r="B30" t="n">
         <v>98365</v>
@@ -4374,12 +4359,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4387,16 +4372,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524145</v>
+        <v>524143</v>
       </c>
       <c r="R30" t="n">
-        <v>6713672</v>
+        <v>6713721</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4428,7 +4418,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4438,7 +4428,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter. Kanske fler.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4465,10 +4460,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122958244</v>
+        <v>122958842</v>
       </c>
       <c r="B31" t="n">
-        <v>98365</v>
+        <v>57848</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4477,60 +4472,50 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvallen, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524143</v>
+        <v>524149</v>
       </c>
       <c r="R31" t="n">
-        <v>6713721</v>
+        <v>6713704</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4559,7 +4544,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4569,12 +4554,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter. Kanske fler.</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4601,10 +4581,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122961337</v>
+        <v>122958484</v>
       </c>
       <c r="B32" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4613,41 +4593,57 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524040</v>
+        <v>524142</v>
       </c>
       <c r="R32" t="n">
-        <v>6713957</v>
+        <v>6713723</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4679,7 +4675,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4689,7 +4685,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4698,7 +4694,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4717,7 +4712,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122957710</v>
+        <v>122958631</v>
       </c>
       <c r="B33" t="n">
         <v>98365</v>
@@ -4752,7 +4747,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4765,16 +4760,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524145</v>
+        <v>524136</v>
       </c>
       <c r="R33" t="n">
-        <v>6713733</v>
+        <v>6713723</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4816,12 +4816,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Under klena granar.</t>
+          <t>Bladrosetter och en överblommad.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4848,7 +4848,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122958631</v>
+        <v>122958064</v>
       </c>
       <c r="B34" t="n">
         <v>98365</v>
@@ -4883,12 +4883,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4907,10 +4907,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524136</v>
+        <v>524144</v>
       </c>
       <c r="R34" t="n">
-        <v>6713723</v>
+        <v>6713722</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4942,7 +4942,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Bladrosetter och en överblommad.</t>
+          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4982,6 +4982,1541 @@
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>123412973</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98368</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>524116</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6713634</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>123413078</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98368</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>524102</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6713632</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>123412439</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98368</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>524137</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6713646</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Inom ca 5 kv/dm.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>123413856</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98368</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>524041</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6713443</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>123414352</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98368</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>524098</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6713405</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>123414270</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98368</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>524085</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6713390</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>123412257</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98368</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>524123</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6713637</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>123412367</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98368</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>524136</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6713648</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>123413119</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98368</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>524101</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6713638</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Spridda sporadiskt över ytan.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>123413726</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98368</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>524030</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6713469</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>123413633</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57497</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>524031</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6713503</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>123412326</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98368</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>524122</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6713640</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -2387,7 +2387,7 @@
         <v>122821745</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2515,10 +2515,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122821198</v>
+        <v>122817980</v>
       </c>
       <c r="B16" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2563,7 +2563,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2571,14 +2570,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524049</v>
+        <v>524038</v>
       </c>
       <c r="R16" t="n">
-        <v>6714097</v>
+        <v>6713288</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2590,7 +2589,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Falun</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2610,7 +2609,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2620,12 +2619,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Under klen gran. En överblommad.</t>
+          <t>10-15 bladrosetter under klen senvuxen gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2634,7 +2633,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2653,10 +2651,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122821104</v>
+        <v>122821729</v>
       </c>
       <c r="B17" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2688,12 +2686,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2712,10 +2710,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524057</v>
+        <v>524077</v>
       </c>
       <c r="R17" t="n">
-        <v>6714094</v>
+        <v>6714076</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2747,7 +2745,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2757,12 +2755,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2789,10 +2787,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122821729</v>
+        <v>122821104</v>
       </c>
       <c r="B18" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2824,12 +2822,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2848,10 +2846,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524077</v>
+        <v>524057</v>
       </c>
       <c r="R18" t="n">
-        <v>6714076</v>
+        <v>6714094</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2883,7 +2881,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2893,12 +2891,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2925,10 +2923,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122817980</v>
+        <v>122821824</v>
       </c>
       <c r="B19" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2980,14 +2978,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524038</v>
+        <v>524055</v>
       </c>
       <c r="R19" t="n">
-        <v>6713288</v>
+        <v>6714048</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3019,7 +3017,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3029,12 +3027,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>10-15 bladrosetter under klen senvuxen gran.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3061,10 +3054,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122821824</v>
+        <v>122821198</v>
       </c>
       <c r="B20" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3109,6 +3102,7 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3120,10 +3114,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524055</v>
+        <v>524049</v>
       </c>
       <c r="R20" t="n">
-        <v>6714048</v>
+        <v>6714097</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3135,7 +3129,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Borlänge</t>
+          <t>Falun</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -3155,7 +3149,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3165,7 +3159,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Under klen gran. En överblommad.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3174,6 +3173,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3192,10 +3192,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122916997</v>
+        <v>122917069</v>
       </c>
       <c r="B21" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3227,12 +3227,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524142</v>
+        <v>524154</v>
       </c>
       <c r="R21" t="n">
         <v>6713729</v>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3445,10 +3445,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122917069</v>
+        <v>122916997</v>
       </c>
       <c r="B23" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3504,7 +3504,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524154</v>
+        <v>524142</v>
       </c>
       <c r="R23" t="n">
         <v>6713729</v>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>En överblommad.</t>
+          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3581,10 +3581,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122961337</v>
+        <v>122958244</v>
       </c>
       <c r="B24" t="n">
-        <v>90952</v>
+        <v>98368</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3593,41 +3593,57 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524040</v>
+        <v>524143</v>
       </c>
       <c r="R24" t="n">
-        <v>6713957</v>
+        <v>6713721</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3659,7 +3675,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3669,7 +3685,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter. Kanske fler.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3678,7 +3699,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3697,10 +3717,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122959503</v>
+        <v>122958631</v>
       </c>
       <c r="B25" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3732,12 +3752,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3745,16 +3765,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524145</v>
+        <v>524136</v>
       </c>
       <c r="R25" t="n">
-        <v>6713672</v>
+        <v>6713723</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3786,7 +3811,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3796,7 +3821,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Bladrosetter och en överblommad.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3823,10 +3853,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122959453</v>
+        <v>122961337</v>
       </c>
       <c r="B26" t="n">
-        <v>8441</v>
+        <v>90955</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3835,43 +3865,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524128</v>
+        <v>524040</v>
       </c>
       <c r="R26" t="n">
-        <v>6713669</v>
+        <v>6713957</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3903,7 +3931,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3913,7 +3941,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3922,6 +3950,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3940,10 +3969,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122958550</v>
+        <v>122957710</v>
       </c>
       <c r="B27" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3975,7 +4004,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3988,21 +4017,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524147</v>
+        <v>524145</v>
       </c>
       <c r="R27" t="n">
-        <v>6713728</v>
+        <v>6713733</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4034,7 +4058,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4044,12 +4068,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>Under klena granar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4076,7 +4100,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122959354</v>
+        <v>122959453</v>
       </c>
       <c r="B28" t="n">
         <v>8441</v>
@@ -4121,10 +4145,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524122</v>
+        <v>524128</v>
       </c>
       <c r="R28" t="n">
-        <v>6713710</v>
+        <v>6713669</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4156,7 +4180,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4166,7 +4190,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4193,10 +4217,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122957710</v>
+        <v>122958842</v>
       </c>
       <c r="B29" t="n">
-        <v>98365</v>
+        <v>57851</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4205,55 +4229,50 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvallen, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524145</v>
+        <v>524149</v>
       </c>
       <c r="R29" t="n">
-        <v>6713733</v>
+        <v>6713704</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4282,7 +4301,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4292,12 +4311,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Under klena granar.</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4324,10 +4338,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122958244</v>
+        <v>122958484</v>
       </c>
       <c r="B30" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4359,7 +4373,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4383,10 +4397,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524143</v>
+        <v>524142</v>
       </c>
       <c r="R30" t="n">
-        <v>6713721</v>
+        <v>6713723</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4418,7 +4432,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4428,12 +4442,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter. Kanske fler.</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4460,10 +4469,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122958842</v>
+        <v>122959354</v>
       </c>
       <c r="B31" t="n">
-        <v>57848</v>
+        <v>8441</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4476,46 +4485,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Banvallen, Smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524149</v>
+        <v>524122</v>
       </c>
       <c r="R31" t="n">
-        <v>6713704</v>
+        <v>6713710</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4544,7 +4549,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4554,7 +4559,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4581,10 +4586,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122958484</v>
+        <v>122959503</v>
       </c>
       <c r="B32" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4616,12 +4621,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4629,21 +4634,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524142</v>
+        <v>524145</v>
       </c>
       <c r="R32" t="n">
-        <v>6713723</v>
+        <v>6713672</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4712,10 +4712,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122958631</v>
+        <v>122958064</v>
       </c>
       <c r="B33" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4747,12 +4747,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4771,10 +4771,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524136</v>
+        <v>524144</v>
       </c>
       <c r="R33" t="n">
-        <v>6713723</v>
+        <v>6713722</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4816,12 +4816,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Bladrosetter och en överblommad.</t>
+          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4848,10 +4848,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122958064</v>
+        <v>122958550</v>
       </c>
       <c r="B34" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4907,10 +4907,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524144</v>
+        <v>524147</v>
       </c>
       <c r="R34" t="n">
-        <v>6713722</v>
+        <v>6713728</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4942,7 +4942,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4984,7 +4984,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123412973</v>
+        <v>123412367</v>
       </c>
       <c r="B35" t="n">
         <v>98368</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5032,21 +5032,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524116</v>
+        <v>524136</v>
       </c>
       <c r="R35" t="n">
-        <v>6713634</v>
+        <v>6713648</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5078,7 +5073,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5088,7 +5083,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5115,10 +5110,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123413078</v>
+        <v>123413633</v>
       </c>
       <c r="B36" t="n">
-        <v>98368</v>
+        <v>57497</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5127,57 +5122,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524102</v>
+        <v>524031</v>
       </c>
       <c r="R36" t="n">
-        <v>6713632</v>
+        <v>6713503</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5209,7 +5190,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5219,7 +5200,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5246,7 +5227,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123412439</v>
+        <v>123413119</v>
       </c>
       <c r="B37" t="n">
         <v>98368</v>
@@ -5281,12 +5262,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -5294,6 +5275,7 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5301,14 +5283,14 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524137</v>
+        <v>524101</v>
       </c>
       <c r="R37" t="n">
-        <v>6713646</v>
+        <v>6713638</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5340,7 +5322,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5350,12 +5332,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Inom ca 5 kv/dm.</t>
+          <t>Spridda sporadiskt över ytan.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5364,6 +5346,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5382,7 +5365,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123413856</v>
+        <v>123412326</v>
       </c>
       <c r="B38" t="n">
         <v>98368</v>
@@ -5417,7 +5400,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5436,10 +5419,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524041</v>
+        <v>524122</v>
       </c>
       <c r="R38" t="n">
-        <v>6713443</v>
+        <v>6713640</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5471,7 +5454,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5481,7 +5464,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5508,7 +5491,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123414352</v>
+        <v>123413726</v>
       </c>
       <c r="B39" t="n">
         <v>98368</v>
@@ -5543,7 +5526,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5562,10 +5545,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524098</v>
+        <v>524030</v>
       </c>
       <c r="R39" t="n">
-        <v>6713405</v>
+        <v>6713469</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5597,7 +5580,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5607,7 +5590,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5634,7 +5617,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123414270</v>
+        <v>123412439</v>
       </c>
       <c r="B40" t="n">
         <v>98368</v>
@@ -5669,7 +5652,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5682,16 +5665,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524085</v>
+        <v>524137</v>
       </c>
       <c r="R40" t="n">
-        <v>6713390</v>
+        <v>6713646</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5723,7 +5711,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5733,7 +5721,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Inom ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5760,7 +5753,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123412257</v>
+        <v>123414270</v>
       </c>
       <c r="B41" t="n">
         <v>98368</v>
@@ -5795,7 +5788,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5814,10 +5807,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524123</v>
+        <v>524085</v>
       </c>
       <c r="R41" t="n">
-        <v>6713637</v>
+        <v>6713390</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5849,7 +5842,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5859,7 +5852,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5886,7 +5879,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123412367</v>
+        <v>123412973</v>
       </c>
       <c r="B42" t="n">
         <v>98368</v>
@@ -5921,7 +5914,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5934,16 +5927,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524136</v>
+        <v>524116</v>
       </c>
       <c r="R42" t="n">
-        <v>6713648</v>
+        <v>6713634</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5975,7 +5973,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5985,7 +5983,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6012,7 +6010,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123413119</v>
+        <v>123413856</v>
       </c>
       <c r="B43" t="n">
         <v>98368</v>
@@ -6047,12 +6045,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -6060,22 +6058,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524101</v>
+        <v>524041</v>
       </c>
       <c r="R43" t="n">
-        <v>6713638</v>
+        <v>6713443</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6107,7 +6099,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6117,12 +6109,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:59</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt över ytan.</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6131,7 +6118,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6150,7 +6136,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123413726</v>
+        <v>123412257</v>
       </c>
       <c r="B44" t="n">
         <v>98368</v>
@@ -6185,7 +6171,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6204,10 +6190,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524030</v>
+        <v>524123</v>
       </c>
       <c r="R44" t="n">
-        <v>6713469</v>
+        <v>6713637</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6239,7 +6225,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6249,7 +6235,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6276,10 +6262,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123413633</v>
+        <v>123413078</v>
       </c>
       <c r="B45" t="n">
-        <v>57497</v>
+        <v>98368</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6288,43 +6274,57 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524031</v>
+        <v>524102</v>
       </c>
       <c r="R45" t="n">
-        <v>6713503</v>
+        <v>6713632</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6393,7 +6393,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123412326</v>
+        <v>123414352</v>
       </c>
       <c r="B46" t="n">
         <v>98368</v>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6447,10 +6447,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524122</v>
+        <v>524098</v>
       </c>
       <c r="R46" t="n">
-        <v>6713640</v>
+        <v>6713405</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -2384,10 +2384,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122821745</v>
+        <v>122821104</v>
       </c>
       <c r="B15" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2419,12 +2419,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524080</v>
+        <v>524057</v>
       </c>
       <c r="R15" t="n">
-        <v>6714074</v>
+        <v>6714094</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2488,7 +2488,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2515,10 +2520,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122817980</v>
+        <v>122821198</v>
       </c>
       <c r="B16" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2563,6 +2568,7 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2570,14 +2576,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524038</v>
+        <v>524049</v>
       </c>
       <c r="R16" t="n">
-        <v>6713288</v>
+        <v>6714097</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2589,7 +2595,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Borlänge</t>
+          <t>Falun</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2609,7 +2615,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2619,12 +2625,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>10-15 bladrosetter under klen senvuxen gran.</t>
+          <t>Under klen gran. En överblommad.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2633,6 +2639,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2651,10 +2658,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122821729</v>
+        <v>122821745</v>
       </c>
       <c r="B17" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2686,7 +2693,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2710,10 +2717,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524077</v>
+        <v>524080</v>
       </c>
       <c r="R17" t="n">
-        <v>6714076</v>
+        <v>6714074</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2745,7 +2752,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2755,12 +2762,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2787,10 +2789,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122821104</v>
+        <v>122821824</v>
       </c>
       <c r="B18" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2822,12 +2824,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2846,10 +2848,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524057</v>
+        <v>524055</v>
       </c>
       <c r="R18" t="n">
-        <v>6714094</v>
+        <v>6714048</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2881,7 +2883,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2891,12 +2893,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2923,10 +2920,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122821824</v>
+        <v>122821729</v>
       </c>
       <c r="B19" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2958,12 +2955,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2982,10 +2979,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524055</v>
+        <v>524077</v>
       </c>
       <c r="R19" t="n">
-        <v>6714048</v>
+        <v>6714076</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3017,7 +3014,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3027,7 +3024,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3054,10 +3056,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122821198</v>
+        <v>122817980</v>
       </c>
       <c r="B20" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3102,7 +3104,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3110,14 +3111,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524049</v>
+        <v>524038</v>
       </c>
       <c r="R20" t="n">
-        <v>6714097</v>
+        <v>6713288</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3129,7 +3130,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Falun</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -3149,7 +3150,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3159,12 +3160,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Under klen gran. En överblommad.</t>
+          <t>10-15 bladrosetter under klen senvuxen gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3173,7 +3174,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3192,10 +3192,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122917069</v>
+        <v>122916997</v>
       </c>
       <c r="B21" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3227,12 +3227,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524154</v>
+        <v>524142</v>
       </c>
       <c r="R21" t="n">
         <v>6713729</v>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>En överblommad.</t>
+          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3328,10 +3328,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122915863</v>
+        <v>122917069</v>
       </c>
       <c r="B22" t="n">
-        <v>8441</v>
+        <v>98370</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3340,43 +3340,57 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524025</v>
+        <v>524154</v>
       </c>
       <c r="R22" t="n">
-        <v>6713544</v>
+        <v>6713729</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3408,7 +3422,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3418,7 +3432,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3445,10 +3464,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122916997</v>
+        <v>122915863</v>
       </c>
       <c r="B23" t="n">
-        <v>98368</v>
+        <v>8441</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3457,57 +3476,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524142</v>
+        <v>524025</v>
       </c>
       <c r="R23" t="n">
-        <v>6713729</v>
+        <v>6713544</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3539,7 +3544,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3549,12 +3554,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:33</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3581,10 +3581,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122958244</v>
+        <v>122958484</v>
       </c>
       <c r="B24" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524143</v>
+        <v>524142</v>
       </c>
       <c r="R24" t="n">
-        <v>6713721</v>
+        <v>6713723</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3685,12 +3685,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter. Kanske fler.</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3717,10 +3712,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122958631</v>
+        <v>122958550</v>
       </c>
       <c r="B25" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3752,7 +3747,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3776,10 +3771,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524136</v>
+        <v>524147</v>
       </c>
       <c r="R25" t="n">
-        <v>6713723</v>
+        <v>6713728</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3811,7 +3806,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3821,12 +3816,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Bladrosetter och en överblommad.</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3853,10 +3848,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122961337</v>
+        <v>122958244</v>
       </c>
       <c r="B26" t="n">
-        <v>90955</v>
+        <v>98370</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3865,41 +3860,57 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524040</v>
+        <v>524143</v>
       </c>
       <c r="R26" t="n">
-        <v>6713957</v>
+        <v>6713721</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3931,7 +3942,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3941,7 +3952,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter. Kanske fler.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3950,7 +3966,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3969,10 +3984,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122957710</v>
+        <v>122959354</v>
       </c>
       <c r="B27" t="n">
-        <v>98368</v>
+        <v>8441</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3981,40 +3996,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -4023,10 +4029,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524145</v>
+        <v>524122</v>
       </c>
       <c r="R27" t="n">
-        <v>6713733</v>
+        <v>6713710</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4058,7 +4064,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4068,12 +4074,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:29</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Under klena granar.</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4217,10 +4218,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122958842</v>
+        <v>122961337</v>
       </c>
       <c r="B29" t="n">
-        <v>57851</v>
+        <v>90957</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4229,50 +4230,44 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Banvallen, Smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524149</v>
+        <v>524040</v>
       </c>
       <c r="R29" t="n">
-        <v>6713704</v>
+        <v>6713957</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4301,7 +4296,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4311,7 +4306,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4320,6 +4315,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4338,10 +4334,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122958484</v>
+        <v>122959503</v>
       </c>
       <c r="B30" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4373,12 +4369,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4386,21 +4382,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524142</v>
+        <v>524145</v>
       </c>
       <c r="R30" t="n">
-        <v>6713723</v>
+        <v>6713672</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4432,7 +4423,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4442,7 +4433,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4469,10 +4460,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122959354</v>
+        <v>122958842</v>
       </c>
       <c r="B31" t="n">
-        <v>8441</v>
+        <v>57851</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4485,42 +4476,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvallen, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524122</v>
+        <v>524149</v>
       </c>
       <c r="R31" t="n">
-        <v>6713710</v>
+        <v>6713704</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4549,7 +4544,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4559,7 +4554,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4586,10 +4581,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122959503</v>
+        <v>122958064</v>
       </c>
       <c r="B32" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4626,7 +4621,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4634,16 +4629,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524145</v>
+        <v>524144</v>
       </c>
       <c r="R32" t="n">
-        <v>6713672</v>
+        <v>6713722</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4685,7 +4685,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4712,10 +4717,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122958064</v>
+        <v>122957710</v>
       </c>
       <c r="B33" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4747,12 +4752,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4760,21 +4765,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524144</v>
+        <v>524145</v>
       </c>
       <c r="R33" t="n">
-        <v>6713722</v>
+        <v>6713733</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4816,12 +4816,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
+          <t>Under klena granar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4848,10 +4848,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122958550</v>
+        <v>122958631</v>
       </c>
       <c r="B34" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4907,10 +4907,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524147</v>
+        <v>524136</v>
       </c>
       <c r="R34" t="n">
-        <v>6713728</v>
+        <v>6713723</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4942,7 +4942,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>Bladrosetter och en överblommad.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4987,7 +4987,7 @@
         <v>123412367</v>
       </c>
       <c r="B35" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5110,10 +5110,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123413633</v>
+        <v>123413726</v>
       </c>
       <c r="B36" t="n">
-        <v>57497</v>
+        <v>98370</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5122,43 +5122,52 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524031</v>
+        <v>524030</v>
       </c>
       <c r="R36" t="n">
-        <v>6713503</v>
+        <v>6713469</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5190,7 +5199,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5200,7 +5209,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5227,10 +5236,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123413119</v>
+        <v>123414352</v>
       </c>
       <c r="B37" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5262,12 +5271,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -5275,22 +5284,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524101</v>
+        <v>524098</v>
       </c>
       <c r="R37" t="n">
-        <v>6713638</v>
+        <v>6713405</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5322,7 +5325,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5332,12 +5335,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:59</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt över ytan.</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5346,7 +5344,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5365,10 +5362,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123412326</v>
+        <v>123413119</v>
       </c>
       <c r="B38" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5405,7 +5402,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5413,16 +5410,22 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524122</v>
+        <v>524101</v>
       </c>
       <c r="R38" t="n">
-        <v>6713640</v>
+        <v>6713638</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5454,7 +5457,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5464,7 +5467,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Spridda sporadiskt över ytan.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5473,6 +5481,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5491,10 +5500,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123413726</v>
+        <v>123412973</v>
       </c>
       <c r="B39" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5526,7 +5535,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5539,16 +5548,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524030</v>
+        <v>524116</v>
       </c>
       <c r="R39" t="n">
-        <v>6713469</v>
+        <v>6713634</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5580,7 +5594,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5590,7 +5604,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5617,10 +5631,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123412439</v>
+        <v>123414270</v>
       </c>
       <c r="B40" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5652,7 +5666,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5665,21 +5679,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524137</v>
+        <v>524085</v>
       </c>
       <c r="R40" t="n">
-        <v>6713646</v>
+        <v>6713390</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5711,7 +5720,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5721,12 +5730,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:39</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Inom ca 5 kv/dm.</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5753,10 +5757,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123414270</v>
+        <v>123412326</v>
       </c>
       <c r="B41" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5788,7 +5792,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5807,10 +5811,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524085</v>
+        <v>524122</v>
       </c>
       <c r="R41" t="n">
-        <v>6713390</v>
+        <v>6713640</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5842,7 +5846,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5852,7 +5856,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5879,10 +5883,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123412973</v>
+        <v>123413856</v>
       </c>
       <c r="B42" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5914,7 +5918,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5927,21 +5931,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524116</v>
+        <v>524041</v>
       </c>
       <c r="R42" t="n">
-        <v>6713634</v>
+        <v>6713443</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5973,7 +5972,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5983,7 +5982,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6010,10 +6009,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123413856</v>
+        <v>123413633</v>
       </c>
       <c r="B43" t="n">
-        <v>98368</v>
+        <v>57497</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6022,52 +6021,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524041</v>
+        <v>524031</v>
       </c>
       <c r="R43" t="n">
-        <v>6713443</v>
+        <v>6713503</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6099,7 +6089,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6109,7 +6099,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6136,10 +6126,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123412257</v>
+        <v>123413078</v>
       </c>
       <c r="B44" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6171,7 +6161,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6184,16 +6174,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524123</v>
+        <v>524102</v>
       </c>
       <c r="R44" t="n">
-        <v>6713637</v>
+        <v>6713632</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6225,7 +6220,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6235,7 +6230,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6262,10 +6257,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123413078</v>
+        <v>123412439</v>
       </c>
       <c r="B45" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6297,7 +6292,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6317,14 +6312,14 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524102</v>
+        <v>524137</v>
       </c>
       <c r="R45" t="n">
-        <v>6713632</v>
+        <v>6713646</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6356,7 +6351,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6366,7 +6361,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Inom ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6393,10 +6393,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123414352</v>
+        <v>123412257</v>
       </c>
       <c r="B46" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6447,10 +6447,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524098</v>
+        <v>524123</v>
       </c>
       <c r="R46" t="n">
-        <v>6713405</v>
+        <v>6713637</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2387,7 +2387,7 @@
         <v>122821104</v>
       </c>
       <c r="B15" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>122821198</v>
       </c>
       <c r="B16" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2658,10 +2658,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122821745</v>
+        <v>122817980</v>
       </c>
       <c r="B17" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2713,14 +2713,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524080</v>
+        <v>524038</v>
       </c>
       <c r="R17" t="n">
-        <v>6714074</v>
+        <v>6713288</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2762,7 +2762,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>10-15 bladrosetter under klen senvuxen gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2789,10 +2794,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122821824</v>
+        <v>122821729</v>
       </c>
       <c r="B18" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2824,12 +2829,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2848,10 +2853,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524055</v>
+        <v>524077</v>
       </c>
       <c r="R18" t="n">
-        <v>6714048</v>
+        <v>6714076</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2883,7 +2888,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2893,7 +2898,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2920,10 +2930,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122821729</v>
+        <v>122821824</v>
       </c>
       <c r="B19" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2955,12 +2965,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2979,10 +2989,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524077</v>
+        <v>524055</v>
       </c>
       <c r="R19" t="n">
-        <v>6714076</v>
+        <v>6714048</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3014,7 +3024,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3024,12 +3034,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3056,10 +3061,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122817980</v>
+        <v>122821745</v>
       </c>
       <c r="B20" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3096,7 +3101,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3111,14 +3116,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524038</v>
+        <v>524080</v>
       </c>
       <c r="R20" t="n">
-        <v>6713288</v>
+        <v>6714074</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3150,7 +3155,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3160,12 +3165,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>10-15 bladrosetter under klen senvuxen gran.</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3192,10 +3192,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122916997</v>
+        <v>122915863</v>
       </c>
       <c r="B21" t="n">
-        <v>98370</v>
+        <v>8441</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3204,57 +3204,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524142</v>
+        <v>524025</v>
       </c>
       <c r="R21" t="n">
-        <v>6713729</v>
+        <v>6713544</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3286,7 +3272,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3296,12 +3282,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:33</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3331,7 +3312,7 @@
         <v>122917069</v>
       </c>
       <c r="B22" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3464,10 +3445,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122915863</v>
+        <v>122916997</v>
       </c>
       <c r="B23" t="n">
-        <v>8441</v>
+        <v>98376</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3476,43 +3457,57 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524025</v>
+        <v>524142</v>
       </c>
       <c r="R23" t="n">
-        <v>6713544</v>
+        <v>6713729</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3544,7 +3539,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3554,7 +3549,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3581,10 +3581,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122958484</v>
+        <v>122961337</v>
       </c>
       <c r="B24" t="n">
-        <v>98370</v>
+        <v>90963</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3593,57 +3593,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524142</v>
+        <v>524040</v>
       </c>
       <c r="R24" t="n">
-        <v>6713723</v>
+        <v>6713957</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3675,7 +3659,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3685,7 +3669,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3694,6 +3678,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3712,10 +3697,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122958550</v>
+        <v>122958842</v>
       </c>
       <c r="B25" t="n">
-        <v>98370</v>
+        <v>57851</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3724,25 +3709,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3750,34 +3735,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvallen, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524147</v>
+        <v>524149</v>
       </c>
       <c r="R25" t="n">
-        <v>6713728</v>
+        <v>6713704</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3806,7 +3781,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3816,12 +3791,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3848,10 +3818,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122958244</v>
+        <v>122959354</v>
       </c>
       <c r="B26" t="n">
-        <v>98370</v>
+        <v>8441</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3860,45 +3830,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3907,10 +3863,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524143</v>
+        <v>524122</v>
       </c>
       <c r="R26" t="n">
-        <v>6713721</v>
+        <v>6713710</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3942,7 +3898,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3952,12 +3908,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter. Kanske fler.</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3984,10 +3935,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122959354</v>
+        <v>122958244</v>
       </c>
       <c r="B27" t="n">
-        <v>8441</v>
+        <v>98376</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3996,31 +3947,45 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -4029,10 +3994,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524122</v>
+        <v>524143</v>
       </c>
       <c r="R27" t="n">
-        <v>6713710</v>
+        <v>6713721</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4064,7 +4029,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4074,7 +4039,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter. Kanske fler.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4101,10 +4071,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122959453</v>
+        <v>122958550</v>
       </c>
       <c r="B28" t="n">
-        <v>8441</v>
+        <v>98376</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4113,31 +4083,45 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -4146,10 +4130,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524128</v>
+        <v>524147</v>
       </c>
       <c r="R28" t="n">
-        <v>6713669</v>
+        <v>6713728</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4181,7 +4165,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4191,7 +4175,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4218,10 +4207,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122961337</v>
+        <v>122957710</v>
       </c>
       <c r="B29" t="n">
-        <v>90957</v>
+        <v>98376</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4230,41 +4219,52 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524040</v>
+        <v>524145</v>
       </c>
       <c r="R29" t="n">
-        <v>6713957</v>
+        <v>6713733</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4306,7 +4306,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Under klena granar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4315,7 +4320,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4334,10 +4338,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122959503</v>
+        <v>122959453</v>
       </c>
       <c r="B30" t="n">
-        <v>98370</v>
+        <v>8441</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4346,40 +4350,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4388,10 +4383,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524145</v>
+        <v>524128</v>
       </c>
       <c r="R30" t="n">
-        <v>6713672</v>
+        <v>6713669</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4423,7 +4418,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4433,7 +4428,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4460,10 +4455,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122958842</v>
+        <v>122959503</v>
       </c>
       <c r="B31" t="n">
-        <v>57851</v>
+        <v>98376</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4472,25 +4467,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4498,24 +4493,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Banvallen, Smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524149</v>
+        <v>524145</v>
       </c>
       <c r="R31" t="n">
-        <v>6713704</v>
+        <v>6713672</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4581,10 +4581,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122958064</v>
+        <v>122958484</v>
       </c>
       <c r="B32" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4640,10 +4640,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524144</v>
+        <v>524142</v>
       </c>
       <c r="R32" t="n">
-        <v>6713722</v>
+        <v>6713723</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4685,12 +4685,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4717,10 +4712,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122957710</v>
+        <v>122958631</v>
       </c>
       <c r="B33" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4752,7 +4747,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4765,16 +4760,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524145</v>
+        <v>524136</v>
       </c>
       <c r="R33" t="n">
-        <v>6713733</v>
+        <v>6713723</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4816,12 +4816,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Under klena granar.</t>
+          <t>Bladrosetter och en överblommad.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4848,10 +4848,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122958631</v>
+        <v>122958064</v>
       </c>
       <c r="B34" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4883,12 +4883,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4907,10 +4907,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524136</v>
+        <v>524144</v>
       </c>
       <c r="R34" t="n">
-        <v>6713723</v>
+        <v>6713722</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4942,7 +4942,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Bladrosetter och en överblommad.</t>
+          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4984,10 +4984,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123412367</v>
+        <v>123413726</v>
       </c>
       <c r="B35" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5034,14 +5034,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524136</v>
+        <v>524030</v>
       </c>
       <c r="R35" t="n">
-        <v>6713648</v>
+        <v>6713469</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5110,10 +5110,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123413726</v>
+        <v>123412973</v>
       </c>
       <c r="B36" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5158,16 +5158,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524030</v>
+        <v>524116</v>
       </c>
       <c r="R36" t="n">
-        <v>6713469</v>
+        <v>6713634</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5199,7 +5204,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5209,7 +5214,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5236,10 +5241,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123414352</v>
+        <v>123413078</v>
       </c>
       <c r="B37" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5271,7 +5276,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5284,16 +5289,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524098</v>
+        <v>524102</v>
       </c>
       <c r="R37" t="n">
-        <v>6713405</v>
+        <v>6713632</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5325,7 +5335,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5335,7 +5345,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5362,10 +5372,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123413119</v>
+        <v>123412326</v>
       </c>
       <c r="B38" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5402,7 +5412,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5410,22 +5420,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524101</v>
+        <v>524122</v>
       </c>
       <c r="R38" t="n">
-        <v>6713638</v>
+        <v>6713640</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5457,7 +5461,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5467,12 +5471,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:59</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt över ytan.</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5481,7 +5480,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5500,10 +5498,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123412973</v>
+        <v>123414270</v>
       </c>
       <c r="B39" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5535,7 +5533,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5548,21 +5546,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524116</v>
+        <v>524085</v>
       </c>
       <c r="R39" t="n">
-        <v>6713634</v>
+        <v>6713390</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5594,7 +5587,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5604,7 +5597,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5631,10 +5624,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123414270</v>
+        <v>123413633</v>
       </c>
       <c r="B40" t="n">
-        <v>98370</v>
+        <v>57497</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5643,52 +5636,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524085</v>
+        <v>524031</v>
       </c>
       <c r="R40" t="n">
-        <v>6713390</v>
+        <v>6713503</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5720,7 +5704,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5730,7 +5714,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5757,10 +5741,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123412326</v>
+        <v>123412257</v>
       </c>
       <c r="B41" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5792,7 +5776,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5811,10 +5795,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524122</v>
+        <v>524123</v>
       </c>
       <c r="R41" t="n">
-        <v>6713640</v>
+        <v>6713637</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5846,7 +5830,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5856,7 +5840,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5883,10 +5867,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123413856</v>
+        <v>123412367</v>
       </c>
       <c r="B42" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5918,7 +5902,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5933,14 +5917,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524041</v>
+        <v>524136</v>
       </c>
       <c r="R42" t="n">
-        <v>6713443</v>
+        <v>6713648</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5972,7 +5956,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5982,7 +5966,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6009,10 +5993,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123413633</v>
+        <v>123413119</v>
       </c>
       <c r="B43" t="n">
-        <v>57497</v>
+        <v>98376</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6021,43 +6005,58 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524031</v>
+        <v>524101</v>
       </c>
       <c r="R43" t="n">
-        <v>6713503</v>
+        <v>6713638</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6089,7 +6088,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6099,7 +6098,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Spridda sporadiskt över ytan.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6108,6 +6112,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6126,10 +6131,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123413078</v>
+        <v>123413856</v>
       </c>
       <c r="B44" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6161,7 +6166,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6174,21 +6179,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524102</v>
+        <v>524041</v>
       </c>
       <c r="R44" t="n">
-        <v>6713632</v>
+        <v>6713443</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6257,10 +6257,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123412439</v>
+        <v>123414352</v>
       </c>
       <c r="B45" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6305,21 +6305,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524137</v>
+        <v>524098</v>
       </c>
       <c r="R45" t="n">
-        <v>6713646</v>
+        <v>6713405</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6351,7 +6346,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6361,12 +6356,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:39</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Inom ca 5 kv/dm.</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6393,10 +6383,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123412257</v>
+        <v>123412439</v>
       </c>
       <c r="B46" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6428,7 +6418,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6441,16 +6431,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524123</v>
+        <v>524137</v>
       </c>
       <c r="R46" t="n">
-        <v>6713637</v>
+        <v>6713646</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6482,7 +6477,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6492,7 +6487,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Inom ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6516,6 +6516,514 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>123528562</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57497</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>524033</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6713503</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>123526470</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98379</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>524101</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6713880</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>123528345</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98379</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>524025</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6713476</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>123527655</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98379</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>524041</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6713460</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -3698,10 +3698,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122958842</v>
+        <v>122958484</v>
       </c>
       <c r="B25" t="n">
-        <v>57851</v>
+        <v>98379</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3710,50 +3710,60 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Banvallen, Smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524149</v>
+        <v>524142</v>
       </c>
       <c r="R25" t="n">
-        <v>6713704</v>
+        <v>6713723</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3782,7 +3792,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3792,7 +3802,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3819,10 +3829,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122958484</v>
+        <v>122958842</v>
       </c>
       <c r="B26" t="n">
-        <v>98379</v>
+        <v>57851</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3831,60 +3841,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvallen, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524142</v>
+        <v>524149</v>
       </c>
       <c r="R26" t="n">
-        <v>6713723</v>
+        <v>6713704</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4086,10 +4086,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122959354</v>
+        <v>122957710</v>
       </c>
       <c r="B28" t="n">
-        <v>8441</v>
+        <v>98379</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4098,31 +4098,40 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -4131,10 +4140,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524122</v>
+        <v>524145</v>
       </c>
       <c r="R28" t="n">
-        <v>6713710</v>
+        <v>6713733</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4166,7 +4175,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4176,7 +4185,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Under klena granar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4203,7 +4217,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122957710</v>
+        <v>122958550</v>
       </c>
       <c r="B29" t="n">
         <v>98379</v>
@@ -4238,7 +4252,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4251,16 +4265,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524145</v>
+        <v>524147</v>
       </c>
       <c r="R29" t="n">
-        <v>6713733</v>
+        <v>6713728</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4292,7 +4311,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4302,12 +4321,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Under klena granar.</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4334,10 +4353,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122958550</v>
+        <v>122959354</v>
       </c>
       <c r="B30" t="n">
-        <v>98379</v>
+        <v>8441</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4346,45 +4365,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4393,10 +4398,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524147</v>
+        <v>524122</v>
       </c>
       <c r="R30" t="n">
-        <v>6713728</v>
+        <v>6713710</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4428,7 +4433,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4438,12 +4443,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -8001,10 +8001,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123569808</v>
+        <v>123572491</v>
       </c>
       <c r="B59" t="n">
-        <v>97333</v>
+        <v>90966</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8013,43 +8013,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>524077</v>
+        <v>523993</v>
       </c>
       <c r="R59" t="n">
-        <v>6713436</v>
+        <v>6713281</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8081,7 +8076,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8091,7 +8086,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8118,10 +8113,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123572491</v>
+        <v>123569808</v>
       </c>
       <c r="B60" t="n">
-        <v>90966</v>
+        <v>97333</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8130,38 +8125,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523993</v>
+        <v>524077</v>
       </c>
       <c r="R60" t="n">
-        <v>6713281</v>
+        <v>6713436</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8193,7 +8193,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3195,7 +3195,7 @@
         <v>122916997</v>
       </c>
       <c r="B21" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>122915863</v>
       </c>
       <c r="B22" t="n">
-        <v>8441</v>
+        <v>8445</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>122917069</v>
       </c>
       <c r="B23" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3581,10 +3581,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122959453</v>
+        <v>122957710</v>
       </c>
       <c r="B24" t="n">
-        <v>8441</v>
+        <v>98396</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3593,31 +3593,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3626,10 +3635,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524128</v>
+        <v>524145</v>
       </c>
       <c r="R24" t="n">
-        <v>6713669</v>
+        <v>6713733</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3661,7 +3670,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3671,7 +3680,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Under klena granar.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3698,10 +3712,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122958484</v>
+        <v>122958842</v>
       </c>
       <c r="B25" t="n">
-        <v>98379</v>
+        <v>57857</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3710,60 +3724,50 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvallen, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524142</v>
+        <v>524149</v>
       </c>
       <c r="R25" t="n">
-        <v>6713723</v>
+        <v>6713704</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3792,7 +3796,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3802,7 +3806,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3829,10 +3833,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122958842</v>
+        <v>122961337</v>
       </c>
       <c r="B26" t="n">
-        <v>57851</v>
+        <v>90983</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3841,50 +3845,44 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Banvallen, Smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524149</v>
+        <v>524040</v>
       </c>
       <c r="R26" t="n">
-        <v>6713704</v>
+        <v>6713957</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3913,7 +3911,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3923,7 +3921,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3932,6 +3930,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3950,10 +3949,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122958064</v>
+        <v>122959453</v>
       </c>
       <c r="B27" t="n">
-        <v>98379</v>
+        <v>8445</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3962,45 +3961,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -4009,10 +3994,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524144</v>
+        <v>524128</v>
       </c>
       <c r="R27" t="n">
-        <v>6713722</v>
+        <v>6713669</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4044,7 +4029,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4054,12 +4039,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4086,10 +4066,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122957710</v>
+        <v>122958484</v>
       </c>
       <c r="B28" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4121,7 +4101,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4134,16 +4114,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524145</v>
+        <v>524142</v>
       </c>
       <c r="R28" t="n">
-        <v>6713733</v>
+        <v>6713723</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4175,7 +4160,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4185,12 +4170,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:29</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Under klena granar.</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4217,10 +4197,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122958550</v>
+        <v>122959503</v>
       </c>
       <c r="B29" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4257,7 +4237,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4265,21 +4245,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524147</v>
+        <v>524145</v>
       </c>
       <c r="R29" t="n">
-        <v>6713728</v>
+        <v>6713672</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4311,7 +4286,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4321,12 +4296,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4353,10 +4323,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122959354</v>
+        <v>122958631</v>
       </c>
       <c r="B30" t="n">
-        <v>8441</v>
+        <v>98396</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4365,31 +4335,45 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4398,10 +4382,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524122</v>
+        <v>524136</v>
       </c>
       <c r="R30" t="n">
-        <v>6713710</v>
+        <v>6713723</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4433,7 +4417,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4443,7 +4427,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Bladrosetter och en överblommad.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4470,10 +4459,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122958631</v>
+        <v>122958064</v>
       </c>
       <c r="B31" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4505,12 +4494,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4529,10 +4518,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524136</v>
+        <v>524144</v>
       </c>
       <c r="R31" t="n">
-        <v>6713723</v>
+        <v>6713722</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4564,7 +4553,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4574,12 +4563,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Bladrosetter och en överblommad.</t>
+          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4606,10 +4595,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122961337</v>
+        <v>122958550</v>
       </c>
       <c r="B32" t="n">
-        <v>90966</v>
+        <v>98396</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4618,41 +4607,57 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524040</v>
+        <v>524147</v>
       </c>
       <c r="R32" t="n">
-        <v>6713957</v>
+        <v>6713728</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4684,7 +4689,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4694,7 +4699,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4703,7 +4713,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4722,10 +4731,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122959503</v>
+        <v>122958244</v>
       </c>
       <c r="B33" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4757,12 +4766,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4770,16 +4779,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524145</v>
+        <v>524143</v>
       </c>
       <c r="R33" t="n">
-        <v>6713672</v>
+        <v>6713721</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4811,7 +4825,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4821,7 +4835,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter. Kanske fler.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4848,10 +4867,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122958244</v>
+        <v>122959354</v>
       </c>
       <c r="B34" t="n">
-        <v>98379</v>
+        <v>8445</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4860,45 +4879,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4907,10 +4912,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524143</v>
+        <v>524122</v>
       </c>
       <c r="R34" t="n">
-        <v>6713721</v>
+        <v>6713710</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4942,7 +4947,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4952,12 +4957,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter. Kanske fler.</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4984,10 +4984,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123413726</v>
+        <v>123413856</v>
       </c>
       <c r="B35" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5038,10 +5038,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524030</v>
+        <v>524041</v>
       </c>
       <c r="R35" t="n">
-        <v>6713469</v>
+        <v>6713443</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5110,10 +5110,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123412439</v>
+        <v>123414270</v>
       </c>
       <c r="B36" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5158,21 +5158,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524137</v>
+        <v>524085</v>
       </c>
       <c r="R36" t="n">
-        <v>6713646</v>
+        <v>6713390</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5204,7 +5199,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5214,12 +5209,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:39</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Inom ca 5 kv/dm.</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5246,10 +5236,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123414270</v>
+        <v>123413633</v>
       </c>
       <c r="B37" t="n">
-        <v>98379</v>
+        <v>57503</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5258,52 +5248,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524085</v>
+        <v>524031</v>
       </c>
       <c r="R37" t="n">
-        <v>6713390</v>
+        <v>6713503</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5335,7 +5316,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5345,7 +5326,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5372,10 +5353,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123413078</v>
+        <v>123412257</v>
       </c>
       <c r="B38" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5407,7 +5388,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5420,21 +5401,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524102</v>
+        <v>524123</v>
       </c>
       <c r="R38" t="n">
-        <v>6713632</v>
+        <v>6713637</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5466,7 +5442,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5476,7 +5452,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5503,10 +5479,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123412257</v>
+        <v>123412973</v>
       </c>
       <c r="B39" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5538,7 +5514,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5551,16 +5527,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524123</v>
+        <v>524116</v>
       </c>
       <c r="R39" t="n">
-        <v>6713637</v>
+        <v>6713634</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5592,7 +5573,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5602,7 +5583,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5629,10 +5610,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123413119</v>
+        <v>123413726</v>
       </c>
       <c r="B40" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5669,7 +5650,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5677,22 +5658,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524101</v>
+        <v>524030</v>
       </c>
       <c r="R40" t="n">
-        <v>6713638</v>
+        <v>6713469</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5724,7 +5699,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5734,12 +5709,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:59</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt över ytan.</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5748,7 +5718,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5767,10 +5736,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123412367</v>
+        <v>123413078</v>
       </c>
       <c r="B41" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5802,7 +5771,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5815,16 +5784,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524136</v>
+        <v>524102</v>
       </c>
       <c r="R41" t="n">
-        <v>6713648</v>
+        <v>6713632</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5856,7 +5830,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5866,7 +5840,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5893,10 +5867,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123412326</v>
+        <v>123412439</v>
       </c>
       <c r="B42" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5928,7 +5902,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5941,16 +5915,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524122</v>
+        <v>524137</v>
       </c>
       <c r="R42" t="n">
-        <v>6713640</v>
+        <v>6713646</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5982,7 +5961,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5992,7 +5971,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Inom ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6019,10 +6003,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123412973</v>
+        <v>123412326</v>
       </c>
       <c r="B43" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6054,7 +6038,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6067,21 +6051,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524116</v>
+        <v>524122</v>
       </c>
       <c r="R43" t="n">
-        <v>6713634</v>
+        <v>6713640</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6113,7 +6092,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6123,7 +6102,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6150,10 +6129,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123413633</v>
+        <v>123414352</v>
       </c>
       <c r="B44" t="n">
-        <v>57497</v>
+        <v>98396</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6162,43 +6141,52 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524031</v>
+        <v>524098</v>
       </c>
       <c r="R44" t="n">
-        <v>6713503</v>
+        <v>6713405</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6230,7 +6218,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6240,7 +6228,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6267,10 +6255,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123414352</v>
+        <v>123412367</v>
       </c>
       <c r="B45" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6302,7 +6290,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6317,14 +6305,14 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524098</v>
+        <v>524136</v>
       </c>
       <c r="R45" t="n">
-        <v>6713405</v>
+        <v>6713648</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6356,7 +6344,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6366,7 +6354,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6393,10 +6381,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123413856</v>
+        <v>123413119</v>
       </c>
       <c r="B46" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6428,12 +6416,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -6441,16 +6429,22 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524041</v>
+        <v>524101</v>
       </c>
       <c r="R46" t="n">
-        <v>6713443</v>
+        <v>6713638</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6482,7 +6476,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6492,7 +6486,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Spridda sporadiskt över ytan.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6501,6 +6500,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6519,10 +6519,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123528345</v>
+        <v>123528562</v>
       </c>
       <c r="B47" t="n">
-        <v>98379</v>
+        <v>57503</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6531,54 +6531,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524025</v>
+        <v>524033</v>
       </c>
       <c r="R47" t="n">
-        <v>6713476</v>
+        <v>6713503</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6623,18 +6612,12 @@
           <t>18:41</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6653,10 +6636,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123527741</v>
+        <v>123526470</v>
       </c>
       <c r="B48" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6688,12 +6671,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -6701,18 +6684,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524029</v>
+        <v>524101</v>
       </c>
       <c r="R48" t="n">
-        <v>6713459</v>
+        <v>6713880</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6744,7 +6730,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6754,12 +6740,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Sporadiskt spridda över ytan.</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6768,7 +6749,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6787,10 +6767,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123528562</v>
+        <v>123527655</v>
       </c>
       <c r="B49" t="n">
-        <v>57497</v>
+        <v>98396</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6799,43 +6779,52 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524033</v>
+        <v>524041</v>
       </c>
       <c r="R49" t="n">
-        <v>6713503</v>
+        <v>6713460</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6867,7 +6856,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6877,7 +6866,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6904,10 +6893,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123526470</v>
+        <v>123528345</v>
       </c>
       <c r="B50" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6939,12 +6928,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -6952,21 +6941,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524101</v>
+        <v>524025</v>
       </c>
       <c r="R50" t="n">
-        <v>6713880</v>
+        <v>6713476</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6998,7 +6984,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7008,7 +6994,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7017,6 +7008,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -7035,10 +7027,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123527655</v>
+        <v>123527741</v>
       </c>
       <c r="B51" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7070,12 +7062,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -7083,16 +7075,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>524041</v>
+        <v>524029</v>
       </c>
       <c r="R51" t="n">
-        <v>6713460</v>
+        <v>6713459</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7124,7 +7118,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7134,7 +7128,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Sporadiskt spridda över ytan.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7143,6 +7142,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7161,10 +7161,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123562313</v>
+        <v>123566767</v>
       </c>
       <c r="B52" t="n">
-        <v>90966</v>
+        <v>98396</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7173,38 +7173,52 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523993</v>
+        <v>524084</v>
       </c>
       <c r="R52" t="n">
-        <v>6713299</v>
+        <v>6713408</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7236,7 +7250,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7246,7 +7260,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7273,10 +7287,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123568589</v>
+        <v>123563043</v>
       </c>
       <c r="B53" t="n">
-        <v>97333</v>
+        <v>58165</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7289,37 +7303,47 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>103044</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>524065</v>
+        <v>524035</v>
       </c>
       <c r="R53" t="n">
-        <v>6713431</v>
+        <v>6713295</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7348,7 +7372,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7358,7 +7382,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7385,10 +7409,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123566656</v>
+        <v>123572491</v>
       </c>
       <c r="B54" t="n">
-        <v>98379</v>
+        <v>90983</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7397,52 +7421,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>524082</v>
+        <v>523993</v>
       </c>
       <c r="R54" t="n">
-        <v>6713393</v>
+        <v>6713281</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7474,7 +7484,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7484,7 +7494,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7511,10 +7521,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123564666</v>
+        <v>123568031</v>
       </c>
       <c r="B55" t="n">
-        <v>98379</v>
+        <v>58165</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7523,52 +7533,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>524034</v>
+        <v>524094</v>
       </c>
       <c r="R55" t="n">
-        <v>6713303</v>
+        <v>6713439</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7600,7 +7601,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7610,7 +7611,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7637,10 +7638,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123565789</v>
+        <v>123569630</v>
       </c>
       <c r="B56" t="n">
-        <v>90966</v>
+        <v>100662</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7649,38 +7650,54 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>524075</v>
+        <v>524047</v>
       </c>
       <c r="R56" t="n">
-        <v>6713354</v>
+        <v>6713427</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7712,7 +7729,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7722,7 +7739,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Spridda över ca 15x10m.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7731,6 +7753,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7749,10 +7772,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123567299</v>
+        <v>123564906</v>
       </c>
       <c r="B57" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7803,10 +7826,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>524117</v>
+        <v>524050</v>
       </c>
       <c r="R57" t="n">
-        <v>6713411</v>
+        <v>6713310</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7838,7 +7861,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7848,7 +7871,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7875,10 +7898,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123570699</v>
+        <v>123569808</v>
       </c>
       <c r="B58" t="n">
-        <v>98379</v>
+        <v>97350</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7887,40 +7910,31 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7929,10 +7943,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>524145</v>
+        <v>524077</v>
       </c>
       <c r="R58" t="n">
-        <v>6713399</v>
+        <v>6713436</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7964,7 +7978,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7974,7 +7988,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8001,10 +8015,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123572491</v>
+        <v>123564666</v>
       </c>
       <c r="B59" t="n">
-        <v>90966</v>
+        <v>98396</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8013,38 +8027,52 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523993</v>
+        <v>524034</v>
       </c>
       <c r="R59" t="n">
-        <v>6713281</v>
+        <v>6713303</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8076,7 +8104,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8086,7 +8114,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8113,10 +8141,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123569808</v>
+        <v>123565789</v>
       </c>
       <c r="B60" t="n">
-        <v>97333</v>
+        <v>90983</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8125,43 +8153,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>524077</v>
+        <v>524075</v>
       </c>
       <c r="R60" t="n">
-        <v>6713436</v>
+        <v>6713354</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8193,7 +8216,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8203,7 +8226,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8233,7 +8256,7 @@
         <v>123567823</v>
       </c>
       <c r="B61" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8356,10 +8379,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123563043</v>
+        <v>123562888</v>
       </c>
       <c r="B62" t="n">
-        <v>58159</v>
+        <v>57857</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8372,16 +8395,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -8389,15 +8412,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>adult</t>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -8406,13 +8428,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>524035</v>
+        <v>524019</v>
       </c>
       <c r="R62" t="n">
-        <v>6713295</v>
+        <v>6713291</v>
       </c>
       <c r="S62" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8441,7 +8463,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8451,7 +8473,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8478,10 +8500,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123566767</v>
+        <v>123571398</v>
       </c>
       <c r="B63" t="n">
-        <v>98379</v>
+        <v>90983</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8490,52 +8512,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>524084</v>
+        <v>524112</v>
       </c>
       <c r="R63" t="n">
-        <v>6713408</v>
+        <v>6713375</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8567,7 +8575,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8577,7 +8585,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8604,10 +8612,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123569917</v>
+        <v>123568589</v>
       </c>
       <c r="B64" t="n">
-        <v>57497</v>
+        <v>97350</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8616,43 +8624,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524078</v>
+        <v>524065</v>
       </c>
       <c r="R64" t="n">
-        <v>6713434</v>
+        <v>6713431</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8684,7 +8687,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8694,7 +8697,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8721,10 +8724,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123562888</v>
+        <v>123569917</v>
       </c>
       <c r="B65" t="n">
-        <v>57851</v>
+        <v>57503</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8733,20 +8736,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -8754,14 +8757,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8770,10 +8769,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>524019</v>
+        <v>524078</v>
       </c>
       <c r="R65" t="n">
-        <v>6713291</v>
+        <v>6713434</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8805,7 +8804,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8815,7 +8814,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8842,10 +8841,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123568031</v>
+        <v>123566656</v>
       </c>
       <c r="B66" t="n">
-        <v>58159</v>
+        <v>98396</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8854,43 +8853,52 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>524094</v>
+        <v>524082</v>
       </c>
       <c r="R66" t="n">
-        <v>6713439</v>
+        <v>6713393</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8922,7 +8930,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8932,7 +8940,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8959,10 +8967,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123564906</v>
+        <v>123562313</v>
       </c>
       <c r="B67" t="n">
-        <v>98379</v>
+        <v>90983</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8971,52 +8979,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>524050</v>
+        <v>523993</v>
       </c>
       <c r="R67" t="n">
-        <v>6713310</v>
+        <v>6713299</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9048,7 +9042,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9058,7 +9052,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9085,10 +9079,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123569630</v>
+        <v>123570699</v>
       </c>
       <c r="B68" t="n">
-        <v>100645</v>
+        <v>98396</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9097,42 +9091,40 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -9141,10 +9133,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>524047</v>
+        <v>524145</v>
       </c>
       <c r="R68" t="n">
-        <v>6713427</v>
+        <v>6713399</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9176,7 +9168,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9186,12 +9178,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Spridda över ca 15x10m.</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9200,7 +9187,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -9219,10 +9205,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123571398</v>
+        <v>123567299</v>
       </c>
       <c r="B69" t="n">
-        <v>90966</v>
+        <v>98396</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9231,38 +9217,52 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>524112</v>
+        <v>524117</v>
       </c>
       <c r="R69" t="n">
-        <v>6713375</v>
+        <v>6713411</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9294,7 +9294,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9328,6 +9328,511 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>123760786</v>
+      </c>
+      <c r="B70" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>523969</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6713750</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>123761045</v>
+      </c>
+      <c r="B71" t="n">
+        <v>8445</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>523984</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6713796</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>123762639</v>
+      </c>
+      <c r="B72" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>524016</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6713966</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På större yta, ca 35x15m, kanske mer.</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>123761091</v>
+      </c>
+      <c r="B73" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>523962</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6713819</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AY81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3581,10 +3581,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122957710</v>
+        <v>122958842</v>
       </c>
       <c r="B24" t="n">
-        <v>98396</v>
+        <v>57857</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3593,55 +3593,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvallen, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524145</v>
+        <v>524149</v>
       </c>
       <c r="R24" t="n">
-        <v>6713733</v>
+        <v>6713704</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3670,7 +3665,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3680,12 +3675,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Under klena granar.</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3712,10 +3702,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122958842</v>
+        <v>122957710</v>
       </c>
       <c r="B25" t="n">
-        <v>57857</v>
+        <v>98396</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3724,50 +3714,55 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Banvallen, Smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524149</v>
+        <v>524145</v>
       </c>
       <c r="R25" t="n">
-        <v>6713704</v>
+        <v>6713733</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3796,7 +3791,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3806,7 +3801,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Under klena granar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -8500,10 +8500,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123571398</v>
+        <v>123569917</v>
       </c>
       <c r="B63" t="n">
-        <v>90983</v>
+        <v>57503</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8516,34 +8516,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>524112</v>
+        <v>524078</v>
       </c>
       <c r="R63" t="n">
-        <v>6713375</v>
+        <v>6713434</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8575,7 +8580,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8585,7 +8590,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8612,10 +8617,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123568589</v>
+        <v>123571398</v>
       </c>
       <c r="B64" t="n">
-        <v>97350</v>
+        <v>90983</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8624,25 +8629,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8652,10 +8657,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524065</v>
+        <v>524112</v>
       </c>
       <c r="R64" t="n">
-        <v>6713431</v>
+        <v>6713375</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8687,7 +8692,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8697,7 +8702,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8724,10 +8729,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123569917</v>
+        <v>123568589</v>
       </c>
       <c r="B65" t="n">
-        <v>57503</v>
+        <v>97350</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8736,43 +8741,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>524078</v>
+        <v>524065</v>
       </c>
       <c r="R65" t="n">
-        <v>6713434</v>
+        <v>6713431</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8804,7 +8804,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9834,6 +9834,969 @@
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>123769023</v>
+      </c>
+      <c r="B74" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>524017</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6713986</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>123768989</v>
+      </c>
+      <c r="B75" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>524017</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6713958</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>123768976</v>
+      </c>
+      <c r="B76" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>524011</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6713981</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>123769093</v>
+      </c>
+      <c r="B77" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>524033</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6713983</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>123768995</v>
+      </c>
+      <c r="B78" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>524011</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6713982</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>123768932</v>
+      </c>
+      <c r="B79" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>524000</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6713968</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>123769126</v>
+      </c>
+      <c r="B80" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>524017</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6713977</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>123769072</v>
+      </c>
+      <c r="B81" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>524031</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6713998</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -4731,10 +4731,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122958244</v>
+        <v>122959354</v>
       </c>
       <c r="B33" t="n">
-        <v>98396</v>
+        <v>8445</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4743,45 +4743,31 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4790,10 +4776,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524143</v>
+        <v>524122</v>
       </c>
       <c r="R33" t="n">
-        <v>6713721</v>
+        <v>6713710</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4825,7 +4811,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4835,12 +4821,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter. Kanske fler.</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4867,10 +4848,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122959354</v>
+        <v>122958244</v>
       </c>
       <c r="B34" t="n">
-        <v>8445</v>
+        <v>98396</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4879,31 +4860,45 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4912,10 +4907,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524122</v>
+        <v>524143</v>
       </c>
       <c r="R34" t="n">
-        <v>6713710</v>
+        <v>6713721</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4947,7 +4942,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4957,7 +4952,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter. Kanske fler.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -7898,10 +7898,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123569808</v>
+        <v>123564666</v>
       </c>
       <c r="B58" t="n">
-        <v>97350</v>
+        <v>98396</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7910,31 +7910,40 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7943,10 +7952,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>524077</v>
+        <v>524034</v>
       </c>
       <c r="R58" t="n">
-        <v>6713436</v>
+        <v>6713303</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7978,7 +7987,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7988,7 +7997,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8015,10 +8024,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123564666</v>
+        <v>123569808</v>
       </c>
       <c r="B59" t="n">
-        <v>98396</v>
+        <v>97350</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8027,40 +8036,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -8069,10 +8069,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>524034</v>
+        <v>524077</v>
       </c>
       <c r="R59" t="n">
-        <v>6713303</v>
+        <v>6713436</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8104,7 +8104,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8500,10 +8500,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123569917</v>
+        <v>123571398</v>
       </c>
       <c r="B63" t="n">
-        <v>57503</v>
+        <v>90983</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8516,39 +8516,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>524078</v>
+        <v>524112</v>
       </c>
       <c r="R63" t="n">
-        <v>6713434</v>
+        <v>6713375</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8580,7 +8575,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8590,7 +8585,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8617,10 +8612,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123571398</v>
+        <v>123568589</v>
       </c>
       <c r="B64" t="n">
-        <v>90983</v>
+        <v>97350</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8629,25 +8624,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8657,10 +8652,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524112</v>
+        <v>524065</v>
       </c>
       <c r="R64" t="n">
-        <v>6713375</v>
+        <v>6713431</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8692,7 +8687,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8702,7 +8697,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8729,10 +8724,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123568589</v>
+        <v>123569917</v>
       </c>
       <c r="B65" t="n">
-        <v>97350</v>
+        <v>57503</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8741,38 +8736,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>524065</v>
+        <v>524078</v>
       </c>
       <c r="R65" t="n">
-        <v>6713431</v>
+        <v>6713434</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8804,7 +8804,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD65" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -8500,10 +8500,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123571398</v>
+        <v>123569917</v>
       </c>
       <c r="B63" t="n">
-        <v>90983</v>
+        <v>57503</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8516,34 +8516,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>524112</v>
+        <v>524078</v>
       </c>
       <c r="R63" t="n">
-        <v>6713375</v>
+        <v>6713434</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8575,7 +8580,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8585,7 +8590,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8612,10 +8617,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123568589</v>
+        <v>123571398</v>
       </c>
       <c r="B64" t="n">
-        <v>97350</v>
+        <v>90983</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8624,25 +8629,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8652,10 +8657,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524065</v>
+        <v>524112</v>
       </c>
       <c r="R64" t="n">
-        <v>6713431</v>
+        <v>6713375</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8687,7 +8692,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8697,7 +8702,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8724,10 +8729,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123569917</v>
+        <v>123568589</v>
       </c>
       <c r="B65" t="n">
-        <v>57503</v>
+        <v>97350</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8736,43 +8741,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>524078</v>
+        <v>524065</v>
       </c>
       <c r="R65" t="n">
-        <v>6713434</v>
+        <v>6713431</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8804,7 +8804,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD65" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -4984,10 +4984,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123413856</v>
+        <v>123413633</v>
       </c>
       <c r="B35" t="n">
-        <v>98396</v>
+        <v>57506</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4996,52 +4996,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524041</v>
+        <v>524031</v>
       </c>
       <c r="R35" t="n">
-        <v>6713443</v>
+        <v>6713503</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5073,7 +5064,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5083,7 +5074,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5110,10 +5101,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123414270</v>
+        <v>123413078</v>
       </c>
       <c r="B36" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5145,7 +5136,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5158,16 +5149,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524085</v>
+        <v>524102</v>
       </c>
       <c r="R36" t="n">
-        <v>6713390</v>
+        <v>6713632</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5199,7 +5195,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5209,7 +5205,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5236,10 +5232,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123413633</v>
+        <v>123413856</v>
       </c>
       <c r="B37" t="n">
-        <v>57503</v>
+        <v>98502</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5248,43 +5244,52 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524031</v>
+        <v>524041</v>
       </c>
       <c r="R37" t="n">
-        <v>6713503</v>
+        <v>6713443</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5316,7 +5321,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5326,7 +5331,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5353,10 +5358,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123412257</v>
+        <v>123412367</v>
       </c>
       <c r="B38" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5388,7 +5393,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5403,14 +5408,14 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524123</v>
+        <v>524136</v>
       </c>
       <c r="R38" t="n">
-        <v>6713637</v>
+        <v>6713648</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5442,7 +5447,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5452,7 +5457,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5479,10 +5484,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123412973</v>
+        <v>123413726</v>
       </c>
       <c r="B39" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5514,7 +5519,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5527,21 +5532,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524116</v>
+        <v>524030</v>
       </c>
       <c r="R39" t="n">
-        <v>6713634</v>
+        <v>6713469</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5573,7 +5573,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5610,10 +5610,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123413726</v>
+        <v>123412973</v>
       </c>
       <c r="B40" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5658,16 +5658,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524030</v>
+        <v>524116</v>
       </c>
       <c r="R40" t="n">
-        <v>6713469</v>
+        <v>6713634</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5699,7 +5704,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5709,7 +5714,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5736,10 +5741,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123413078</v>
+        <v>123412439</v>
       </c>
       <c r="B41" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5771,7 +5776,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5791,14 +5796,14 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524102</v>
+        <v>524137</v>
       </c>
       <c r="R41" t="n">
-        <v>6713632</v>
+        <v>6713646</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5830,7 +5835,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5840,7 +5845,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Inom ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5867,10 +5877,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123412439</v>
+        <v>123412326</v>
       </c>
       <c r="B42" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5902,7 +5912,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5915,21 +5925,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524137</v>
+        <v>524122</v>
       </c>
       <c r="R42" t="n">
-        <v>6713646</v>
+        <v>6713640</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5961,7 +5966,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5971,12 +5976,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:39</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Inom ca 5 kv/dm.</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6003,10 +6003,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123412326</v>
+        <v>123412257</v>
       </c>
       <c r="B43" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6057,10 +6057,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524122</v>
+        <v>524123</v>
       </c>
       <c r="R43" t="n">
-        <v>6713640</v>
+        <v>6713637</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6129,10 +6129,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123414352</v>
+        <v>123414270</v>
       </c>
       <c r="B44" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6183,10 +6183,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524098</v>
+        <v>524085</v>
       </c>
       <c r="R44" t="n">
-        <v>6713405</v>
+        <v>6713390</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6255,10 +6255,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123412367</v>
+        <v>123414352</v>
       </c>
       <c r="B45" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6305,14 +6305,14 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524136</v>
+        <v>524098</v>
       </c>
       <c r="R45" t="n">
-        <v>6713648</v>
+        <v>6713405</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6344,7 +6344,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6384,7 +6384,7 @@
         <v>123413119</v>
       </c>
       <c r="B46" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123528562</v>
+        <v>123527741</v>
       </c>
       <c r="B47" t="n">
-        <v>57503</v>
+        <v>98502</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6531,43 +6531,54 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524033</v>
+        <v>524029</v>
       </c>
       <c r="R47" t="n">
-        <v>6713503</v>
+        <v>6713459</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6599,7 +6610,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6609,7 +6620,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Sporadiskt spridda över ytan.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6618,6 +6634,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6636,10 +6653,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123526470</v>
+        <v>123528345</v>
       </c>
       <c r="B48" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6671,12 +6688,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -6684,21 +6701,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524101</v>
+        <v>524025</v>
       </c>
       <c r="R48" t="n">
-        <v>6713880</v>
+        <v>6713476</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6730,7 +6744,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6740,7 +6754,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6749,6 +6768,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6767,10 +6787,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123527655</v>
+        <v>123526470</v>
       </c>
       <c r="B49" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6802,7 +6822,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6815,16 +6835,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524041</v>
+        <v>524101</v>
       </c>
       <c r="R49" t="n">
-        <v>6713460</v>
+        <v>6713880</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6856,7 +6881,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6866,7 +6891,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6893,10 +6918,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123528345</v>
+        <v>123527655</v>
       </c>
       <c r="B50" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6933,7 +6958,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -6941,18 +6966,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524025</v>
+        <v>524041</v>
       </c>
       <c r="R50" t="n">
-        <v>6713476</v>
+        <v>6713460</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6984,7 +7007,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6994,12 +7017,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:41</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7008,7 +7026,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -7027,10 +7044,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123527741</v>
+        <v>123528562</v>
       </c>
       <c r="B51" t="n">
-        <v>98396</v>
+        <v>57506</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7039,54 +7056,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>524029</v>
+        <v>524033</v>
       </c>
       <c r="R51" t="n">
-        <v>6713459</v>
+        <v>6713503</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7118,7 +7124,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7128,12 +7134,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Sporadiskt spridda över ytan.</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7142,7 +7143,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7161,10 +7161,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123566767</v>
+        <v>123564666</v>
       </c>
       <c r="B52" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7215,10 +7215,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>524084</v>
+        <v>524034</v>
       </c>
       <c r="R52" t="n">
-        <v>6713408</v>
+        <v>6713303</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7250,7 +7250,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7287,10 +7287,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123563043</v>
+        <v>123569630</v>
       </c>
       <c r="B53" t="n">
-        <v>58165</v>
+        <v>100680</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7303,47 +7303,53 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103044</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>524035</v>
+        <v>524047</v>
       </c>
       <c r="R53" t="n">
-        <v>6713295</v>
+        <v>6713427</v>
       </c>
       <c r="S53" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7372,7 +7378,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7382,7 +7388,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Spridda över ca 15x10m.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7391,6 +7402,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7409,10 +7421,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123572491</v>
+        <v>123562888</v>
       </c>
       <c r="B54" t="n">
-        <v>90983</v>
+        <v>57860</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7421,38 +7433,47 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>523993</v>
+        <v>524019</v>
       </c>
       <c r="R54" t="n">
-        <v>6713281</v>
+        <v>6713291</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7484,7 +7505,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7494,7 +7515,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7521,10 +7542,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123568031</v>
+        <v>123567823</v>
       </c>
       <c r="B55" t="n">
-        <v>58165</v>
+        <v>98502</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7533,40 +7554,49 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>524094</v>
+        <v>524093</v>
       </c>
       <c r="R55" t="n">
         <v>6713439</v>
@@ -7601,7 +7631,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7611,7 +7641,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7638,10 +7668,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123569630</v>
+        <v>123564906</v>
       </c>
       <c r="B56" t="n">
-        <v>100662</v>
+        <v>98502</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7650,42 +7680,40 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7694,10 +7722,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>524047</v>
+        <v>524050</v>
       </c>
       <c r="R56" t="n">
-        <v>6713427</v>
+        <v>6713310</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7729,7 +7757,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7739,12 +7767,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Spridda över ca 15x10m.</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7753,7 +7776,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7772,10 +7794,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123564906</v>
+        <v>123565789</v>
       </c>
       <c r="B57" t="n">
-        <v>98396</v>
+        <v>90988</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7784,52 +7806,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>524050</v>
+        <v>524075</v>
       </c>
       <c r="R57" t="n">
-        <v>6713310</v>
+        <v>6713354</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7861,7 +7869,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7871,7 +7879,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7898,10 +7906,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123564666</v>
+        <v>123568031</v>
       </c>
       <c r="B58" t="n">
-        <v>98396</v>
+        <v>58168</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7910,52 +7918,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>524034</v>
+        <v>524094</v>
       </c>
       <c r="R58" t="n">
-        <v>6713303</v>
+        <v>6713439</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7987,7 +7986,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7997,7 +7996,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8024,10 +8023,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123569808</v>
+        <v>123570699</v>
       </c>
       <c r="B59" t="n">
-        <v>97350</v>
+        <v>98502</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8036,31 +8035,40 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -8069,10 +8077,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>524077</v>
+        <v>524145</v>
       </c>
       <c r="R59" t="n">
-        <v>6713436</v>
+        <v>6713399</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8104,7 +8112,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8114,7 +8122,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8141,10 +8149,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123565789</v>
+        <v>123568589</v>
       </c>
       <c r="B60" t="n">
-        <v>90983</v>
+        <v>97367</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8153,25 +8161,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -8181,10 +8189,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>524075</v>
+        <v>524065</v>
       </c>
       <c r="R60" t="n">
-        <v>6713354</v>
+        <v>6713431</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8216,7 +8224,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8226,7 +8234,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8253,10 +8261,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123567823</v>
+        <v>123571398</v>
       </c>
       <c r="B61" t="n">
-        <v>98396</v>
+        <v>90988</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8265,52 +8273,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>524093</v>
+        <v>524112</v>
       </c>
       <c r="R61" t="n">
-        <v>6713439</v>
+        <v>6713375</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8342,7 +8336,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8352,7 +8346,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8379,10 +8373,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123562888</v>
+        <v>123566656</v>
       </c>
       <c r="B62" t="n">
-        <v>57857</v>
+        <v>98502</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8391,47 +8385,52 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>524019</v>
+        <v>524082</v>
       </c>
       <c r="R62" t="n">
-        <v>6713291</v>
+        <v>6713393</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8463,7 +8462,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8473,7 +8472,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8500,10 +8499,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123569917</v>
+        <v>123572491</v>
       </c>
       <c r="B63" t="n">
-        <v>57503</v>
+        <v>90988</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8516,39 +8515,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>524078</v>
+        <v>523993</v>
       </c>
       <c r="R63" t="n">
-        <v>6713434</v>
+        <v>6713281</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8580,7 +8574,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8590,7 +8584,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8617,10 +8611,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123571398</v>
+        <v>123569917</v>
       </c>
       <c r="B64" t="n">
-        <v>90983</v>
+        <v>57506</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8633,34 +8627,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524112</v>
+        <v>524078</v>
       </c>
       <c r="R64" t="n">
-        <v>6713375</v>
+        <v>6713434</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8692,7 +8691,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8702,7 +8701,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8729,10 +8728,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123568589</v>
+        <v>123566767</v>
       </c>
       <c r="B65" t="n">
-        <v>97350</v>
+        <v>98502</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8741,38 +8740,52 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>524065</v>
+        <v>524084</v>
       </c>
       <c r="R65" t="n">
-        <v>6713431</v>
+        <v>6713408</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8804,7 +8817,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8814,7 +8827,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8841,10 +8854,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123566656</v>
+        <v>123563043</v>
       </c>
       <c r="B66" t="n">
-        <v>98396</v>
+        <v>58168</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8853,55 +8866,51 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>524082</v>
+        <v>524035</v>
       </c>
       <c r="R66" t="n">
-        <v>6713393</v>
+        <v>6713295</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8930,7 +8939,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8940,7 +8949,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8970,7 +8979,7 @@
         <v>123562313</v>
       </c>
       <c r="B67" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9079,10 +9088,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123570699</v>
+        <v>123569808</v>
       </c>
       <c r="B68" t="n">
-        <v>98396</v>
+        <v>97367</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9091,40 +9100,31 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -9133,10 +9133,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>524145</v>
+        <v>524077</v>
       </c>
       <c r="R68" t="n">
-        <v>6713399</v>
+        <v>6713436</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9178,7 +9178,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9208,7 +9208,7 @@
         <v>123567299</v>
       </c>
       <c r="B69" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>123760786</v>
       </c>
       <c r="B70" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>123761045</v>
       </c>
       <c r="B71" t="n">
-        <v>8445</v>
+        <v>8447</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9574,10 +9574,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123762639</v>
+        <v>123761091</v>
       </c>
       <c r="B72" t="n">
-        <v>100662</v>
+        <v>98502</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9586,30 +9586,30 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9619,24 +9619,19 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>524016</v>
+        <v>523962</v>
       </c>
       <c r="R72" t="n">
-        <v>6713966</v>
+        <v>6713819</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9668,7 +9663,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9678,12 +9673,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>20:14</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På större yta, ca 35x15m, kanske mer.</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9710,10 +9700,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123761091</v>
+        <v>123768932</v>
       </c>
       <c r="B73" t="n">
-        <v>98396</v>
+        <v>100680</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9722,52 +9712,52 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523962</v>
+        <v>524000</v>
       </c>
       <c r="R73" t="n">
-        <v>6713819</v>
+        <v>6713968</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9794,22 +9784,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9836,10 +9826,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123769023</v>
+        <v>123769126</v>
       </c>
       <c r="B74" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9884,7 +9874,7 @@
         <v>524017</v>
       </c>
       <c r="R74" t="n">
-        <v>6713986</v>
+        <v>6713977</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9916,7 +9906,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9926,7 +9916,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9953,10 +9943,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123768989</v>
+        <v>123768995</v>
       </c>
       <c r="B75" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9998,10 +9988,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>524017</v>
+        <v>524011</v>
       </c>
       <c r="R75" t="n">
-        <v>6713958</v>
+        <v>6713982</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10033,7 +10023,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10043,7 +10033,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10070,10 +10060,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123768976</v>
+        <v>123769072</v>
       </c>
       <c r="B76" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10103,22 +10093,31 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>524011</v>
+        <v>524031</v>
       </c>
       <c r="R76" t="n">
-        <v>6713981</v>
+        <v>6713998</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10150,7 +10149,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10160,7 +10159,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10187,10 +10186,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123769093</v>
+        <v>123769023</v>
       </c>
       <c r="B77" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10220,16 +10219,7 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -10241,10 +10231,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>524033</v>
+        <v>524017</v>
       </c>
       <c r="R77" t="n">
-        <v>6713983</v>
+        <v>6713986</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10276,7 +10266,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10286,7 +10276,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10313,10 +10303,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123768995</v>
+        <v>123768989</v>
       </c>
       <c r="B78" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10358,10 +10348,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>524011</v>
+        <v>524017</v>
       </c>
       <c r="R78" t="n">
-        <v>6713982</v>
+        <v>6713958</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10393,7 +10383,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10403,7 +10393,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10430,10 +10420,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123768932</v>
+        <v>123769093</v>
       </c>
       <c r="B79" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10484,10 +10474,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>524000</v>
+        <v>524033</v>
       </c>
       <c r="R79" t="n">
-        <v>6713968</v>
+        <v>6713983</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10519,7 +10509,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10529,7 +10519,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10556,10 +10546,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123769126</v>
+        <v>123768976</v>
       </c>
       <c r="B80" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10601,10 +10591,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>524017</v>
+        <v>524011</v>
       </c>
       <c r="R80" t="n">
-        <v>6713977</v>
+        <v>6713981</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10636,7 +10626,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10646,7 +10636,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10673,10 +10663,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123769072</v>
+        <v>123762639</v>
       </c>
       <c r="B81" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10708,7 +10698,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -10718,19 +10708,25 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>524031</v>
+        <v>524016</v>
       </c>
       <c r="R81" t="n">
-        <v>6713998</v>
+        <v>6713966</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10757,22 +10753,27 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På större yta, ca 35x15m, kanske mer. På avverkningsyta där dom dragit basväg rakt över växtplatsen.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10781,6 +10782,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -4984,10 +4984,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123413633</v>
+        <v>123413856</v>
       </c>
       <c r="B35" t="n">
-        <v>57506</v>
+        <v>98504</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4996,43 +4996,52 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524031</v>
+        <v>524041</v>
       </c>
       <c r="R35" t="n">
-        <v>6713503</v>
+        <v>6713443</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5064,7 +5073,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5074,7 +5083,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5101,10 +5110,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123413078</v>
+        <v>123412257</v>
       </c>
       <c r="B36" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5136,7 +5145,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5149,21 +5158,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524102</v>
+        <v>524123</v>
       </c>
       <c r="R36" t="n">
-        <v>6713632</v>
+        <v>6713637</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5195,7 +5199,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5205,7 +5209,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5232,10 +5236,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123413856</v>
+        <v>123412326</v>
       </c>
       <c r="B37" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5267,7 +5271,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5286,10 +5290,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524041</v>
+        <v>524122</v>
       </c>
       <c r="R37" t="n">
-        <v>6713443</v>
+        <v>6713640</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5321,7 +5325,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5331,7 +5335,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5358,10 +5362,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123412367</v>
+        <v>123413078</v>
       </c>
       <c r="B38" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5393,7 +5397,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5406,16 +5410,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524136</v>
+        <v>524102</v>
       </c>
       <c r="R38" t="n">
-        <v>6713648</v>
+        <v>6713632</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5447,7 +5456,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5457,7 +5466,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5484,10 +5493,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123413726</v>
+        <v>123413119</v>
       </c>
       <c r="B39" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5524,7 +5533,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -5532,16 +5541,22 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524030</v>
+        <v>524101</v>
       </c>
       <c r="R39" t="n">
-        <v>6713469</v>
+        <v>6713638</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5573,7 +5588,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5583,7 +5598,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Spridda sporadiskt över ytan.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5592,6 +5612,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5610,10 +5631,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123412973</v>
+        <v>123412439</v>
       </c>
       <c r="B40" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5645,7 +5666,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5669,10 +5690,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524116</v>
+        <v>524137</v>
       </c>
       <c r="R40" t="n">
-        <v>6713634</v>
+        <v>6713646</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5704,7 +5725,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5714,7 +5735,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Inom ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5741,10 +5767,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123412439</v>
+        <v>123414270</v>
       </c>
       <c r="B41" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5776,7 +5802,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5789,21 +5815,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524137</v>
+        <v>524085</v>
       </c>
       <c r="R41" t="n">
-        <v>6713646</v>
+        <v>6713390</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5835,7 +5856,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5845,12 +5866,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:39</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Inom ca 5 kv/dm.</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5877,10 +5893,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123412326</v>
+        <v>123413633</v>
       </c>
       <c r="B42" t="n">
-        <v>98502</v>
+        <v>57507</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5889,52 +5905,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524122</v>
+        <v>524031</v>
       </c>
       <c r="R42" t="n">
-        <v>6713640</v>
+        <v>6713503</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5966,7 +5973,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5976,7 +5983,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6003,10 +6010,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123412257</v>
+        <v>123414352</v>
       </c>
       <c r="B43" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6038,7 +6045,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6057,10 +6064,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524123</v>
+        <v>524098</v>
       </c>
       <c r="R43" t="n">
-        <v>6713637</v>
+        <v>6713405</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6092,7 +6099,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6102,7 +6109,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6129,10 +6136,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123414270</v>
+        <v>123412367</v>
       </c>
       <c r="B44" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6164,7 +6171,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6179,14 +6186,14 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524085</v>
+        <v>524136</v>
       </c>
       <c r="R44" t="n">
-        <v>6713390</v>
+        <v>6713648</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6218,7 +6225,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6228,7 +6235,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6255,10 +6262,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123414352</v>
+        <v>123413726</v>
       </c>
       <c r="B45" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6290,7 +6297,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6309,10 +6316,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524098</v>
+        <v>524030</v>
       </c>
       <c r="R45" t="n">
-        <v>6713405</v>
+        <v>6713469</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6344,7 +6351,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6354,7 +6361,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6381,10 +6388,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123413119</v>
+        <v>123412973</v>
       </c>
       <c r="B46" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6416,12 +6423,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -6429,7 +6436,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6437,14 +6443,14 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524101</v>
+        <v>524116</v>
       </c>
       <c r="R46" t="n">
-        <v>6713638</v>
+        <v>6713634</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6476,7 +6482,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6486,12 +6492,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:59</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt över ytan.</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6500,7 +6501,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6519,10 +6519,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123527741</v>
+        <v>123528562</v>
       </c>
       <c r="B47" t="n">
-        <v>98502</v>
+        <v>57507</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6531,54 +6531,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524029</v>
+        <v>524033</v>
       </c>
       <c r="R47" t="n">
-        <v>6713459</v>
+        <v>6713503</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6610,7 +6599,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6620,12 +6609,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Sporadiskt spridda över ytan.</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6634,7 +6618,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6653,10 +6636,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123528345</v>
+        <v>123527741</v>
       </c>
       <c r="B48" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6688,7 +6671,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6709,10 +6692,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524025</v>
+        <v>524029</v>
       </c>
       <c r="R48" t="n">
-        <v>6713476</v>
+        <v>6713459</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6744,7 +6727,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6754,12 +6737,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>En överblommad.</t>
+          <t>Sporadiskt spridda över ytan.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6790,7 +6773,7 @@
         <v>123526470</v>
       </c>
       <c r="B49" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6921,7 +6904,7 @@
         <v>123527655</v>
       </c>
       <c r="B50" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7044,10 +7027,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123528562</v>
+        <v>123528345</v>
       </c>
       <c r="B51" t="n">
-        <v>57506</v>
+        <v>98504</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7056,43 +7039,54 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>524033</v>
+        <v>524025</v>
       </c>
       <c r="R51" t="n">
-        <v>6713503</v>
+        <v>6713476</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7137,12 +7131,18 @@
           <t>18:41</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7164,7 +7164,7 @@
         <v>123564666</v>
       </c>
       <c r="B52" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7287,10 +7287,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123569630</v>
+        <v>123569808</v>
       </c>
       <c r="B53" t="n">
-        <v>100680</v>
+        <v>97369</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7303,35 +7303,24 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -7343,10 +7332,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>524047</v>
+        <v>524077</v>
       </c>
       <c r="R53" t="n">
-        <v>6713427</v>
+        <v>6713436</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7378,7 +7367,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7388,12 +7377,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Spridda över ca 15x10m.</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7402,7 +7386,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7421,10 +7404,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123562888</v>
+        <v>123564906</v>
       </c>
       <c r="B54" t="n">
-        <v>57860</v>
+        <v>98504</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7433,47 +7416,52 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>524019</v>
+        <v>524050</v>
       </c>
       <c r="R54" t="n">
-        <v>6713291</v>
+        <v>6713310</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7505,7 +7493,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7515,7 +7503,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7542,10 +7530,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123567823</v>
+        <v>123567299</v>
       </c>
       <c r="B55" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7577,7 +7565,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7596,10 +7584,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>524093</v>
+        <v>524117</v>
       </c>
       <c r="R55" t="n">
-        <v>6713439</v>
+        <v>6713411</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7631,7 +7619,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7641,7 +7629,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7668,10 +7656,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123564906</v>
+        <v>123568031</v>
       </c>
       <c r="B56" t="n">
-        <v>98502</v>
+        <v>58169</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7680,52 +7668,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>524050</v>
+        <v>524094</v>
       </c>
       <c r="R56" t="n">
-        <v>6713310</v>
+        <v>6713439</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7757,7 +7736,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7767,7 +7746,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7794,10 +7773,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123565789</v>
+        <v>123569630</v>
       </c>
       <c r="B57" t="n">
-        <v>90988</v>
+        <v>100682</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7806,38 +7785,54 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>524075</v>
+        <v>524047</v>
       </c>
       <c r="R57" t="n">
-        <v>6713354</v>
+        <v>6713427</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7869,7 +7864,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7879,7 +7874,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Spridda över ca 15x10m.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7888,6 +7888,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7906,10 +7907,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123568031</v>
+        <v>123562888</v>
       </c>
       <c r="B58" t="n">
-        <v>58168</v>
+        <v>57861</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7922,16 +7923,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -7939,10 +7940,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7951,10 +7956,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>524094</v>
+        <v>524019</v>
       </c>
       <c r="R58" t="n">
-        <v>6713439</v>
+        <v>6713291</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7986,7 +7991,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7996,7 +8001,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8023,10 +8028,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123570699</v>
+        <v>123566656</v>
       </c>
       <c r="B59" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8058,7 +8063,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -8077,10 +8082,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>524145</v>
+        <v>524082</v>
       </c>
       <c r="R59" t="n">
-        <v>6713399</v>
+        <v>6713393</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8112,7 +8117,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8122,7 +8127,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8152,7 +8157,7 @@
         <v>123568589</v>
       </c>
       <c r="B60" t="n">
-        <v>97367</v>
+        <v>97369</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8261,10 +8266,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123571398</v>
+        <v>123569917</v>
       </c>
       <c r="B61" t="n">
-        <v>90988</v>
+        <v>57507</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8277,34 +8282,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>524112</v>
+        <v>524078</v>
       </c>
       <c r="R61" t="n">
-        <v>6713375</v>
+        <v>6713434</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8336,7 +8346,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8346,7 +8356,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8373,10 +8383,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123566656</v>
+        <v>123572491</v>
       </c>
       <c r="B62" t="n">
-        <v>98502</v>
+        <v>90990</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8385,52 +8395,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>524082</v>
+        <v>523993</v>
       </c>
       <c r="R62" t="n">
-        <v>6713393</v>
+        <v>6713281</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8462,7 +8458,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8472,7 +8468,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8499,10 +8495,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123572491</v>
+        <v>123567823</v>
       </c>
       <c r="B63" t="n">
-        <v>90988</v>
+        <v>98504</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8511,38 +8507,52 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523993</v>
+        <v>524093</v>
       </c>
       <c r="R63" t="n">
-        <v>6713281</v>
+        <v>6713439</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8574,7 +8584,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8584,7 +8594,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8611,10 +8621,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123569917</v>
+        <v>123570699</v>
       </c>
       <c r="B64" t="n">
-        <v>57506</v>
+        <v>98504</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8623,43 +8633,52 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524078</v>
+        <v>524145</v>
       </c>
       <c r="R64" t="n">
-        <v>6713434</v>
+        <v>6713399</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8691,7 +8710,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8701,7 +8720,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8728,10 +8747,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123566767</v>
+        <v>123571398</v>
       </c>
       <c r="B65" t="n">
-        <v>98502</v>
+        <v>90990</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8740,52 +8759,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>524084</v>
+        <v>524112</v>
       </c>
       <c r="R65" t="n">
-        <v>6713408</v>
+        <v>6713375</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8817,7 +8822,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8827,7 +8832,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8857,7 +8862,7 @@
         <v>123563043</v>
       </c>
       <c r="B66" t="n">
-        <v>58168</v>
+        <v>58169</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8979,7 +8984,7 @@
         <v>123562313</v>
       </c>
       <c r="B67" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9088,10 +9093,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123569808</v>
+        <v>123566767</v>
       </c>
       <c r="B68" t="n">
-        <v>97367</v>
+        <v>98504</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9100,31 +9105,40 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -9133,10 +9147,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>524077</v>
+        <v>524084</v>
       </c>
       <c r="R68" t="n">
-        <v>6713436</v>
+        <v>6713408</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9168,7 +9182,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9178,7 +9192,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9205,10 +9219,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123567299</v>
+        <v>123565789</v>
       </c>
       <c r="B69" t="n">
-        <v>98502</v>
+        <v>90990</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9217,52 +9231,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>524117</v>
+        <v>524075</v>
       </c>
       <c r="R69" t="n">
-        <v>6713411</v>
+        <v>6713354</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9294,7 +9294,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9331,10 +9331,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123760786</v>
+        <v>123761091</v>
       </c>
       <c r="B70" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9385,10 +9385,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523969</v>
+        <v>523962</v>
       </c>
       <c r="R70" t="n">
-        <v>6713750</v>
+        <v>6713819</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9420,7 +9420,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9574,10 +9574,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123761091</v>
+        <v>123760786</v>
       </c>
       <c r="B72" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9628,10 +9628,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523962</v>
+        <v>523969</v>
       </c>
       <c r="R72" t="n">
-        <v>6713819</v>
+        <v>6713750</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9700,10 +9700,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123768932</v>
+        <v>123768989</v>
       </c>
       <c r="B73" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9733,16 +9733,7 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -9754,10 +9745,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>524000</v>
+        <v>524017</v>
       </c>
       <c r="R73" t="n">
-        <v>6713968</v>
+        <v>6713958</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9789,7 +9780,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9799,7 +9790,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9826,10 +9817,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123769126</v>
+        <v>123768976</v>
       </c>
       <c r="B74" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9871,10 +9862,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>524017</v>
+        <v>524011</v>
       </c>
       <c r="R74" t="n">
-        <v>6713977</v>
+        <v>6713981</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9906,7 +9897,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9916,7 +9907,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9943,10 +9934,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123768995</v>
+        <v>123769023</v>
       </c>
       <c r="B75" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9988,10 +9979,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>524011</v>
+        <v>524017</v>
       </c>
       <c r="R75" t="n">
-        <v>6713982</v>
+        <v>6713986</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10063,7 +10054,7 @@
         <v>123769072</v>
       </c>
       <c r="B76" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10186,10 +10177,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123769023</v>
+        <v>123769093</v>
       </c>
       <c r="B77" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10219,7 +10210,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -10231,10 +10231,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>524017</v>
+        <v>524033</v>
       </c>
       <c r="R77" t="n">
-        <v>6713986</v>
+        <v>6713983</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10266,7 +10266,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10303,10 +10303,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123768989</v>
+        <v>123769126</v>
       </c>
       <c r="B78" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>524017</v>
       </c>
       <c r="R78" t="n">
-        <v>6713958</v>
+        <v>6713977</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10383,7 +10383,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10420,10 +10420,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123769093</v>
+        <v>123768995</v>
       </c>
       <c r="B79" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10453,16 +10453,7 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -10474,10 +10465,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>524033</v>
+        <v>524011</v>
       </c>
       <c r="R79" t="n">
-        <v>6713983</v>
+        <v>6713982</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10509,7 +10500,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10519,7 +10510,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10546,10 +10537,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123768976</v>
+        <v>123768932</v>
       </c>
       <c r="B80" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10579,7 +10570,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -10591,10 +10591,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>524011</v>
+        <v>524000</v>
       </c>
       <c r="R80" t="n">
-        <v>6713981</v>
+        <v>6713968</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10636,7 +10636,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10666,7 +10666,7 @@
         <v>123762639</v>
       </c>
       <c r="B81" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -8383,10 +8383,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123572491</v>
+        <v>123567823</v>
       </c>
       <c r="B62" t="n">
-        <v>90990</v>
+        <v>98504</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8395,38 +8395,52 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>523993</v>
+        <v>524093</v>
       </c>
       <c r="R62" t="n">
-        <v>6713281</v>
+        <v>6713439</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8458,7 +8472,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8468,7 +8482,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8495,7 +8509,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123567823</v>
+        <v>123570699</v>
       </c>
       <c r="B63" t="n">
         <v>98504</v>
@@ -8530,7 +8544,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -8549,10 +8563,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>524093</v>
+        <v>524145</v>
       </c>
       <c r="R63" t="n">
-        <v>6713439</v>
+        <v>6713399</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8584,7 +8598,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8594,7 +8608,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8621,10 +8635,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123570699</v>
+        <v>123572491</v>
       </c>
       <c r="B64" t="n">
-        <v>98504</v>
+        <v>90990</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8633,52 +8647,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524145</v>
+        <v>523993</v>
       </c>
       <c r="R64" t="n">
-        <v>6713399</v>
+        <v>6713281</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8710,7 +8710,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD64" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -7530,10 +7530,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123567299</v>
+        <v>123568031</v>
       </c>
       <c r="B55" t="n">
-        <v>98504</v>
+        <v>58169</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7542,52 +7542,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>524117</v>
+        <v>524094</v>
       </c>
       <c r="R55" t="n">
-        <v>6713411</v>
+        <v>6713439</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7619,7 +7610,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7629,7 +7620,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7656,10 +7647,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123568031</v>
+        <v>123567299</v>
       </c>
       <c r="B56" t="n">
-        <v>58169</v>
+        <v>98504</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7668,43 +7659,52 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>524094</v>
+        <v>524117</v>
       </c>
       <c r="R56" t="n">
-        <v>6713439</v>
+        <v>6713411</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7736,7 +7736,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -4987,7 +4987,7 @@
         <v>123413856</v>
       </c>
       <c r="B35" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5110,10 +5110,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123412257</v>
+        <v>123412367</v>
       </c>
       <c r="B36" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5160,14 +5160,14 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524123</v>
+        <v>524136</v>
       </c>
       <c r="R36" t="n">
-        <v>6713637</v>
+        <v>6713648</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5236,10 +5236,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123412326</v>
+        <v>123413633</v>
       </c>
       <c r="B37" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5248,52 +5248,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524122</v>
+        <v>524031</v>
       </c>
       <c r="R37" t="n">
-        <v>6713640</v>
+        <v>6713503</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5325,7 +5316,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5335,7 +5326,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5362,10 +5353,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123413078</v>
+        <v>123414352</v>
       </c>
       <c r="B38" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5397,7 +5388,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5410,21 +5401,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524102</v>
+        <v>524098</v>
       </c>
       <c r="R38" t="n">
-        <v>6713632</v>
+        <v>6713405</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5456,7 +5442,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5466,7 +5452,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5493,10 +5479,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123413119</v>
+        <v>123412973</v>
       </c>
       <c r="B39" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5528,12 +5514,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -5541,7 +5527,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5549,14 +5534,14 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524101</v>
+        <v>524116</v>
       </c>
       <c r="R39" t="n">
-        <v>6713638</v>
+        <v>6713634</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5588,7 +5573,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5598,12 +5583,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:59</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt över ytan.</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5612,7 +5592,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5631,10 +5610,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123412439</v>
+        <v>123413119</v>
       </c>
       <c r="B40" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5666,12 +5645,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5679,6 +5658,7 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5686,14 +5666,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524137</v>
+        <v>524101</v>
       </c>
       <c r="R40" t="n">
-        <v>6713646</v>
+        <v>6713638</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5725,7 +5705,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5735,12 +5715,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Inom ca 5 kv/dm.</t>
+          <t>Spridda sporadiskt över ytan.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5749,6 +5729,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5770,7 +5751,7 @@
         <v>123414270</v>
       </c>
       <c r="B41" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5893,10 +5874,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123413633</v>
+        <v>123412326</v>
       </c>
       <c r="B42" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5905,43 +5886,52 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524031</v>
+        <v>524122</v>
       </c>
       <c r="R42" t="n">
-        <v>6713503</v>
+        <v>6713640</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5973,7 +5963,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5983,7 +5973,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6010,10 +6000,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123414352</v>
+        <v>123413726</v>
       </c>
       <c r="B43" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6045,7 +6035,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6064,10 +6054,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524098</v>
+        <v>524030</v>
       </c>
       <c r="R43" t="n">
-        <v>6713405</v>
+        <v>6713469</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6099,7 +6089,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6109,7 +6099,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6136,10 +6126,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123412367</v>
+        <v>123412439</v>
       </c>
       <c r="B44" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6171,7 +6161,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6184,16 +6174,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524136</v>
+        <v>524137</v>
       </c>
       <c r="R44" t="n">
-        <v>6713648</v>
+        <v>6713646</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6225,7 +6220,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6235,7 +6230,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Inom ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6262,10 +6262,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123413726</v>
+        <v>123413078</v>
       </c>
       <c r="B45" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6310,16 +6310,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524030</v>
+        <v>524102</v>
       </c>
       <c r="R45" t="n">
-        <v>6713469</v>
+        <v>6713632</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6351,7 +6356,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6361,7 +6366,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6388,10 +6393,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123412973</v>
+        <v>123412257</v>
       </c>
       <c r="B46" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6423,7 +6428,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6436,21 +6441,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524116</v>
+        <v>524123</v>
       </c>
       <c r="R46" t="n">
-        <v>6713634</v>
+        <v>6713637</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6519,10 +6519,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123528562</v>
+        <v>123526470</v>
       </c>
       <c r="B47" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6531,43 +6531,57 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524033</v>
+        <v>524101</v>
       </c>
       <c r="R47" t="n">
-        <v>6713503</v>
+        <v>6713880</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6599,7 +6613,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6609,7 +6623,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6636,10 +6650,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123527741</v>
+        <v>123528345</v>
       </c>
       <c r="B48" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6671,7 +6685,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6692,10 +6706,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524029</v>
+        <v>524025</v>
       </c>
       <c r="R48" t="n">
-        <v>6713459</v>
+        <v>6713476</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6727,7 +6741,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6737,12 +6751,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Sporadiskt spridda över ytan.</t>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6770,10 +6784,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123526470</v>
+        <v>123527741</v>
       </c>
       <c r="B49" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6805,12 +6819,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -6818,21 +6832,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524101</v>
+        <v>524029</v>
       </c>
       <c r="R49" t="n">
-        <v>6713880</v>
+        <v>6713459</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6864,7 +6875,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6874,7 +6885,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Sporadiskt spridda över ytan.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6883,6 +6899,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6904,7 +6921,7 @@
         <v>123527655</v>
       </c>
       <c r="B50" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7027,10 +7044,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123528345</v>
+        <v>123528562</v>
       </c>
       <c r="B51" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7039,54 +7056,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>524025</v>
+        <v>524033</v>
       </c>
       <c r="R51" t="n">
-        <v>6713476</v>
+        <v>6713503</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7131,18 +7137,12 @@
           <t>18:41</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7161,10 +7161,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123564666</v>
+        <v>123563043</v>
       </c>
       <c r="B52" t="n">
-        <v>98504</v>
+        <v>58169</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7173,55 +7173,51 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>524034</v>
+        <v>524035</v>
       </c>
       <c r="R52" t="n">
-        <v>6713303</v>
+        <v>6713295</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7250,7 +7246,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7260,7 +7256,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7290,7 +7286,7 @@
         <v>123569808</v>
       </c>
       <c r="B53" t="n">
-        <v>97369</v>
+        <v>96957</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7407,7 +7403,7 @@
         <v>123564906</v>
       </c>
       <c r="B54" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7530,10 +7526,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123568031</v>
+        <v>123567823</v>
       </c>
       <c r="B55" t="n">
-        <v>58169</v>
+        <v>98079</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7542,40 +7538,49 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>524094</v>
+        <v>524093</v>
       </c>
       <c r="R55" t="n">
         <v>6713439</v>
@@ -7610,7 +7615,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7620,7 +7625,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7647,10 +7652,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123567299</v>
+        <v>123570699</v>
       </c>
       <c r="B56" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7682,7 +7687,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7701,10 +7706,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>524117</v>
+        <v>524145</v>
       </c>
       <c r="R56" t="n">
-        <v>6713411</v>
+        <v>6713399</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7736,7 +7741,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7746,7 +7751,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7773,10 +7778,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123569630</v>
+        <v>123566767</v>
       </c>
       <c r="B57" t="n">
-        <v>100682</v>
+        <v>98079</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7785,42 +7790,40 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7829,10 +7832,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>524047</v>
+        <v>524084</v>
       </c>
       <c r="R57" t="n">
-        <v>6713427</v>
+        <v>6713408</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7864,7 +7867,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7874,12 +7877,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Spridda över ca 15x10m.</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7888,7 +7886,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7907,10 +7904,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123562888</v>
+        <v>123566656</v>
       </c>
       <c r="B58" t="n">
-        <v>57861</v>
+        <v>98079</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7919,47 +7916,52 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>524019</v>
+        <v>524082</v>
       </c>
       <c r="R58" t="n">
-        <v>6713291</v>
+        <v>6713393</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7991,7 +7993,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8001,7 +8003,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8028,10 +8030,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123566656</v>
+        <v>123564666</v>
       </c>
       <c r="B59" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8082,10 +8084,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>524082</v>
+        <v>524034</v>
       </c>
       <c r="R59" t="n">
-        <v>6713393</v>
+        <v>6713303</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8117,7 +8119,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8127,7 +8129,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8154,10 +8156,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123568589</v>
+        <v>123565789</v>
       </c>
       <c r="B60" t="n">
-        <v>97369</v>
+        <v>90990</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8166,25 +8168,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -8194,10 +8196,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>524065</v>
+        <v>524075</v>
       </c>
       <c r="R60" t="n">
-        <v>6713431</v>
+        <v>6713354</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8229,7 +8231,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8239,7 +8241,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8266,10 +8268,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123569917</v>
+        <v>123567299</v>
       </c>
       <c r="B61" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8278,43 +8280,52 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>524078</v>
+        <v>524117</v>
       </c>
       <c r="R61" t="n">
-        <v>6713434</v>
+        <v>6713411</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8346,7 +8357,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8356,7 +8367,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8383,10 +8394,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123567823</v>
+        <v>123562313</v>
       </c>
       <c r="B62" t="n">
-        <v>98504</v>
+        <v>90990</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8395,52 +8406,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>524093</v>
+        <v>523993</v>
       </c>
       <c r="R62" t="n">
-        <v>6713439</v>
+        <v>6713299</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8472,7 +8469,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8482,7 +8479,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8509,10 +8506,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123570699</v>
+        <v>123562888</v>
       </c>
       <c r="B63" t="n">
-        <v>98504</v>
+        <v>57861</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8521,52 +8518,47 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>524145</v>
+        <v>524019</v>
       </c>
       <c r="R63" t="n">
-        <v>6713399</v>
+        <v>6713291</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8598,7 +8590,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8608,7 +8600,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8859,10 +8851,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123563043</v>
+        <v>123569630</v>
       </c>
       <c r="B66" t="n">
-        <v>58169</v>
+        <v>100257</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8875,47 +8867,53 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103044</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>524035</v>
+        <v>524047</v>
       </c>
       <c r="R66" t="n">
-        <v>6713295</v>
+        <v>6713427</v>
       </c>
       <c r="S66" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8944,7 +8942,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8954,7 +8952,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Spridda över ca 15x10m.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8963,6 +8966,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -8981,10 +8985,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123562313</v>
+        <v>123568589</v>
       </c>
       <c r="B67" t="n">
-        <v>90990</v>
+        <v>96957</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8993,25 +8997,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9021,10 +9025,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>523993</v>
+        <v>524065</v>
       </c>
       <c r="R67" t="n">
-        <v>6713299</v>
+        <v>6713431</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9056,7 +9060,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9066,7 +9070,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9093,10 +9097,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123566767</v>
+        <v>123568031</v>
       </c>
       <c r="B68" t="n">
-        <v>98504</v>
+        <v>58169</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9105,52 +9109,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>524084</v>
+        <v>524094</v>
       </c>
       <c r="R68" t="n">
-        <v>6713408</v>
+        <v>6713439</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9182,7 +9177,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9192,7 +9187,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9219,10 +9214,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123565789</v>
+        <v>123569917</v>
       </c>
       <c r="B69" t="n">
-        <v>90990</v>
+        <v>57507</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9235,34 +9230,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>524075</v>
+        <v>524078</v>
       </c>
       <c r="R69" t="n">
-        <v>6713354</v>
+        <v>6713434</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9294,7 +9294,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9331,10 +9331,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123761091</v>
+        <v>123761045</v>
       </c>
       <c r="B70" t="n">
-        <v>98504</v>
+        <v>8447</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9343,40 +9343,31 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -9385,10 +9376,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523962</v>
+        <v>523984</v>
       </c>
       <c r="R70" t="n">
-        <v>6713819</v>
+        <v>6713796</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9420,7 +9411,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9430,7 +9421,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9457,10 +9448,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123761045</v>
+        <v>123761091</v>
       </c>
       <c r="B71" t="n">
-        <v>8447</v>
+        <v>98079</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9469,31 +9460,40 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -9502,10 +9502,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523984</v>
+        <v>523962</v>
       </c>
       <c r="R71" t="n">
-        <v>6713796</v>
+        <v>6713819</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9537,7 +9537,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9577,7 +9577,7 @@
         <v>123760786</v>
       </c>
       <c r="B72" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9700,10 +9700,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123768989</v>
+        <v>123769072</v>
       </c>
       <c r="B73" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9733,22 +9733,31 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>524017</v>
+        <v>524031</v>
       </c>
       <c r="R73" t="n">
-        <v>6713958</v>
+        <v>6713998</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9780,7 +9789,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9790,7 +9799,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9820,7 +9829,7 @@
         <v>123768976</v>
       </c>
       <c r="B74" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9934,10 +9943,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123769023</v>
+        <v>123769093</v>
       </c>
       <c r="B75" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9967,7 +9976,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -9979,10 +9997,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>524017</v>
+        <v>524033</v>
       </c>
       <c r="R75" t="n">
-        <v>6713986</v>
+        <v>6713983</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10014,7 +10032,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10024,7 +10042,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10051,10 +10069,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123769072</v>
+        <v>123769023</v>
       </c>
       <c r="B76" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10084,31 +10102,22 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>524031</v>
+        <v>524017</v>
       </c>
       <c r="R76" t="n">
-        <v>6713998</v>
+        <v>6713986</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10140,7 +10149,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10150,7 +10159,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10177,10 +10186,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123769093</v>
+        <v>123768932</v>
       </c>
       <c r="B77" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10231,10 +10240,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>524033</v>
+        <v>524000</v>
       </c>
       <c r="R77" t="n">
-        <v>6713983</v>
+        <v>6713968</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10266,7 +10275,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10276,7 +10285,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10303,10 +10312,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123769126</v>
+        <v>123768995</v>
       </c>
       <c r="B78" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10348,10 +10357,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>524017</v>
+        <v>524011</v>
       </c>
       <c r="R78" t="n">
-        <v>6713977</v>
+        <v>6713982</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10383,7 +10392,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10393,7 +10402,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10420,10 +10429,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123768995</v>
+        <v>123769126</v>
       </c>
       <c r="B79" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10465,10 +10474,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>524011</v>
+        <v>524017</v>
       </c>
       <c r="R79" t="n">
-        <v>6713982</v>
+        <v>6713977</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10500,7 +10509,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10510,7 +10519,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10537,10 +10546,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123768932</v>
+        <v>123768989</v>
       </c>
       <c r="B80" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10570,16 +10579,7 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -10591,10 +10591,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>524000</v>
+        <v>524017</v>
       </c>
       <c r="R80" t="n">
-        <v>6713968</v>
+        <v>6713958</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10636,7 +10636,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10666,7 +10666,7 @@
         <v>123762639</v>
       </c>
       <c r="B81" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -4984,7 +4984,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123413856</v>
+        <v>123412367</v>
       </c>
       <c r="B35" t="n">
         <v>98079</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5034,14 +5034,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524041</v>
+        <v>524136</v>
       </c>
       <c r="R35" t="n">
-        <v>6713443</v>
+        <v>6713648</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5110,7 +5110,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123412367</v>
+        <v>123413856</v>
       </c>
       <c r="B36" t="n">
         <v>98079</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5160,14 +5160,14 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524136</v>
+        <v>524041</v>
       </c>
       <c r="R36" t="n">
-        <v>6713648</v>
+        <v>6713443</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5236,10 +5236,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123413633</v>
+        <v>123412257</v>
       </c>
       <c r="B37" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5248,43 +5248,52 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524031</v>
+        <v>524123</v>
       </c>
       <c r="R37" t="n">
-        <v>6713503</v>
+        <v>6713637</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5316,7 +5325,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5326,7 +5335,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5353,7 +5362,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123414352</v>
+        <v>123412973</v>
       </c>
       <c r="B38" t="n">
         <v>98079</v>
@@ -5401,16 +5410,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524098</v>
+        <v>524116</v>
       </c>
       <c r="R38" t="n">
-        <v>6713405</v>
+        <v>6713634</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5442,7 +5456,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5452,7 +5466,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5479,7 +5493,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123412973</v>
+        <v>123412439</v>
       </c>
       <c r="B39" t="n">
         <v>98079</v>
@@ -5514,7 +5528,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5538,10 +5552,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524116</v>
+        <v>524137</v>
       </c>
       <c r="R39" t="n">
-        <v>6713634</v>
+        <v>6713646</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5573,7 +5587,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5583,7 +5597,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Inom ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5610,7 +5629,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123413119</v>
+        <v>123414352</v>
       </c>
       <c r="B40" t="n">
         <v>98079</v>
@@ -5645,12 +5664,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5658,22 +5677,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524101</v>
+        <v>524098</v>
       </c>
       <c r="R40" t="n">
-        <v>6713638</v>
+        <v>6713405</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5705,7 +5718,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5715,12 +5728,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:59</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt över ytan.</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5729,7 +5737,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5748,7 +5755,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123414270</v>
+        <v>123412326</v>
       </c>
       <c r="B41" t="n">
         <v>98079</v>
@@ -5783,7 +5790,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5802,10 +5809,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524085</v>
+        <v>524122</v>
       </c>
       <c r="R41" t="n">
-        <v>6713390</v>
+        <v>6713640</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5837,7 +5844,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5847,7 +5854,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5874,7 +5881,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123412326</v>
+        <v>123413078</v>
       </c>
       <c r="B42" t="n">
         <v>98079</v>
@@ -5909,7 +5916,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5922,16 +5929,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524122</v>
+        <v>524102</v>
       </c>
       <c r="R42" t="n">
-        <v>6713640</v>
+        <v>6713632</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5963,7 +5975,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5973,7 +5985,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6126,7 +6138,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123412439</v>
+        <v>123414270</v>
       </c>
       <c r="B44" t="n">
         <v>98079</v>
@@ -6161,7 +6173,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6174,21 +6186,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524137</v>
+        <v>524085</v>
       </c>
       <c r="R44" t="n">
-        <v>6713646</v>
+        <v>6713390</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6220,7 +6227,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6230,12 +6237,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:39</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Inom ca 5 kv/dm.</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6262,7 +6264,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123413078</v>
+        <v>123413119</v>
       </c>
       <c r="B45" t="n">
         <v>98079</v>
@@ -6297,12 +6299,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -6310,6 +6312,7 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6321,10 +6324,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524102</v>
+        <v>524101</v>
       </c>
       <c r="R45" t="n">
-        <v>6713632</v>
+        <v>6713638</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6356,7 +6359,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6366,7 +6369,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Spridda sporadiskt över ytan.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6375,6 +6383,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6393,10 +6402,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123412257</v>
+        <v>123413633</v>
       </c>
       <c r="B46" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6405,52 +6414,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524123</v>
+        <v>524031</v>
       </c>
       <c r="R46" t="n">
-        <v>6713637</v>
+        <v>6713503</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6519,7 +6519,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123526470</v>
+        <v>123527655</v>
       </c>
       <c r="B47" t="n">
         <v>98079</v>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6567,21 +6567,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524101</v>
+        <v>524041</v>
       </c>
       <c r="R47" t="n">
-        <v>6713880</v>
+        <v>6713460</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6613,7 +6608,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6623,7 +6618,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6650,7 +6645,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123528345</v>
+        <v>123527741</v>
       </c>
       <c r="B48" t="n">
         <v>98079</v>
@@ -6685,7 +6680,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6706,10 +6701,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524025</v>
+        <v>524029</v>
       </c>
       <c r="R48" t="n">
-        <v>6713476</v>
+        <v>6713459</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6741,7 +6736,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6751,12 +6746,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>En överblommad.</t>
+          <t>Sporadiskt spridda över ytan.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6784,7 +6779,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123527741</v>
+        <v>123526470</v>
       </c>
       <c r="B49" t="n">
         <v>98079</v>
@@ -6819,12 +6814,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -6832,18 +6827,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524029</v>
+        <v>524101</v>
       </c>
       <c r="R49" t="n">
-        <v>6713459</v>
+        <v>6713880</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6875,7 +6873,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6885,12 +6883,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Sporadiskt spridda över ytan.</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6899,7 +6892,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6918,10 +6910,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123527655</v>
+        <v>123528562</v>
       </c>
       <c r="B50" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6930,52 +6922,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524041</v>
+        <v>524033</v>
       </c>
       <c r="R50" t="n">
-        <v>6713460</v>
+        <v>6713503</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7007,7 +6990,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7017,7 +7000,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7044,10 +7027,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123528562</v>
+        <v>123528345</v>
       </c>
       <c r="B51" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7056,43 +7039,54 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>524033</v>
+        <v>524025</v>
       </c>
       <c r="R51" t="n">
-        <v>6713503</v>
+        <v>6713476</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7137,12 +7131,18 @@
           <t>18:41</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7161,10 +7161,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123563043</v>
+        <v>123569630</v>
       </c>
       <c r="B52" t="n">
-        <v>58169</v>
+        <v>100257</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7177,47 +7177,53 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103044</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>524035</v>
+        <v>524047</v>
       </c>
       <c r="R52" t="n">
-        <v>6713295</v>
+        <v>6713427</v>
       </c>
       <c r="S52" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7246,7 +7252,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7256,7 +7262,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Spridda över ca 15x10m.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7265,6 +7276,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7400,7 +7412,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123564906</v>
+        <v>123567823</v>
       </c>
       <c r="B54" t="n">
         <v>98079</v>
@@ -7435,7 +7447,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -7454,10 +7466,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>524050</v>
+        <v>524093</v>
       </c>
       <c r="R54" t="n">
-        <v>6713310</v>
+        <v>6713439</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7489,7 +7501,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7499,7 +7511,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7526,10 +7538,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123567823</v>
+        <v>123568589</v>
       </c>
       <c r="B55" t="n">
-        <v>98079</v>
+        <v>96957</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7538,52 +7550,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>524093</v>
+        <v>524065</v>
       </c>
       <c r="R55" t="n">
-        <v>6713439</v>
+        <v>6713431</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7615,7 +7613,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7625,7 +7623,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7652,7 +7650,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123570699</v>
+        <v>123566767</v>
       </c>
       <c r="B56" t="n">
         <v>98079</v>
@@ -7687,7 +7685,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7706,10 +7704,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>524145</v>
+        <v>524084</v>
       </c>
       <c r="R56" t="n">
-        <v>6713399</v>
+        <v>6713408</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7741,7 +7739,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7751,7 +7749,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7778,10 +7776,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123566767</v>
+        <v>123563043</v>
       </c>
       <c r="B57" t="n">
-        <v>98079</v>
+        <v>58169</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7790,55 +7788,51 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>524084</v>
+        <v>524035</v>
       </c>
       <c r="R57" t="n">
-        <v>6713408</v>
+        <v>6713295</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7867,7 +7861,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7877,7 +7871,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7904,10 +7898,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123566656</v>
+        <v>123569917</v>
       </c>
       <c r="B58" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7916,52 +7910,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>524082</v>
+        <v>524078</v>
       </c>
       <c r="R58" t="n">
-        <v>6713393</v>
+        <v>6713434</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7993,7 +7978,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8003,7 +7988,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8030,7 +8015,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123564666</v>
+        <v>123570699</v>
       </c>
       <c r="B59" t="n">
         <v>98079</v>
@@ -8065,7 +8050,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -8084,10 +8069,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>524034</v>
+        <v>524145</v>
       </c>
       <c r="R59" t="n">
-        <v>6713303</v>
+        <v>6713399</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8119,7 +8104,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8129,7 +8114,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8156,10 +8141,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123565789</v>
+        <v>123564906</v>
       </c>
       <c r="B60" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8168,38 +8153,52 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>524075</v>
+        <v>524050</v>
       </c>
       <c r="R60" t="n">
-        <v>6713354</v>
+        <v>6713310</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8231,7 +8230,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8241,7 +8240,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8268,10 +8267,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123567299</v>
+        <v>123565789</v>
       </c>
       <c r="B61" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8280,52 +8279,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>524117</v>
+        <v>524075</v>
       </c>
       <c r="R61" t="n">
-        <v>6713411</v>
+        <v>6713354</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8357,7 +8342,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8367,7 +8352,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8394,10 +8379,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123562313</v>
+        <v>123562888</v>
       </c>
       <c r="B62" t="n">
-        <v>90990</v>
+        <v>57861</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8406,38 +8391,47 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>523993</v>
+        <v>524019</v>
       </c>
       <c r="R62" t="n">
-        <v>6713299</v>
+        <v>6713291</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8469,7 +8463,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8479,7 +8473,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8506,10 +8500,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123562888</v>
+        <v>123571398</v>
       </c>
       <c r="B63" t="n">
-        <v>57861</v>
+        <v>90990</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8518,47 +8512,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>524019</v>
+        <v>524112</v>
       </c>
       <c r="R63" t="n">
-        <v>6713291</v>
+        <v>6713375</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8590,7 +8575,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8600,7 +8585,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8627,10 +8612,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123572491</v>
+        <v>123567299</v>
       </c>
       <c r="B64" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8639,38 +8624,52 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>523993</v>
+        <v>524117</v>
       </c>
       <c r="R64" t="n">
-        <v>6713281</v>
+        <v>6713411</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8702,7 +8701,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8712,7 +8711,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8739,7 +8738,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123571398</v>
+        <v>123572491</v>
       </c>
       <c r="B65" t="n">
         <v>90990</v>
@@ -8779,10 +8778,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>524112</v>
+        <v>523993</v>
       </c>
       <c r="R65" t="n">
-        <v>6713375</v>
+        <v>6713281</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8814,7 +8813,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8824,7 +8823,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8851,10 +8850,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123569630</v>
+        <v>123562313</v>
       </c>
       <c r="B66" t="n">
-        <v>100257</v>
+        <v>90990</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8863,54 +8862,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>524047</v>
+        <v>523993</v>
       </c>
       <c r="R66" t="n">
-        <v>6713427</v>
+        <v>6713299</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8942,7 +8925,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8952,12 +8935,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Spridda över ca 15x10m.</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8966,7 +8944,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -8985,10 +8962,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123568589</v>
+        <v>123568031</v>
       </c>
       <c r="B67" t="n">
-        <v>96957</v>
+        <v>58169</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9001,34 +8978,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221945</v>
+        <v>103044</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>524065</v>
+        <v>524094</v>
       </c>
       <c r="R67" t="n">
-        <v>6713431</v>
+        <v>6713439</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9060,7 +9042,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9070,7 +9052,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9097,10 +9079,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123568031</v>
+        <v>123564666</v>
       </c>
       <c r="B68" t="n">
-        <v>58169</v>
+        <v>98079</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9109,43 +9091,52 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>524094</v>
+        <v>524034</v>
       </c>
       <c r="R68" t="n">
-        <v>6713439</v>
+        <v>6713303</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9177,7 +9168,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9187,7 +9178,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9214,10 +9205,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123569917</v>
+        <v>123566656</v>
       </c>
       <c r="B69" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9226,43 +9217,52 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>524078</v>
+        <v>524082</v>
       </c>
       <c r="R69" t="n">
-        <v>6713434</v>
+        <v>6713393</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9294,7 +9294,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9331,10 +9331,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123761045</v>
+        <v>123760786</v>
       </c>
       <c r="B70" t="n">
-        <v>8447</v>
+        <v>98079</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9343,31 +9343,40 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -9376,10 +9385,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523984</v>
+        <v>523969</v>
       </c>
       <c r="R70" t="n">
-        <v>6713796</v>
+        <v>6713750</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9411,7 +9420,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9421,7 +9430,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9448,10 +9457,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123761091</v>
+        <v>123761045</v>
       </c>
       <c r="B71" t="n">
-        <v>98079</v>
+        <v>8447</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9460,40 +9469,31 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -9502,10 +9502,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523962</v>
+        <v>523984</v>
       </c>
       <c r="R71" t="n">
-        <v>6713819</v>
+        <v>6713796</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9537,7 +9537,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9574,7 +9574,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123760786</v>
+        <v>123761091</v>
       </c>
       <c r="B72" t="n">
         <v>98079</v>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9628,10 +9628,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523969</v>
+        <v>523962</v>
       </c>
       <c r="R72" t="n">
-        <v>6713750</v>
+        <v>6713819</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9700,7 +9700,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123769072</v>
+        <v>123768989</v>
       </c>
       <c r="B73" t="n">
         <v>100257</v>
@@ -9733,31 +9733,22 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>524031</v>
+        <v>524017</v>
       </c>
       <c r="R73" t="n">
-        <v>6713998</v>
+        <v>6713958</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9789,7 +9780,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9799,7 +9790,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9826,7 +9817,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123768976</v>
+        <v>123768932</v>
       </c>
       <c r="B74" t="n">
         <v>100257</v>
@@ -9859,7 +9850,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -9871,10 +9871,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>524011</v>
+        <v>524000</v>
       </c>
       <c r="R74" t="n">
-        <v>6713981</v>
+        <v>6713968</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9943,7 +9943,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123769093</v>
+        <v>123768995</v>
       </c>
       <c r="B75" t="n">
         <v>100257</v>
@@ -9976,16 +9976,7 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -9997,10 +9988,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>524033</v>
+        <v>524011</v>
       </c>
       <c r="R75" t="n">
-        <v>6713983</v>
+        <v>6713982</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10032,7 +10023,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10042,7 +10033,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10069,7 +10060,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123769023</v>
+        <v>123769072</v>
       </c>
       <c r="B76" t="n">
         <v>100257</v>
@@ -10102,22 +10093,31 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>524017</v>
+        <v>524031</v>
       </c>
       <c r="R76" t="n">
-        <v>6713986</v>
+        <v>6713998</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10159,7 +10159,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10186,7 +10186,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123768932</v>
+        <v>123768976</v>
       </c>
       <c r="B77" t="n">
         <v>100257</v>
@@ -10219,16 +10219,7 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -10240,10 +10231,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>524000</v>
+        <v>524011</v>
       </c>
       <c r="R77" t="n">
-        <v>6713968</v>
+        <v>6713981</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10275,7 +10266,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10285,7 +10276,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10312,7 +10303,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123768995</v>
+        <v>123769126</v>
       </c>
       <c r="B78" t="n">
         <v>100257</v>
@@ -10357,10 +10348,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>524011</v>
+        <v>524017</v>
       </c>
       <c r="R78" t="n">
-        <v>6713982</v>
+        <v>6713977</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10392,7 +10383,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10402,7 +10393,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10429,7 +10420,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123769126</v>
+        <v>123769023</v>
       </c>
       <c r="B79" t="n">
         <v>100257</v>
@@ -10477,7 +10468,7 @@
         <v>524017</v>
       </c>
       <c r="R79" t="n">
-        <v>6713977</v>
+        <v>6713986</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10509,7 +10500,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10519,7 +10510,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10546,7 +10537,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123768989</v>
+        <v>123769093</v>
       </c>
       <c r="B80" t="n">
         <v>100257</v>
@@ -10579,7 +10570,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -10591,10 +10591,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>524017</v>
+        <v>524033</v>
       </c>
       <c r="R80" t="n">
-        <v>6713958</v>
+        <v>6713983</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10636,7 +10636,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD80" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -4984,7 +4984,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123412367</v>
+        <v>123412257</v>
       </c>
       <c r="B35" t="n">
         <v>98079</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5034,14 +5034,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524136</v>
+        <v>524123</v>
       </c>
       <c r="R35" t="n">
-        <v>6713648</v>
+        <v>6713637</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5110,7 +5110,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123413856</v>
+        <v>123414270</v>
       </c>
       <c r="B36" t="n">
         <v>98079</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5164,10 +5164,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524041</v>
+        <v>524085</v>
       </c>
       <c r="R36" t="n">
-        <v>6713443</v>
+        <v>6713390</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5236,7 +5236,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123412257</v>
+        <v>123412326</v>
       </c>
       <c r="B37" t="n">
         <v>98079</v>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5290,10 +5290,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524123</v>
+        <v>524122</v>
       </c>
       <c r="R37" t="n">
-        <v>6713637</v>
+        <v>6713640</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5362,7 +5362,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123412973</v>
+        <v>123413119</v>
       </c>
       <c r="B38" t="n">
         <v>98079</v>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5410,6 +5410,7 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5417,14 +5418,14 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524116</v>
+        <v>524101</v>
       </c>
       <c r="R38" t="n">
-        <v>6713634</v>
+        <v>6713638</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5456,7 +5457,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5466,7 +5467,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Spridda sporadiskt över ytan.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5475,6 +5481,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5493,7 +5500,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123412439</v>
+        <v>123412367</v>
       </c>
       <c r="B39" t="n">
         <v>98079</v>
@@ -5528,7 +5535,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5541,21 +5548,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524137</v>
+        <v>524136</v>
       </c>
       <c r="R39" t="n">
-        <v>6713646</v>
+        <v>6713648</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5587,7 +5589,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5597,12 +5599,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:39</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Inom ca 5 kv/dm.</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5629,7 +5626,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123414352</v>
+        <v>123412439</v>
       </c>
       <c r="B40" t="n">
         <v>98079</v>
@@ -5664,7 +5661,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5677,16 +5674,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524098</v>
+        <v>524137</v>
       </c>
       <c r="R40" t="n">
-        <v>6713405</v>
+        <v>6713646</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5718,7 +5720,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5728,7 +5730,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Inom ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5755,7 +5762,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123412326</v>
+        <v>123412973</v>
       </c>
       <c r="B41" t="n">
         <v>98079</v>
@@ -5790,7 +5797,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5803,16 +5810,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524122</v>
+        <v>524116</v>
       </c>
       <c r="R41" t="n">
-        <v>6713640</v>
+        <v>6713634</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5844,7 +5856,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5854,7 +5866,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6138,7 +6150,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123414270</v>
+        <v>123413856</v>
       </c>
       <c r="B44" t="n">
         <v>98079</v>
@@ -6173,7 +6185,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6192,10 +6204,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524085</v>
+        <v>524041</v>
       </c>
       <c r="R44" t="n">
-        <v>6713390</v>
+        <v>6713443</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6227,7 +6239,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6237,7 +6249,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6264,10 +6276,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123413119</v>
+        <v>123413633</v>
       </c>
       <c r="B45" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6276,58 +6288,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524101</v>
+        <v>524031</v>
       </c>
       <c r="R45" t="n">
-        <v>6713638</v>
+        <v>6713503</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6359,7 +6356,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6369,12 +6366,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:59</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt över ytan.</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6383,7 +6375,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6402,10 +6393,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123413633</v>
+        <v>123414352</v>
       </c>
       <c r="B46" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6414,43 +6405,52 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524031</v>
+        <v>524098</v>
       </c>
       <c r="R46" t="n">
-        <v>6713503</v>
+        <v>6713405</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6519,7 +6519,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123527655</v>
+        <v>123527741</v>
       </c>
       <c r="B47" t="n">
         <v>98079</v>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -6567,16 +6567,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524041</v>
+        <v>524029</v>
       </c>
       <c r="R47" t="n">
-        <v>6713460</v>
+        <v>6713459</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6608,7 +6610,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6618,7 +6620,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Sporadiskt spridda över ytan.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6627,6 +6634,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6645,10 +6653,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123527741</v>
+        <v>123528562</v>
       </c>
       <c r="B48" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6657,54 +6665,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524029</v>
+        <v>524033</v>
       </c>
       <c r="R48" t="n">
-        <v>6713459</v>
+        <v>6713503</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6736,7 +6733,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6746,12 +6743,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Sporadiskt spridda över ytan.</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6760,7 +6752,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6779,7 +6770,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123526470</v>
+        <v>123527655</v>
       </c>
       <c r="B49" t="n">
         <v>98079</v>
@@ -6814,7 +6805,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6827,21 +6818,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524101</v>
+        <v>524041</v>
       </c>
       <c r="R49" t="n">
-        <v>6713880</v>
+        <v>6713460</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6873,7 +6859,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6883,7 +6869,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6910,10 +6896,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123528562</v>
+        <v>123528345</v>
       </c>
       <c r="B50" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6922,43 +6908,54 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524033</v>
+        <v>524025</v>
       </c>
       <c r="R50" t="n">
-        <v>6713503</v>
+        <v>6713476</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7003,12 +7000,18 @@
           <t>18:41</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -7027,7 +7030,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123528345</v>
+        <v>123526470</v>
       </c>
       <c r="B51" t="n">
         <v>98079</v>
@@ -7062,12 +7065,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -7075,18 +7078,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>524025</v>
+        <v>524101</v>
       </c>
       <c r="R51" t="n">
-        <v>6713476</v>
+        <v>6713880</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7118,7 +7124,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7128,12 +7134,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:41</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7142,7 +7143,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7295,10 +7295,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123569808</v>
+        <v>123566656</v>
       </c>
       <c r="B53" t="n">
-        <v>96957</v>
+        <v>98079</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7307,31 +7307,40 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -7340,10 +7349,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>524077</v>
+        <v>524082</v>
       </c>
       <c r="R53" t="n">
-        <v>6713436</v>
+        <v>6713393</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7375,7 +7384,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7385,7 +7394,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7538,10 +7547,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123568589</v>
+        <v>123562313</v>
       </c>
       <c r="B55" t="n">
-        <v>96957</v>
+        <v>90990</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7550,25 +7559,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7578,10 +7587,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>524065</v>
+        <v>523993</v>
       </c>
       <c r="R55" t="n">
-        <v>6713431</v>
+        <v>6713299</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7613,7 +7622,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7623,7 +7632,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7650,7 +7659,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123566767</v>
+        <v>123567299</v>
       </c>
       <c r="B56" t="n">
         <v>98079</v>
@@ -7685,7 +7694,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7704,10 +7713,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>524084</v>
+        <v>524117</v>
       </c>
       <c r="R56" t="n">
-        <v>6713408</v>
+        <v>6713411</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7739,7 +7748,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7749,7 +7758,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7776,10 +7785,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123563043</v>
+        <v>123568589</v>
       </c>
       <c r="B57" t="n">
-        <v>58169</v>
+        <v>96957</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7792,47 +7801,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103044</v>
+        <v>221945</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>524035</v>
+        <v>524065</v>
       </c>
       <c r="R57" t="n">
-        <v>6713295</v>
+        <v>6713431</v>
       </c>
       <c r="S57" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7861,7 +7860,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7871,7 +7870,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7898,10 +7897,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123569917</v>
+        <v>123572491</v>
       </c>
       <c r="B58" t="n">
-        <v>57507</v>
+        <v>90990</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7914,39 +7913,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>524078</v>
+        <v>523993</v>
       </c>
       <c r="R58" t="n">
-        <v>6713434</v>
+        <v>6713281</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7978,7 +7972,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7988,7 +7982,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8015,7 +8009,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123570699</v>
+        <v>123564666</v>
       </c>
       <c r="B59" t="n">
         <v>98079</v>
@@ -8050,7 +8044,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -8069,10 +8063,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>524145</v>
+        <v>524034</v>
       </c>
       <c r="R59" t="n">
-        <v>6713399</v>
+        <v>6713303</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8104,7 +8098,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8114,7 +8108,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8141,10 +8135,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123564906</v>
+        <v>123571398</v>
       </c>
       <c r="B60" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8153,52 +8147,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>524050</v>
+        <v>524112</v>
       </c>
       <c r="R60" t="n">
-        <v>6713310</v>
+        <v>6713375</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8230,7 +8210,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8240,7 +8220,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8267,10 +8247,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123565789</v>
+        <v>123563043</v>
       </c>
       <c r="B61" t="n">
-        <v>90990</v>
+        <v>58169</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8279,41 +8259,51 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>103044</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>524075</v>
+        <v>524035</v>
       </c>
       <c r="R61" t="n">
-        <v>6713354</v>
+        <v>6713295</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8342,7 +8332,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8352,7 +8342,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8379,10 +8369,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123562888</v>
+        <v>123568031</v>
       </c>
       <c r="B62" t="n">
-        <v>57861</v>
+        <v>58169</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8395,16 +8385,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -8412,14 +8402,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -8428,10 +8414,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>524019</v>
+        <v>524094</v>
       </c>
       <c r="R62" t="n">
-        <v>6713291</v>
+        <v>6713439</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8463,7 +8449,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8473,7 +8459,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8500,10 +8486,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123571398</v>
+        <v>123569808</v>
       </c>
       <c r="B63" t="n">
-        <v>90990</v>
+        <v>96957</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8512,38 +8498,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>524112</v>
+        <v>524077</v>
       </c>
       <c r="R63" t="n">
-        <v>6713375</v>
+        <v>6713436</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8575,7 +8566,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8585,7 +8576,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8612,10 +8603,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123567299</v>
+        <v>123565789</v>
       </c>
       <c r="B64" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8624,52 +8615,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524117</v>
+        <v>524075</v>
       </c>
       <c r="R64" t="n">
-        <v>6713411</v>
+        <v>6713354</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8701,7 +8678,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8711,7 +8688,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8738,10 +8715,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123572491</v>
+        <v>123564906</v>
       </c>
       <c r="B65" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8750,38 +8727,52 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>523993</v>
+        <v>524050</v>
       </c>
       <c r="R65" t="n">
-        <v>6713281</v>
+        <v>6713310</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8813,7 +8804,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8823,7 +8814,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8850,10 +8841,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123562313</v>
+        <v>123569917</v>
       </c>
       <c r="B66" t="n">
-        <v>90990</v>
+        <v>57507</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8866,34 +8857,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>523993</v>
+        <v>524078</v>
       </c>
       <c r="R66" t="n">
-        <v>6713299</v>
+        <v>6713434</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8925,7 +8921,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8935,7 +8931,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8962,10 +8958,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123568031</v>
+        <v>123562888</v>
       </c>
       <c r="B67" t="n">
-        <v>58169</v>
+        <v>57861</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8978,16 +8974,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -8995,10 +8991,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -9007,10 +9007,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>524094</v>
+        <v>524019</v>
       </c>
       <c r="R67" t="n">
-        <v>6713439</v>
+        <v>6713291</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9079,7 +9079,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123564666</v>
+        <v>123566767</v>
       </c>
       <c r="B68" t="n">
         <v>98079</v>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -9133,10 +9133,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>524034</v>
+        <v>524084</v>
       </c>
       <c r="R68" t="n">
-        <v>6713303</v>
+        <v>6713408</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9178,7 +9178,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9205,7 +9205,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123566656</v>
+        <v>123570699</v>
       </c>
       <c r="B69" t="n">
         <v>98079</v>
@@ -9240,7 +9240,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9259,10 +9259,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>524082</v>
+        <v>524145</v>
       </c>
       <c r="R69" t="n">
-        <v>6713393</v>
+        <v>6713399</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9294,7 +9294,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9700,7 +9700,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123768989</v>
+        <v>123768932</v>
       </c>
       <c r="B73" t="n">
         <v>100257</v>
@@ -9733,7 +9733,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -9745,10 +9754,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>524017</v>
+        <v>524000</v>
       </c>
       <c r="R73" t="n">
-        <v>6713958</v>
+        <v>6713968</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9780,7 +9789,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9790,7 +9799,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9817,7 +9826,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123768932</v>
+        <v>123769023</v>
       </c>
       <c r="B74" t="n">
         <v>100257</v>
@@ -9850,16 +9859,7 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -9871,10 +9871,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>524000</v>
+        <v>524017</v>
       </c>
       <c r="R74" t="n">
-        <v>6713968</v>
+        <v>6713986</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10060,7 +10060,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123769072</v>
+        <v>123768989</v>
       </c>
       <c r="B76" t="n">
         <v>100257</v>
@@ -10093,31 +10093,22 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>524031</v>
+        <v>524017</v>
       </c>
       <c r="R76" t="n">
-        <v>6713998</v>
+        <v>6713958</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10149,7 +10140,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10159,7 +10150,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10303,7 +10294,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123769126</v>
+        <v>123769093</v>
       </c>
       <c r="B78" t="n">
         <v>100257</v>
@@ -10336,7 +10327,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -10348,10 +10348,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>524017</v>
+        <v>524033</v>
       </c>
       <c r="R78" t="n">
-        <v>6713977</v>
+        <v>6713983</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10383,7 +10383,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10420,7 +10420,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123769023</v>
+        <v>123769126</v>
       </c>
       <c r="B79" t="n">
         <v>100257</v>
@@ -10468,7 +10468,7 @@
         <v>524017</v>
       </c>
       <c r="R79" t="n">
-        <v>6713986</v>
+        <v>6713977</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10537,7 +10537,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123769093</v>
+        <v>123769072</v>
       </c>
       <c r="B80" t="n">
         <v>100257</v>
@@ -10572,29 +10572,29 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>524033</v>
+        <v>524031</v>
       </c>
       <c r="R80" t="n">
-        <v>6713983</v>
+        <v>6713998</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10636,7 +10636,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD80" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -4984,7 +4984,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123412257</v>
+        <v>123413119</v>
       </c>
       <c r="B35" t="n">
         <v>98079</v>
@@ -5019,12 +5019,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -5032,16 +5032,22 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524123</v>
+        <v>524101</v>
       </c>
       <c r="R35" t="n">
-        <v>6713637</v>
+        <v>6713638</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5073,7 +5079,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5083,7 +5089,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spridda sporadiskt över ytan.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5092,6 +5103,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5110,7 +5122,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123414270</v>
+        <v>123412326</v>
       </c>
       <c r="B36" t="n">
         <v>98079</v>
@@ -5145,7 +5157,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5164,10 +5176,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524085</v>
+        <v>524122</v>
       </c>
       <c r="R36" t="n">
-        <v>6713390</v>
+        <v>6713640</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5199,7 +5211,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5209,7 +5221,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5236,7 +5248,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123412326</v>
+        <v>123413078</v>
       </c>
       <c r="B37" t="n">
         <v>98079</v>
@@ -5271,7 +5283,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5284,16 +5296,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524122</v>
+        <v>524102</v>
       </c>
       <c r="R37" t="n">
-        <v>6713640</v>
+        <v>6713632</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5325,7 +5342,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5335,7 +5352,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5362,7 +5379,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123413119</v>
+        <v>123414270</v>
       </c>
       <c r="B38" t="n">
         <v>98079</v>
@@ -5397,12 +5414,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5410,22 +5427,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524101</v>
+        <v>524085</v>
       </c>
       <c r="R38" t="n">
-        <v>6713638</v>
+        <v>6713390</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5457,7 +5468,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5467,12 +5478,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:59</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt över ytan.</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5481,7 +5487,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5500,7 +5505,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123412367</v>
+        <v>123412973</v>
       </c>
       <c r="B39" t="n">
         <v>98079</v>
@@ -5535,7 +5540,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5548,16 +5553,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524136</v>
+        <v>524116</v>
       </c>
       <c r="R39" t="n">
-        <v>6713648</v>
+        <v>6713634</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5589,7 +5599,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5599,7 +5609,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5626,7 +5636,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123412439</v>
+        <v>123412367</v>
       </c>
       <c r="B40" t="n">
         <v>98079</v>
@@ -5661,7 +5671,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5674,21 +5684,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524137</v>
+        <v>524136</v>
       </c>
       <c r="R40" t="n">
-        <v>6713646</v>
+        <v>6713648</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5720,7 +5725,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5730,12 +5735,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:39</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Inom ca 5 kv/dm.</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5762,7 +5762,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123412973</v>
+        <v>123413856</v>
       </c>
       <c r="B41" t="n">
         <v>98079</v>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5810,21 +5810,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524116</v>
+        <v>524041</v>
       </c>
       <c r="R41" t="n">
-        <v>6713634</v>
+        <v>6713443</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5856,7 +5851,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5866,7 +5861,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5893,7 +5888,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123413078</v>
+        <v>123413726</v>
       </c>
       <c r="B42" t="n">
         <v>98079</v>
@@ -5928,7 +5923,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5941,21 +5936,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524102</v>
+        <v>524030</v>
       </c>
       <c r="R42" t="n">
-        <v>6713632</v>
+        <v>6713469</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5987,7 +5977,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5997,7 +5987,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6024,7 +6014,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123413726</v>
+        <v>123412439</v>
       </c>
       <c r="B43" t="n">
         <v>98079</v>
@@ -6059,7 +6049,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6072,16 +6062,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524030</v>
+        <v>524137</v>
       </c>
       <c r="R43" t="n">
-        <v>6713469</v>
+        <v>6713646</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6113,7 +6108,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6123,7 +6118,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Inom ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6150,10 +6150,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123413856</v>
+        <v>123413633</v>
       </c>
       <c r="B44" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6162,52 +6162,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524041</v>
+        <v>524031</v>
       </c>
       <c r="R44" t="n">
-        <v>6713443</v>
+        <v>6713503</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6239,7 +6230,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6249,7 +6240,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6276,10 +6267,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123413633</v>
+        <v>123414352</v>
       </c>
       <c r="B45" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6288,43 +6279,52 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524031</v>
+        <v>524098</v>
       </c>
       <c r="R45" t="n">
-        <v>6713503</v>
+        <v>6713405</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6393,7 +6393,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123414352</v>
+        <v>123412257</v>
       </c>
       <c r="B46" t="n">
         <v>98079</v>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6447,10 +6447,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524098</v>
+        <v>524123</v>
       </c>
       <c r="R46" t="n">
-        <v>6713405</v>
+        <v>6713637</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6519,10 +6519,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123527741</v>
+        <v>123528562</v>
       </c>
       <c r="B47" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6531,54 +6531,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524029</v>
+        <v>524033</v>
       </c>
       <c r="R47" t="n">
-        <v>6713459</v>
+        <v>6713503</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6610,7 +6599,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6620,12 +6609,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Sporadiskt spridda över ytan.</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6634,7 +6618,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6653,10 +6636,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123528562</v>
+        <v>123526470</v>
       </c>
       <c r="B48" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6665,43 +6648,57 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524033</v>
+        <v>524101</v>
       </c>
       <c r="R48" t="n">
-        <v>6713503</v>
+        <v>6713880</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6733,7 +6730,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6743,7 +6740,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6770,7 +6767,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123527655</v>
+        <v>123527741</v>
       </c>
       <c r="B49" t="n">
         <v>98079</v>
@@ -6805,12 +6802,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -6818,16 +6815,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524041</v>
+        <v>524029</v>
       </c>
       <c r="R49" t="n">
-        <v>6713460</v>
+        <v>6713459</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6859,7 +6858,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6869,7 +6868,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Sporadiskt spridda över ytan.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6878,6 +6882,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -7030,7 +7035,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123526470</v>
+        <v>123527655</v>
       </c>
       <c r="B51" t="n">
         <v>98079</v>
@@ -7065,7 +7070,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7078,21 +7083,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>524101</v>
+        <v>524041</v>
       </c>
       <c r="R51" t="n">
-        <v>6713880</v>
+        <v>6713460</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7161,10 +7161,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123569630</v>
+        <v>123572491</v>
       </c>
       <c r="B52" t="n">
-        <v>100257</v>
+        <v>90990</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7173,54 +7173,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>524047</v>
+        <v>523993</v>
       </c>
       <c r="R52" t="n">
-        <v>6713427</v>
+        <v>6713281</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7252,7 +7236,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7262,12 +7246,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Spridda över ca 15x10m.</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7276,7 +7255,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7295,7 +7273,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123566656</v>
+        <v>123564666</v>
       </c>
       <c r="B53" t="n">
         <v>98079</v>
@@ -7349,10 +7327,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>524082</v>
+        <v>524034</v>
       </c>
       <c r="R53" t="n">
-        <v>6713393</v>
+        <v>6713303</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7384,7 +7362,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7394,7 +7372,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7421,10 +7399,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123567823</v>
+        <v>123569808</v>
       </c>
       <c r="B54" t="n">
-        <v>98079</v>
+        <v>96957</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7433,40 +7411,31 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -7475,10 +7444,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>524093</v>
+        <v>524077</v>
       </c>
       <c r="R54" t="n">
-        <v>6713439</v>
+        <v>6713436</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7510,7 +7479,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7520,7 +7489,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7547,10 +7516,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123562313</v>
+        <v>123568589</v>
       </c>
       <c r="B55" t="n">
-        <v>90990</v>
+        <v>96957</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7559,25 +7528,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7587,10 +7556,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>523993</v>
+        <v>524065</v>
       </c>
       <c r="R55" t="n">
-        <v>6713299</v>
+        <v>6713431</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7622,7 +7591,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7632,7 +7601,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7659,10 +7628,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123567299</v>
+        <v>123563043</v>
       </c>
       <c r="B56" t="n">
-        <v>98079</v>
+        <v>58169</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7671,55 +7640,51 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>524117</v>
+        <v>524035</v>
       </c>
       <c r="R56" t="n">
-        <v>6713411</v>
+        <v>6713295</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7748,7 +7713,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7758,7 +7723,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7785,10 +7750,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123568589</v>
+        <v>123567299</v>
       </c>
       <c r="B57" t="n">
-        <v>96957</v>
+        <v>98079</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7797,38 +7762,52 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>524065</v>
+        <v>524117</v>
       </c>
       <c r="R57" t="n">
-        <v>6713431</v>
+        <v>6713411</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7860,7 +7839,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7870,7 +7849,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7897,10 +7876,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123572491</v>
+        <v>123568031</v>
       </c>
       <c r="B58" t="n">
-        <v>90990</v>
+        <v>58169</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7909,38 +7888,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>103044</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>523993</v>
+        <v>524094</v>
       </c>
       <c r="R58" t="n">
-        <v>6713281</v>
+        <v>6713439</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7972,7 +7956,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7982,7 +7966,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8009,10 +7993,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123564666</v>
+        <v>123562313</v>
       </c>
       <c r="B59" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8021,52 +8005,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>524034</v>
+        <v>523993</v>
       </c>
       <c r="R59" t="n">
-        <v>6713303</v>
+        <v>6713299</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8098,7 +8068,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8108,7 +8078,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8135,10 +8105,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123571398</v>
+        <v>123566656</v>
       </c>
       <c r="B60" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8147,38 +8117,52 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>524112</v>
+        <v>524082</v>
       </c>
       <c r="R60" t="n">
-        <v>6713375</v>
+        <v>6713393</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8210,7 +8194,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8220,7 +8204,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8247,10 +8231,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123563043</v>
+        <v>123564906</v>
       </c>
       <c r="B61" t="n">
-        <v>58169</v>
+        <v>98079</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8259,51 +8243,55 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>524035</v>
+        <v>524050</v>
       </c>
       <c r="R61" t="n">
-        <v>6713295</v>
+        <v>6713310</v>
       </c>
       <c r="S61" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8332,7 +8320,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8342,7 +8330,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8369,10 +8357,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123568031</v>
+        <v>123571398</v>
       </c>
       <c r="B62" t="n">
-        <v>58169</v>
+        <v>90990</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8381,43 +8369,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103044</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>524094</v>
+        <v>524112</v>
       </c>
       <c r="R62" t="n">
-        <v>6713439</v>
+        <v>6713375</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8449,7 +8432,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8459,7 +8442,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8486,10 +8469,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123569808</v>
+        <v>123562888</v>
       </c>
       <c r="B63" t="n">
-        <v>96957</v>
+        <v>57861</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8502,39 +8485,43 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>524077</v>
+        <v>524019</v>
       </c>
       <c r="R63" t="n">
-        <v>6713436</v>
+        <v>6713291</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8566,7 +8553,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8576,7 +8563,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8603,10 +8590,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123565789</v>
+        <v>123570699</v>
       </c>
       <c r="B64" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8615,38 +8602,52 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524075</v>
+        <v>524145</v>
       </c>
       <c r="R64" t="n">
-        <v>6713354</v>
+        <v>6713399</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8678,7 +8679,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8688,7 +8689,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8715,7 +8716,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123564906</v>
+        <v>123567823</v>
       </c>
       <c r="B65" t="n">
         <v>98079</v>
@@ -8750,7 +8751,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8769,10 +8770,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>524050</v>
+        <v>524093</v>
       </c>
       <c r="R65" t="n">
-        <v>6713310</v>
+        <v>6713439</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8804,7 +8805,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8814,7 +8815,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8841,10 +8842,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123569917</v>
+        <v>123566767</v>
       </c>
       <c r="B66" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8853,43 +8854,52 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>524078</v>
+        <v>524084</v>
       </c>
       <c r="R66" t="n">
-        <v>6713434</v>
+        <v>6713408</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8921,7 +8931,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8931,7 +8941,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8958,10 +8968,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123562888</v>
+        <v>123569917</v>
       </c>
       <c r="B67" t="n">
-        <v>57861</v>
+        <v>57507</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8970,20 +8980,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -8991,14 +9001,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -9007,10 +9013,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>524019</v>
+        <v>524078</v>
       </c>
       <c r="R67" t="n">
-        <v>6713291</v>
+        <v>6713434</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9042,7 +9048,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9052,7 +9058,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9079,10 +9085,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123566767</v>
+        <v>123565789</v>
       </c>
       <c r="B68" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9091,52 +9097,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>524084</v>
+        <v>524075</v>
       </c>
       <c r="R68" t="n">
-        <v>6713408</v>
+        <v>6713354</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9168,7 +9160,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9178,7 +9170,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9205,10 +9197,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123570699</v>
+        <v>123569630</v>
       </c>
       <c r="B69" t="n">
-        <v>98079</v>
+        <v>100257</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9217,40 +9209,42 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -9259,10 +9253,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>524145</v>
+        <v>524047</v>
       </c>
       <c r="R69" t="n">
-        <v>6713399</v>
+        <v>6713427</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9294,7 +9288,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9304,7 +9298,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Spridda över ca 15x10m.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9313,6 +9312,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -9331,7 +9331,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123760786</v>
+        <v>123761091</v>
       </c>
       <c r="B70" t="n">
         <v>98079</v>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9385,10 +9385,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523969</v>
+        <v>523962</v>
       </c>
       <c r="R70" t="n">
-        <v>6713750</v>
+        <v>6713819</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9420,7 +9420,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9457,10 +9457,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123761045</v>
+        <v>123760786</v>
       </c>
       <c r="B71" t="n">
-        <v>8447</v>
+        <v>98079</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9469,31 +9469,40 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -9502,10 +9511,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523984</v>
+        <v>523969</v>
       </c>
       <c r="R71" t="n">
-        <v>6713796</v>
+        <v>6713750</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9537,7 +9546,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9547,7 +9556,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9574,10 +9583,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123761091</v>
+        <v>123761045</v>
       </c>
       <c r="B72" t="n">
-        <v>98079</v>
+        <v>8447</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9586,40 +9595,31 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -9628,10 +9628,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523962</v>
+        <v>523984</v>
       </c>
       <c r="R72" t="n">
-        <v>6713819</v>
+        <v>6713796</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9700,7 +9700,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123768932</v>
+        <v>123768995</v>
       </c>
       <c r="B73" t="n">
         <v>100257</v>
@@ -9733,16 +9733,7 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -9754,10 +9745,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>524000</v>
+        <v>524011</v>
       </c>
       <c r="R73" t="n">
-        <v>6713968</v>
+        <v>6713982</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9789,7 +9780,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9799,7 +9790,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9826,7 +9817,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123769023</v>
+        <v>123768976</v>
       </c>
       <c r="B74" t="n">
         <v>100257</v>
@@ -9871,10 +9862,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>524017</v>
+        <v>524011</v>
       </c>
       <c r="R74" t="n">
-        <v>6713986</v>
+        <v>6713981</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9906,7 +9897,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9916,7 +9907,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9943,7 +9934,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123768995</v>
+        <v>123768989</v>
       </c>
       <c r="B75" t="n">
         <v>100257</v>
@@ -9988,10 +9979,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>524011</v>
+        <v>524017</v>
       </c>
       <c r="R75" t="n">
-        <v>6713982</v>
+        <v>6713958</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10023,7 +10014,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10033,7 +10024,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10060,7 +10051,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123768989</v>
+        <v>123768932</v>
       </c>
       <c r="B76" t="n">
         <v>100257</v>
@@ -10093,7 +10084,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -10105,10 +10105,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>524017</v>
+        <v>524000</v>
       </c>
       <c r="R76" t="n">
-        <v>6713958</v>
+        <v>6713968</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10140,7 +10140,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10177,7 +10177,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123768976</v>
+        <v>123769093</v>
       </c>
       <c r="B77" t="n">
         <v>100257</v>
@@ -10210,7 +10210,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -10222,10 +10231,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>524011</v>
+        <v>524033</v>
       </c>
       <c r="R77" t="n">
-        <v>6713981</v>
+        <v>6713983</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10257,7 +10266,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10267,7 +10276,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10294,7 +10303,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123769093</v>
+        <v>123769072</v>
       </c>
       <c r="B78" t="n">
         <v>100257</v>
@@ -10329,29 +10338,29 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>524033</v>
+        <v>524031</v>
       </c>
       <c r="R78" t="n">
-        <v>6713983</v>
+        <v>6713998</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10383,7 +10392,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10393,7 +10402,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10420,7 +10429,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123769126</v>
+        <v>123769023</v>
       </c>
       <c r="B79" t="n">
         <v>100257</v>
@@ -10468,7 +10477,7 @@
         <v>524017</v>
       </c>
       <c r="R79" t="n">
-        <v>6713977</v>
+        <v>6713986</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10500,7 +10509,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10510,7 +10519,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10537,7 +10546,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123769072</v>
+        <v>123769126</v>
       </c>
       <c r="B80" t="n">
         <v>100257</v>
@@ -10570,31 +10579,22 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>524031</v>
+        <v>524017</v>
       </c>
       <c r="R80" t="n">
-        <v>6713998</v>
+        <v>6713977</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10636,7 +10636,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD80" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -7161,10 +7161,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123572491</v>
+        <v>123564666</v>
       </c>
       <c r="B52" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7173,38 +7173,52 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523993</v>
+        <v>524034</v>
       </c>
       <c r="R52" t="n">
-        <v>6713281</v>
+        <v>6713303</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7236,7 +7250,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7246,7 +7260,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7273,10 +7287,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123564666</v>
+        <v>123572491</v>
       </c>
       <c r="B53" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7285,52 +7299,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>524034</v>
+        <v>523993</v>
       </c>
       <c r="R53" t="n">
-        <v>6713303</v>
+        <v>6713281</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7362,7 +7362,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7876,10 +7876,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123568031</v>
+        <v>123562313</v>
       </c>
       <c r="B58" t="n">
-        <v>58169</v>
+        <v>90990</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7888,43 +7888,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103044</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>524094</v>
+        <v>523993</v>
       </c>
       <c r="R58" t="n">
-        <v>6713439</v>
+        <v>6713299</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7956,7 +7951,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7966,7 +7961,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7993,10 +7988,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123562313</v>
+        <v>123568031</v>
       </c>
       <c r="B59" t="n">
-        <v>90990</v>
+        <v>58169</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8005,38 +8000,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>103044</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523993</v>
+        <v>524094</v>
       </c>
       <c r="R59" t="n">
-        <v>6713299</v>
+        <v>6713439</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8357,10 +8357,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123571398</v>
+        <v>123562888</v>
       </c>
       <c r="B62" t="n">
-        <v>90990</v>
+        <v>57861</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8369,38 +8369,47 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>524112</v>
+        <v>524019</v>
       </c>
       <c r="R62" t="n">
-        <v>6713375</v>
+        <v>6713291</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8432,7 +8441,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8442,7 +8451,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8469,10 +8478,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123562888</v>
+        <v>123570699</v>
       </c>
       <c r="B63" t="n">
-        <v>57861</v>
+        <v>98079</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8481,47 +8490,52 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>524019</v>
+        <v>524145</v>
       </c>
       <c r="R63" t="n">
-        <v>6713291</v>
+        <v>6713399</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8553,7 +8567,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8563,7 +8577,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8590,7 +8604,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123570699</v>
+        <v>123567823</v>
       </c>
       <c r="B64" t="n">
         <v>98079</v>
@@ -8625,7 +8639,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -8644,10 +8658,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524145</v>
+        <v>524093</v>
       </c>
       <c r="R64" t="n">
-        <v>6713399</v>
+        <v>6713439</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8679,7 +8693,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8689,7 +8703,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8716,7 +8730,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123567823</v>
+        <v>123566767</v>
       </c>
       <c r="B65" t="n">
         <v>98079</v>
@@ -8751,7 +8765,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8770,10 +8784,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>524093</v>
+        <v>524084</v>
       </c>
       <c r="R65" t="n">
-        <v>6713439</v>
+        <v>6713408</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8805,7 +8819,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8815,7 +8829,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8842,10 +8856,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123566767</v>
+        <v>123571398</v>
       </c>
       <c r="B66" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8854,52 +8868,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>524084</v>
+        <v>524112</v>
       </c>
       <c r="R66" t="n">
-        <v>6713408</v>
+        <v>6713375</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY88"/>
+  <dimension ref="A1:AY89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9219,10 +9219,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123761045</v>
+        <v>123761091</v>
       </c>
       <c r="B69" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9231,31 +9231,40 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -9264,10 +9273,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523984</v>
+        <v>523962</v>
       </c>
       <c r="R69" t="n">
-        <v>6713796</v>
+        <v>6713819</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9299,7 +9308,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9309,7 +9318,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9336,10 +9345,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123760786</v>
+        <v>123761045</v>
       </c>
       <c r="B70" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9348,40 +9357,31 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -9390,10 +9390,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523969</v>
+        <v>523984</v>
       </c>
       <c r="R70" t="n">
-        <v>6713750</v>
+        <v>6713796</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9462,7 +9462,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123761091</v>
+        <v>123760786</v>
       </c>
       <c r="B71" t="n">
         <v>98101</v>
@@ -9497,7 +9497,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9516,10 +9516,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523962</v>
+        <v>523969</v>
       </c>
       <c r="R71" t="n">
-        <v>6713819</v>
+        <v>6713750</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9551,7 +9551,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9588,7 +9588,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123768976</v>
+        <v>123769093</v>
       </c>
       <c r="B72" t="n">
         <v>100279</v>
@@ -9621,7 +9621,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -9633,10 +9642,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>524011</v>
+        <v>524033</v>
       </c>
       <c r="R72" t="n">
-        <v>6713981</v>
+        <v>6713983</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9668,7 +9677,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9678,7 +9687,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9705,7 +9714,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123768932</v>
+        <v>123769023</v>
       </c>
       <c r="B73" t="n">
         <v>100279</v>
@@ -9738,16 +9747,7 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -9759,10 +9759,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>524000</v>
+        <v>524017</v>
       </c>
       <c r="R73" t="n">
-        <v>6713968</v>
+        <v>6713986</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9831,7 +9831,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123769093</v>
+        <v>123768989</v>
       </c>
       <c r="B74" t="n">
         <v>100279</v>
@@ -9864,16 +9864,7 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -9885,10 +9876,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>524033</v>
+        <v>524017</v>
       </c>
       <c r="R74" t="n">
-        <v>6713983</v>
+        <v>6713958</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9920,7 +9911,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9930,7 +9921,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9957,7 +9948,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123768989</v>
+        <v>123768976</v>
       </c>
       <c r="B75" t="n">
         <v>100279</v>
@@ -10002,10 +9993,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>524017</v>
+        <v>524011</v>
       </c>
       <c r="R75" t="n">
-        <v>6713958</v>
+        <v>6713981</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10037,7 +10028,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10047,7 +10038,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10074,7 +10065,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123768995</v>
+        <v>123769126</v>
       </c>
       <c r="B76" t="n">
         <v>100279</v>
@@ -10119,10 +10110,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>524011</v>
+        <v>524017</v>
       </c>
       <c r="R76" t="n">
-        <v>6713982</v>
+        <v>6713977</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10154,7 +10145,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10164,7 +10155,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10191,7 +10182,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123769126</v>
+        <v>123769072</v>
       </c>
       <c r="B77" t="n">
         <v>100279</v>
@@ -10224,22 +10215,31 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>524017</v>
+        <v>524031</v>
       </c>
       <c r="R77" t="n">
-        <v>6713977</v>
+        <v>6713998</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10271,7 +10271,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10308,7 +10308,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123769072</v>
+        <v>123768932</v>
       </c>
       <c r="B78" t="n">
         <v>100279</v>
@@ -10343,29 +10343,29 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>524031</v>
+        <v>524000</v>
       </c>
       <c r="R78" t="n">
-        <v>6713998</v>
+        <v>6713968</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10397,7 +10397,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10434,7 +10434,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123769023</v>
+        <v>123768995</v>
       </c>
       <c r="B79" t="n">
         <v>100279</v>
@@ -10479,10 +10479,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>524017</v>
+        <v>524011</v>
       </c>
       <c r="R79" t="n">
-        <v>6713986</v>
+        <v>6713982</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10689,7 +10689,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124433963</v>
+        <v>124431841</v>
       </c>
       <c r="B81" t="n">
         <v>98101</v>
@@ -10724,7 +10724,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -10743,10 +10743,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>524033</v>
+        <v>524168</v>
       </c>
       <c r="R81" t="n">
-        <v>6713451</v>
+        <v>6713526</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10815,7 +10815,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124432135</v>
+        <v>124434100</v>
       </c>
       <c r="B82" t="n">
         <v>98101</v>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10863,16 +10863,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524180</v>
+        <v>524042</v>
       </c>
       <c r="R82" t="n">
-        <v>6713485</v>
+        <v>6713423</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10904,7 +10909,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10914,7 +10919,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Över ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10941,10 +10951,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124431841</v>
+        <v>124434324</v>
       </c>
       <c r="B83" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10953,40 +10963,31 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10995,10 +10996,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524168</v>
+        <v>524045</v>
       </c>
       <c r="R83" t="n">
-        <v>6713526</v>
+        <v>6713403</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11030,7 +11031,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11040,7 +11041,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11067,7 +11068,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124434100</v>
+        <v>124432412</v>
       </c>
       <c r="B84" t="n">
         <v>98101</v>
@@ -11115,21 +11116,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524042</v>
+        <v>524183</v>
       </c>
       <c r="R84" t="n">
-        <v>6713423</v>
+        <v>6713449</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11161,7 +11157,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11171,12 +11167,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Över ca 5 kv/dm.</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11203,7 +11194,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124431501</v>
+        <v>124433963</v>
       </c>
       <c r="B85" t="n">
         <v>98101</v>
@@ -11238,7 +11229,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -11257,10 +11248,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524175</v>
+        <v>524033</v>
       </c>
       <c r="R85" t="n">
-        <v>6713573</v>
+        <v>6713451</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11292,7 +11283,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11302,12 +11293,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>18:08</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Under senvuxen klen gran.</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11470,10 +11456,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124434324</v>
+        <v>124432135</v>
       </c>
       <c r="B87" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11482,31 +11468,40 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -11515,10 +11510,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524045</v>
+        <v>524180</v>
       </c>
       <c r="R87" t="n">
-        <v>6713403</v>
+        <v>6713485</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11550,7 +11545,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11560,7 +11555,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11587,7 +11582,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124432412</v>
+        <v>124431501</v>
       </c>
       <c r="B88" t="n">
         <v>98101</v>
@@ -11622,7 +11617,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -11641,10 +11636,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524183</v>
+        <v>524175</v>
       </c>
       <c r="R88" t="n">
-        <v>6713449</v>
+        <v>6713573</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11676,7 +11671,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11686,7 +11681,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Under senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11710,6 +11710,132 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>124711417</v>
+      </c>
+      <c r="B89" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>524045</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6713421</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -10815,10 +10815,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124434100</v>
+        <v>124434324</v>
       </c>
       <c r="B82" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10827,45 +10827,31 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -10874,10 +10860,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524042</v>
+        <v>524045</v>
       </c>
       <c r="R82" t="n">
-        <v>6713423</v>
+        <v>6713403</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10909,7 +10895,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10919,12 +10905,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Över ca 5 kv/dm.</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10951,10 +10932,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124434324</v>
+        <v>124431501</v>
       </c>
       <c r="B83" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10963,31 +10944,40 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10996,10 +10986,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524045</v>
+        <v>524175</v>
       </c>
       <c r="R83" t="n">
-        <v>6713403</v>
+        <v>6713573</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11031,7 +11021,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11041,7 +11031,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Under senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11582,7 +11577,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124431501</v>
+        <v>124434100</v>
       </c>
       <c r="B88" t="n">
         <v>98101</v>
@@ -11617,7 +11612,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -11630,16 +11625,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524175</v>
+        <v>524042</v>
       </c>
       <c r="R88" t="n">
-        <v>6713573</v>
+        <v>6713423</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11681,12 +11681,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Under senvuxen klen gran.</t>
+          <t>Över ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -10689,7 +10689,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124431841</v>
+        <v>124433963</v>
       </c>
       <c r="B81" t="n">
         <v>98101</v>
@@ -10724,7 +10724,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -10743,10 +10743,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>524168</v>
+        <v>524033</v>
       </c>
       <c r="R81" t="n">
-        <v>6713526</v>
+        <v>6713451</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10932,7 +10932,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124431501</v>
+        <v>124432135</v>
       </c>
       <c r="B83" t="n">
         <v>98101</v>
@@ -10967,7 +10967,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10986,10 +10986,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524175</v>
+        <v>524180</v>
       </c>
       <c r="R83" t="n">
-        <v>6713573</v>
+        <v>6713485</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11031,12 +11031,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>18:08</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Under senvuxen klen gran.</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11063,7 +11058,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124432412</v>
+        <v>124435133</v>
       </c>
       <c r="B84" t="n">
         <v>98101</v>
@@ -11098,7 +11093,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -11111,16 +11106,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524183</v>
+        <v>523934</v>
       </c>
       <c r="R84" t="n">
-        <v>6713449</v>
+        <v>6713790</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11152,7 +11152,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11162,7 +11162,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>En vinterståndare.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11189,7 +11194,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124433963</v>
+        <v>124431841</v>
       </c>
       <c r="B85" t="n">
         <v>98101</v>
@@ -11224,7 +11229,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -11243,10 +11248,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524033</v>
+        <v>524168</v>
       </c>
       <c r="R85" t="n">
-        <v>6713451</v>
+        <v>6713526</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11278,7 +11283,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11288,7 +11293,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11315,7 +11320,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124435133</v>
+        <v>124432412</v>
       </c>
       <c r="B86" t="n">
         <v>98101</v>
@@ -11350,7 +11355,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -11363,21 +11368,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>523934</v>
+        <v>524183</v>
       </c>
       <c r="R86" t="n">
-        <v>6713790</v>
+        <v>6713449</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11409,7 +11409,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11419,12 +11419,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>20:13</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>En vinterståndare.</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11451,7 +11446,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124432135</v>
+        <v>124434100</v>
       </c>
       <c r="B87" t="n">
         <v>98101</v>
@@ -11486,7 +11481,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -11499,16 +11494,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524180</v>
+        <v>524042</v>
       </c>
       <c r="R87" t="n">
-        <v>6713485</v>
+        <v>6713423</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11540,7 +11540,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11550,7 +11550,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Över ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11577,7 +11582,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124434100</v>
+        <v>124431501</v>
       </c>
       <c r="B88" t="n">
         <v>98101</v>
@@ -11612,7 +11617,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -11625,21 +11630,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524042</v>
+        <v>524175</v>
       </c>
       <c r="R88" t="n">
-        <v>6713423</v>
+        <v>6713573</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11681,12 +11681,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Över ca 5 kv/dm.</t>
+          <t>Under senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -10815,10 +10815,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124434324</v>
+        <v>124434100</v>
       </c>
       <c r="B82" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10827,31 +10827,45 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -10860,10 +10874,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524045</v>
+        <v>524042</v>
       </c>
       <c r="R82" t="n">
-        <v>6713403</v>
+        <v>6713423</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10895,7 +10909,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10905,7 +10919,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Över ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10932,7 +10951,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124432135</v>
+        <v>124431501</v>
       </c>
       <c r="B83" t="n">
         <v>98101</v>
@@ -10967,7 +10986,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10986,10 +11005,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524180</v>
+        <v>524175</v>
       </c>
       <c r="R83" t="n">
-        <v>6713485</v>
+        <v>6713573</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11021,7 +11040,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11031,7 +11050,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Under senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11194,7 +11218,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124431841</v>
+        <v>124432412</v>
       </c>
       <c r="B85" t="n">
         <v>98101</v>
@@ -11229,7 +11253,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -11248,10 +11272,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524168</v>
+        <v>524183</v>
       </c>
       <c r="R85" t="n">
-        <v>6713526</v>
+        <v>6713449</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11283,7 +11307,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11293,7 +11317,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11320,7 +11344,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124432412</v>
+        <v>124431841</v>
       </c>
       <c r="B86" t="n">
         <v>98101</v>
@@ -11355,7 +11379,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -11374,10 +11398,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>524183</v>
+        <v>524168</v>
       </c>
       <c r="R86" t="n">
-        <v>6713449</v>
+        <v>6713526</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11409,7 +11433,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11419,7 +11443,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11446,10 +11470,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124434100</v>
+        <v>124434324</v>
       </c>
       <c r="B87" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11458,45 +11482,31 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -11505,10 +11515,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524042</v>
+        <v>524045</v>
       </c>
       <c r="R87" t="n">
-        <v>6713423</v>
+        <v>6713403</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11540,7 +11550,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11550,12 +11560,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Över ca 5 kv/dm.</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11582,7 +11587,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124431501</v>
+        <v>124432135</v>
       </c>
       <c r="B88" t="n">
         <v>98101</v>
@@ -11617,7 +11622,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -11636,10 +11641,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524175</v>
+        <v>524180</v>
       </c>
       <c r="R88" t="n">
-        <v>6713573</v>
+        <v>6713485</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11671,7 +11676,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11681,12 +11686,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>18:08</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Under senvuxen klen gran.</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -10815,7 +10815,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124434100</v>
+        <v>124435133</v>
       </c>
       <c r="B82" t="n">
         <v>98101</v>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10870,14 +10870,14 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524042</v>
+        <v>523934</v>
       </c>
       <c r="R82" t="n">
-        <v>6713423</v>
+        <v>6713790</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10919,12 +10919,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Över ca 5 kv/dm.</t>
+          <t>En vinterståndare.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10951,7 +10951,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124431501</v>
+        <v>124434100</v>
       </c>
       <c r="B83" t="n">
         <v>98101</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10999,16 +10999,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524175</v>
+        <v>524042</v>
       </c>
       <c r="R83" t="n">
-        <v>6713573</v>
+        <v>6713423</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11040,7 +11045,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11050,12 +11055,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Under senvuxen klen gran.</t>
+          <t>Över ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11082,10 +11087,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124435133</v>
+        <v>124434324</v>
       </c>
       <c r="B84" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11094,57 +11099,43 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523934</v>
+        <v>524045</v>
       </c>
       <c r="R84" t="n">
-        <v>6713790</v>
+        <v>6713403</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11176,7 +11167,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11186,12 +11177,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>20:13</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>En vinterståndare.</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11218,7 +11204,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124432412</v>
+        <v>124431841</v>
       </c>
       <c r="B85" t="n">
         <v>98101</v>
@@ -11253,7 +11239,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -11272,10 +11258,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524183</v>
+        <v>524168</v>
       </c>
       <c r="R85" t="n">
-        <v>6713449</v>
+        <v>6713526</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11307,7 +11293,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11317,7 +11303,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11344,7 +11330,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124431841</v>
+        <v>124432412</v>
       </c>
       <c r="B86" t="n">
         <v>98101</v>
@@ -11379,7 +11365,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -11398,10 +11384,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>524168</v>
+        <v>524183</v>
       </c>
       <c r="R86" t="n">
-        <v>6713526</v>
+        <v>6713449</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11433,7 +11419,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11443,7 +11429,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11470,10 +11456,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124434324</v>
+        <v>124431501</v>
       </c>
       <c r="B87" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11482,31 +11468,40 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -11515,10 +11510,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524045</v>
+        <v>524175</v>
       </c>
       <c r="R87" t="n">
-        <v>6713403</v>
+        <v>6713573</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11550,7 +11545,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11560,7 +11555,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Under senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -10689,7 +10689,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124433963</v>
+        <v>124431841</v>
       </c>
       <c r="B81" t="n">
         <v>98101</v>
@@ -10724,7 +10724,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -10743,10 +10743,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>524033</v>
+        <v>524168</v>
       </c>
       <c r="R81" t="n">
-        <v>6713451</v>
+        <v>6713526</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10815,7 +10815,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124435133</v>
+        <v>124432135</v>
       </c>
       <c r="B82" t="n">
         <v>98101</v>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10863,21 +10863,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>523934</v>
+        <v>524180</v>
       </c>
       <c r="R82" t="n">
-        <v>6713790</v>
+        <v>6713485</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10909,7 +10904,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10919,12 +10914,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>20:13</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>En vinterståndare.</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10951,7 +10941,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124434100</v>
+        <v>124435133</v>
       </c>
       <c r="B83" t="n">
         <v>98101</v>
@@ -10986,7 +10976,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -11006,14 +10996,14 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524042</v>
+        <v>523934</v>
       </c>
       <c r="R83" t="n">
-        <v>6713423</v>
+        <v>6713790</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11045,7 +11035,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11055,12 +11045,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Över ca 5 kv/dm.</t>
+          <t>En vinterståndare.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11087,10 +11077,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124434324</v>
+        <v>124433963</v>
       </c>
       <c r="B84" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11099,31 +11089,40 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -11132,10 +11131,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524045</v>
+        <v>524033</v>
       </c>
       <c r="R84" t="n">
-        <v>6713403</v>
+        <v>6713451</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11167,7 +11166,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11177,7 +11176,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11204,7 +11203,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124431841</v>
+        <v>124434100</v>
       </c>
       <c r="B85" t="n">
         <v>98101</v>
@@ -11239,7 +11238,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -11252,16 +11251,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524168</v>
+        <v>524042</v>
       </c>
       <c r="R85" t="n">
-        <v>6713526</v>
+        <v>6713423</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11293,7 +11297,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11303,7 +11307,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Över ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11456,10 +11465,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124431501</v>
+        <v>124434324</v>
       </c>
       <c r="B87" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11468,40 +11477,31 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -11510,10 +11510,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524175</v>
+        <v>524045</v>
       </c>
       <c r="R87" t="n">
-        <v>6713573</v>
+        <v>6713403</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11545,7 +11545,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11555,12 +11555,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>18:08</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Under senvuxen klen gran.</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11587,7 +11582,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124432135</v>
+        <v>124431501</v>
       </c>
       <c r="B88" t="n">
         <v>98101</v>
@@ -11622,7 +11617,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -11641,10 +11636,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524180</v>
+        <v>524175</v>
       </c>
       <c r="R88" t="n">
-        <v>6713485</v>
+        <v>6713573</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11676,7 +11671,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11686,7 +11681,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Under senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -10689,7 +10689,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124431841</v>
+        <v>124432135</v>
       </c>
       <c r="B81" t="n">
         <v>98101</v>
@@ -10724,7 +10724,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -10743,10 +10743,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>524168</v>
+        <v>524180</v>
       </c>
       <c r="R81" t="n">
-        <v>6713526</v>
+        <v>6713485</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10815,7 +10815,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124432135</v>
+        <v>124432412</v>
       </c>
       <c r="B82" t="n">
         <v>98101</v>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10869,10 +10869,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524180</v>
+        <v>524183</v>
       </c>
       <c r="R82" t="n">
-        <v>6713485</v>
+        <v>6713449</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10904,7 +10904,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10941,10 +10941,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124435133</v>
+        <v>124434324</v>
       </c>
       <c r="B83" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10953,57 +10953,43 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>523934</v>
+        <v>524045</v>
       </c>
       <c r="R83" t="n">
-        <v>6713790</v>
+        <v>6713403</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11035,7 +11021,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11045,12 +11031,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>20:13</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>En vinterståndare.</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11077,7 +11058,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124433963</v>
+        <v>124431841</v>
       </c>
       <c r="B84" t="n">
         <v>98101</v>
@@ -11112,7 +11093,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -11131,10 +11112,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524033</v>
+        <v>524168</v>
       </c>
       <c r="R84" t="n">
-        <v>6713451</v>
+        <v>6713526</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11166,7 +11147,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11176,7 +11157,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11203,7 +11184,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124434100</v>
+        <v>124435133</v>
       </c>
       <c r="B85" t="n">
         <v>98101</v>
@@ -11238,7 +11219,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -11258,14 +11239,14 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524042</v>
+        <v>523934</v>
       </c>
       <c r="R85" t="n">
-        <v>6713423</v>
+        <v>6713790</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11297,7 +11278,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11307,12 +11288,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Över ca 5 kv/dm.</t>
+          <t>En vinterståndare.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11339,7 +11320,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124432412</v>
+        <v>124431501</v>
       </c>
       <c r="B86" t="n">
         <v>98101</v>
@@ -11374,7 +11355,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -11393,10 +11374,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>524183</v>
+        <v>524175</v>
       </c>
       <c r="R86" t="n">
-        <v>6713449</v>
+        <v>6713573</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11428,7 +11409,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11438,7 +11419,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Under senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11465,10 +11451,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124434324</v>
+        <v>124433963</v>
       </c>
       <c r="B87" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11477,31 +11463,40 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -11510,10 +11505,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524045</v>
+        <v>524033</v>
       </c>
       <c r="R87" t="n">
-        <v>6713403</v>
+        <v>6713451</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11545,7 +11540,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11555,7 +11550,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11582,7 +11577,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124431501</v>
+        <v>124434100</v>
       </c>
       <c r="B88" t="n">
         <v>98101</v>
@@ -11617,7 +11612,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -11630,16 +11625,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524175</v>
+        <v>524042</v>
       </c>
       <c r="R88" t="n">
-        <v>6713573</v>
+        <v>6713423</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11681,12 +11681,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Under senvuxen klen gran.</t>
+          <t>Över ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -10689,7 +10689,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124432135</v>
+        <v>124432412</v>
       </c>
       <c r="B81" t="n">
         <v>98101</v>
@@ -10724,7 +10724,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -10743,10 +10743,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>524180</v>
+        <v>524183</v>
       </c>
       <c r="R81" t="n">
-        <v>6713485</v>
+        <v>6713449</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10815,10 +10815,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124432412</v>
+        <v>124434324</v>
       </c>
       <c r="B82" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10827,40 +10827,31 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -10869,10 +10860,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524183</v>
+        <v>524045</v>
       </c>
       <c r="R82" t="n">
-        <v>6713449</v>
+        <v>6713403</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10904,7 +10895,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10914,7 +10905,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10941,10 +10932,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124434324</v>
+        <v>124433963</v>
       </c>
       <c r="B83" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10953,31 +10944,40 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10986,10 +10986,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524045</v>
+        <v>524033</v>
       </c>
       <c r="R83" t="n">
-        <v>6713403</v>
+        <v>6713451</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11058,7 +11058,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124431841</v>
+        <v>124432135</v>
       </c>
       <c r="B84" t="n">
         <v>98101</v>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -11112,10 +11112,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524168</v>
+        <v>524180</v>
       </c>
       <c r="R84" t="n">
-        <v>6713526</v>
+        <v>6713485</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11147,7 +11147,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11157,7 +11157,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11184,7 +11184,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124435133</v>
+        <v>124434100</v>
       </c>
       <c r="B85" t="n">
         <v>98101</v>
@@ -11219,7 +11219,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -11239,14 +11239,14 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523934</v>
+        <v>524042</v>
       </c>
       <c r="R85" t="n">
-        <v>6713790</v>
+        <v>6713423</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11278,7 +11278,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11288,12 +11288,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>En vinterståndare.</t>
+          <t>Över ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11320,7 +11320,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124431501</v>
+        <v>124435133</v>
       </c>
       <c r="B86" t="n">
         <v>98101</v>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -11368,16 +11368,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>524175</v>
+        <v>523934</v>
       </c>
       <c r="R86" t="n">
-        <v>6713573</v>
+        <v>6713790</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11409,7 +11414,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11419,12 +11424,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Under senvuxen klen gran.</t>
+          <t>En vinterståndare.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11451,7 +11456,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124433963</v>
+        <v>124431841</v>
       </c>
       <c r="B87" t="n">
         <v>98101</v>
@@ -11486,7 +11491,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -11505,10 +11510,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524033</v>
+        <v>524168</v>
       </c>
       <c r="R87" t="n">
-        <v>6713451</v>
+        <v>6713526</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11540,7 +11545,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11550,7 +11555,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11577,7 +11582,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124434100</v>
+        <v>124431501</v>
       </c>
       <c r="B88" t="n">
         <v>98101</v>
@@ -11612,7 +11617,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -11625,21 +11630,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524042</v>
+        <v>524175</v>
       </c>
       <c r="R88" t="n">
-        <v>6713423</v>
+        <v>6713573</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11681,12 +11681,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Över ca 5 kv/dm.</t>
+          <t>Under senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -10689,7 +10689,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124432412</v>
+        <v>124435133</v>
       </c>
       <c r="B81" t="n">
         <v>98101</v>
@@ -10724,7 +10724,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -10737,16 +10737,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>524183</v>
+        <v>523934</v>
       </c>
       <c r="R81" t="n">
-        <v>6713449</v>
+        <v>6713790</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10778,7 +10783,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10788,7 +10793,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>En vinterståndare.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10815,10 +10825,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124434324</v>
+        <v>124431841</v>
       </c>
       <c r="B82" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10827,31 +10837,40 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -10860,10 +10879,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524045</v>
+        <v>524168</v>
       </c>
       <c r="R82" t="n">
-        <v>6713403</v>
+        <v>6713526</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10895,7 +10914,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10905,7 +10924,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10932,7 +10951,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124433963</v>
+        <v>124432412</v>
       </c>
       <c r="B83" t="n">
         <v>98101</v>
@@ -10967,7 +10986,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10986,10 +11005,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524033</v>
+        <v>524183</v>
       </c>
       <c r="R83" t="n">
-        <v>6713451</v>
+        <v>6713449</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11021,7 +11040,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11031,7 +11050,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11058,7 +11077,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124432135</v>
+        <v>124433963</v>
       </c>
       <c r="B84" t="n">
         <v>98101</v>
@@ -11112,10 +11131,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524180</v>
+        <v>524033</v>
       </c>
       <c r="R84" t="n">
-        <v>6713485</v>
+        <v>6713451</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11147,7 +11166,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11157,7 +11176,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11184,7 +11203,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124434100</v>
+        <v>124431501</v>
       </c>
       <c r="B85" t="n">
         <v>98101</v>
@@ -11219,7 +11238,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -11232,21 +11251,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524042</v>
+        <v>524175</v>
       </c>
       <c r="R85" t="n">
-        <v>6713423</v>
+        <v>6713573</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11278,7 +11292,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11288,12 +11302,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Över ca 5 kv/dm.</t>
+          <t>Under senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11320,7 +11334,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124435133</v>
+        <v>124434100</v>
       </c>
       <c r="B86" t="n">
         <v>98101</v>
@@ -11355,7 +11369,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -11375,14 +11389,14 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>523934</v>
+        <v>524042</v>
       </c>
       <c r="R86" t="n">
-        <v>6713790</v>
+        <v>6713423</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11414,7 +11428,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11424,12 +11438,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>En vinterståndare.</t>
+          <t>Över ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11456,10 +11470,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124431841</v>
+        <v>124434324</v>
       </c>
       <c r="B87" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11468,40 +11482,31 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -11510,10 +11515,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524168</v>
+        <v>524045</v>
       </c>
       <c r="R87" t="n">
-        <v>6713526</v>
+        <v>6713403</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11545,7 +11550,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11555,7 +11560,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11582,7 +11587,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124431501</v>
+        <v>124432135</v>
       </c>
       <c r="B88" t="n">
         <v>98101</v>
@@ -11617,7 +11622,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -11636,10 +11641,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524175</v>
+        <v>524180</v>
       </c>
       <c r="R88" t="n">
-        <v>6713573</v>
+        <v>6713485</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11671,7 +11676,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11681,12 +11686,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>18:08</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Under senvuxen klen gran.</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -10689,10 +10689,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124435133</v>
+        <v>124434324</v>
       </c>
       <c r="B81" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10701,57 +10701,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>523934</v>
+        <v>524045</v>
       </c>
       <c r="R81" t="n">
-        <v>6713790</v>
+        <v>6713403</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10783,7 +10769,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10793,12 +10779,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>20:13</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>En vinterståndare.</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10825,7 +10806,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124431841</v>
+        <v>124432135</v>
       </c>
       <c r="B82" t="n">
         <v>98101</v>
@@ -10860,7 +10841,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10879,10 +10860,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524168</v>
+        <v>524180</v>
       </c>
       <c r="R82" t="n">
-        <v>6713526</v>
+        <v>6713485</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10914,7 +10895,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10924,7 +10905,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10951,7 +10932,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124432412</v>
+        <v>124435133</v>
       </c>
       <c r="B83" t="n">
         <v>98101</v>
@@ -10986,7 +10967,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10999,16 +10980,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524183</v>
+        <v>523934</v>
       </c>
       <c r="R83" t="n">
-        <v>6713449</v>
+        <v>6713790</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11040,7 +11026,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11050,7 +11036,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>En vinterståndare.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11077,7 +11068,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124433963</v>
+        <v>124431841</v>
       </c>
       <c r="B84" t="n">
         <v>98101</v>
@@ -11112,7 +11103,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -11131,10 +11122,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524033</v>
+        <v>524168</v>
       </c>
       <c r="R84" t="n">
-        <v>6713451</v>
+        <v>6713526</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11166,7 +11157,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11176,7 +11167,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11470,10 +11461,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124434324</v>
+        <v>124433963</v>
       </c>
       <c r="B87" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11482,31 +11473,40 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -11515,10 +11515,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524045</v>
+        <v>524033</v>
       </c>
       <c r="R87" t="n">
-        <v>6713403</v>
+        <v>6713451</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11587,7 +11587,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124432135</v>
+        <v>124432412</v>
       </c>
       <c r="B88" t="n">
         <v>98101</v>
@@ -11622,7 +11622,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -11641,10 +11641,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524180</v>
+        <v>524183</v>
       </c>
       <c r="R88" t="n">
-        <v>6713485</v>
+        <v>6713449</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11676,7 +11676,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -10689,10 +10689,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124434324</v>
+        <v>124431841</v>
       </c>
       <c r="B81" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10701,31 +10701,40 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -10734,10 +10743,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>524045</v>
+        <v>524168</v>
       </c>
       <c r="R81" t="n">
-        <v>6713403</v>
+        <v>6713526</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10769,7 +10778,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10779,7 +10788,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10806,7 +10815,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124432135</v>
+        <v>124431501</v>
       </c>
       <c r="B82" t="n">
         <v>98101</v>
@@ -10841,7 +10850,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10860,10 +10869,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524180</v>
+        <v>524175</v>
       </c>
       <c r="R82" t="n">
-        <v>6713485</v>
+        <v>6713573</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10895,7 +10904,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10905,7 +10914,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Under senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10932,7 +10946,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124435133</v>
+        <v>124434100</v>
       </c>
       <c r="B83" t="n">
         <v>98101</v>
@@ -10967,7 +10981,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10987,14 +11001,14 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>523934</v>
+        <v>524042</v>
       </c>
       <c r="R83" t="n">
-        <v>6713790</v>
+        <v>6713423</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11026,7 +11040,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11036,12 +11050,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>En vinterståndare.</t>
+          <t>Över ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11068,7 +11082,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124431841</v>
+        <v>124435133</v>
       </c>
       <c r="B84" t="n">
         <v>98101</v>
@@ -11103,7 +11117,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -11116,16 +11130,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524168</v>
+        <v>523934</v>
       </c>
       <c r="R84" t="n">
-        <v>6713526</v>
+        <v>6713790</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11157,7 +11176,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11167,7 +11186,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>En vinterståndare.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11194,10 +11218,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124431501</v>
+        <v>124434324</v>
       </c>
       <c r="B85" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11206,40 +11230,31 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -11248,10 +11263,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524175</v>
+        <v>524045</v>
       </c>
       <c r="R85" t="n">
-        <v>6713573</v>
+        <v>6713403</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11283,7 +11298,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11293,12 +11308,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>18:08</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Under senvuxen klen gran.</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11325,7 +11335,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124434100</v>
+        <v>124432135</v>
       </c>
       <c r="B86" t="n">
         <v>98101</v>
@@ -11360,7 +11370,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -11373,21 +11383,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>524042</v>
+        <v>524180</v>
       </c>
       <c r="R86" t="n">
-        <v>6713423</v>
+        <v>6713485</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11419,7 +11424,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11429,12 +11434,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Över ca 5 kv/dm.</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD86" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -10815,7 +10815,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124431501</v>
+        <v>124433963</v>
       </c>
       <c r="B82" t="n">
         <v>98101</v>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10869,10 +10869,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524175</v>
+        <v>524033</v>
       </c>
       <c r="R82" t="n">
-        <v>6713573</v>
+        <v>6713451</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10904,7 +10904,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10914,12 +10914,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>18:08</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Under senvuxen klen gran.</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10946,7 +10941,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124434100</v>
+        <v>124432412</v>
       </c>
       <c r="B83" t="n">
         <v>98101</v>
@@ -10994,21 +10989,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524042</v>
+        <v>524183</v>
       </c>
       <c r="R83" t="n">
-        <v>6713423</v>
+        <v>6713449</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11040,7 +11030,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11050,12 +11040,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Över ca 5 kv/dm.</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11082,7 +11067,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124435133</v>
+        <v>124432135</v>
       </c>
       <c r="B84" t="n">
         <v>98101</v>
@@ -11117,7 +11102,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -11130,21 +11115,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523934</v>
+        <v>524180</v>
       </c>
       <c r="R84" t="n">
-        <v>6713790</v>
+        <v>6713485</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11176,7 +11156,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11186,12 +11166,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>20:13</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>En vinterståndare.</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11218,10 +11193,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124434324</v>
+        <v>124435133</v>
       </c>
       <c r="B85" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11230,43 +11205,57 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524045</v>
+        <v>523934</v>
       </c>
       <c r="R85" t="n">
-        <v>6713403</v>
+        <v>6713790</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11298,7 +11287,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11308,7 +11297,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>En vinterståndare.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11335,7 +11329,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124432135</v>
+        <v>124431501</v>
       </c>
       <c r="B86" t="n">
         <v>98101</v>
@@ -11370,7 +11364,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -11389,10 +11383,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>524180</v>
+        <v>524175</v>
       </c>
       <c r="R86" t="n">
-        <v>6713485</v>
+        <v>6713573</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11424,7 +11418,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11434,7 +11428,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Under senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11461,7 +11460,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124433963</v>
+        <v>124434100</v>
       </c>
       <c r="B87" t="n">
         <v>98101</v>
@@ -11496,7 +11495,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -11509,16 +11508,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524033</v>
+        <v>524042</v>
       </c>
       <c r="R87" t="n">
-        <v>6713451</v>
+        <v>6713423</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11550,7 +11554,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11560,7 +11564,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Över ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11587,10 +11596,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124432412</v>
+        <v>124434324</v>
       </c>
       <c r="B88" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11599,40 +11608,31 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -11641,10 +11641,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524183</v>
+        <v>524045</v>
       </c>
       <c r="R88" t="n">
-        <v>6713449</v>
+        <v>6713403</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11676,7 +11676,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -10689,7 +10689,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124431841</v>
+        <v>124432412</v>
       </c>
       <c r="B81" t="n">
         <v>98101</v>
@@ -10724,7 +10724,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -10743,10 +10743,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>524168</v>
+        <v>524183</v>
       </c>
       <c r="R81" t="n">
-        <v>6713526</v>
+        <v>6713449</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10941,10 +10941,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124432412</v>
+        <v>124434324</v>
       </c>
       <c r="B83" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10953,40 +10953,31 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10995,10 +10986,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524183</v>
+        <v>524045</v>
       </c>
       <c r="R83" t="n">
-        <v>6713449</v>
+        <v>6713403</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11030,7 +11021,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11040,7 +11031,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11067,7 +11058,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124432135</v>
+        <v>124431501</v>
       </c>
       <c r="B84" t="n">
         <v>98101</v>
@@ -11102,7 +11093,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -11121,10 +11112,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524180</v>
+        <v>524175</v>
       </c>
       <c r="R84" t="n">
-        <v>6713485</v>
+        <v>6713573</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11156,7 +11147,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11166,7 +11157,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Under senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11193,7 +11189,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124435133</v>
+        <v>124434100</v>
       </c>
       <c r="B85" t="n">
         <v>98101</v>
@@ -11228,7 +11224,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -11248,14 +11244,14 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523934</v>
+        <v>524042</v>
       </c>
       <c r="R85" t="n">
-        <v>6713790</v>
+        <v>6713423</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11287,7 +11283,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11297,12 +11293,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>En vinterståndare.</t>
+          <t>Över ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11329,7 +11325,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124431501</v>
+        <v>124435133</v>
       </c>
       <c r="B86" t="n">
         <v>98101</v>
@@ -11364,7 +11360,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -11377,16 +11373,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>524175</v>
+        <v>523934</v>
       </c>
       <c r="R86" t="n">
-        <v>6713573</v>
+        <v>6713790</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11418,7 +11419,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11428,12 +11429,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Under senvuxen klen gran.</t>
+          <t>En vinterståndare.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11460,7 +11461,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124434100</v>
+        <v>124431841</v>
       </c>
       <c r="B87" t="n">
         <v>98101</v>
@@ -11495,7 +11496,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -11508,21 +11509,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524042</v>
+        <v>524168</v>
       </c>
       <c r="R87" t="n">
-        <v>6713423</v>
+        <v>6713526</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11554,7 +11550,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11564,12 +11560,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Över ca 5 kv/dm.</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11596,10 +11587,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124434324</v>
+        <v>124432135</v>
       </c>
       <c r="B88" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11608,31 +11599,40 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -11641,10 +11641,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524045</v>
+        <v>524180</v>
       </c>
       <c r="R88" t="n">
-        <v>6713403</v>
+        <v>6713485</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11676,7 +11676,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -10689,7 +10689,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124432412</v>
+        <v>124434100</v>
       </c>
       <c r="B81" t="n">
         <v>98101</v>
@@ -10737,16 +10737,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>524183</v>
+        <v>524042</v>
       </c>
       <c r="R81" t="n">
-        <v>6713449</v>
+        <v>6713423</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10778,7 +10783,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10788,7 +10793,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Över ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10941,10 +10951,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124434324</v>
+        <v>124435133</v>
       </c>
       <c r="B83" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10953,43 +10963,57 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524045</v>
+        <v>523934</v>
       </c>
       <c r="R83" t="n">
-        <v>6713403</v>
+        <v>6713790</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11021,7 +11045,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11031,7 +11055,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>En vinterståndare.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11058,7 +11087,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124431501</v>
+        <v>124432135</v>
       </c>
       <c r="B84" t="n">
         <v>98101</v>
@@ -11093,7 +11122,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -11112,10 +11141,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524175</v>
+        <v>524180</v>
       </c>
       <c r="R84" t="n">
-        <v>6713573</v>
+        <v>6713485</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11147,7 +11176,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11157,12 +11186,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>18:08</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Under senvuxen klen gran.</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11189,7 +11213,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124434100</v>
+        <v>124431501</v>
       </c>
       <c r="B85" t="n">
         <v>98101</v>
@@ -11224,7 +11248,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -11237,21 +11261,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524042</v>
+        <v>524175</v>
       </c>
       <c r="R85" t="n">
-        <v>6713423</v>
+        <v>6713573</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11283,7 +11302,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11293,12 +11312,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Över ca 5 kv/dm.</t>
+          <t>Under senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11325,7 +11344,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124435133</v>
+        <v>124431841</v>
       </c>
       <c r="B86" t="n">
         <v>98101</v>
@@ -11360,7 +11379,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -11373,21 +11392,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>523934</v>
+        <v>524168</v>
       </c>
       <c r="R86" t="n">
-        <v>6713790</v>
+        <v>6713526</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11419,7 +11433,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11429,12 +11443,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>20:13</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>En vinterståndare.</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11461,10 +11470,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124431841</v>
+        <v>124434324</v>
       </c>
       <c r="B87" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11473,40 +11482,31 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -11515,10 +11515,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524168</v>
+        <v>524045</v>
       </c>
       <c r="R87" t="n">
-        <v>6713526</v>
+        <v>6713403</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11587,7 +11587,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124432135</v>
+        <v>124432412</v>
       </c>
       <c r="B88" t="n">
         <v>98101</v>
@@ -11622,7 +11622,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -11641,10 +11641,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524180</v>
+        <v>524183</v>
       </c>
       <c r="R88" t="n">
-        <v>6713485</v>
+        <v>6713449</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11676,7 +11676,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -11716,7 +11716,7 @@
         <v>124711417</v>
       </c>
       <c r="B89" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY89"/>
+  <dimension ref="A1:AY91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11837,6 +11837,242 @@
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>125899247</v>
+      </c>
+      <c r="B90" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>524042</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6713304</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>125899180</v>
+      </c>
+      <c r="B91" t="n">
+        <v>58125</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>100058</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Mindre flugsnappare</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Ficedula parva</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1794)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>524025</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6713299</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -11842,7 +11842,7 @@
         <v>125899247</v>
       </c>
       <c r="B90" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -11842,7 +11842,7 @@
         <v>125899247</v>
       </c>
       <c r="B90" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>125899180</v>
       </c>
       <c r="B91" t="n">
-        <v>58125</v>
+        <v>58126</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -11842,7 +11842,7 @@
         <v>125899247</v>
       </c>
       <c r="B90" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -11842,7 +11842,7 @@
         <v>125899247</v>
       </c>
       <c r="B90" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -11842,7 +11842,7 @@
         <v>125899247</v>
       </c>
       <c r="B90" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -11842,7 +11842,7 @@
         <v>125899247</v>
       </c>
       <c r="B90" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>125899180</v>
       </c>
       <c r="B91" t="n">
-        <v>58126</v>
+        <v>58127</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY91"/>
+  <dimension ref="A1:AY92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12073,6 +12073,113 @@
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>126231015</v>
+      </c>
+      <c r="B92" t="n">
+        <v>91236</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>524063</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6713991</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -11842,7 +11842,7 @@
         <v>125899247</v>
       </c>
       <c r="B90" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -11842,7 +11842,7 @@
         <v>125899247</v>
       </c>
       <c r="B90" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>126231015</v>
       </c>
       <c r="B92" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -11842,7 +11842,7 @@
         <v>125899247</v>
       </c>
       <c r="B90" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>125899180</v>
       </c>
       <c r="B91" t="n">
-        <v>58127</v>
+        <v>58131</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>126231015</v>
       </c>
       <c r="B92" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -11842,7 +11842,7 @@
         <v>125899247</v>
       </c>
       <c r="B90" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -11842,7 +11842,7 @@
         <v>125899247</v>
       </c>
       <c r="B90" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>125899180</v>
       </c>
       <c r="B91" t="n">
-        <v>58131</v>
+        <v>58134</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>126231015</v>
       </c>
       <c r="B92" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -12185,7 +12185,7 @@
         <v>126936299</v>
       </c>
       <c r="B93" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12306,7 +12306,7 @@
         <v>126934586</v>
       </c>
       <c r="B94" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>126934603</v>
       </c>
       <c r="B95" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12551,7 +12551,7 @@
         <v>126934577</v>
       </c>
       <c r="B96" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>126934164</v>
       </c>
       <c r="B97" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         <v>126933611</v>
       </c>
       <c r="B98" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>126933275</v>
       </c>
       <c r="B99" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>126936539</v>
       </c>
       <c r="B100" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>126932846</v>
       </c>
       <c r="B101" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>126933692</v>
       </c>
       <c r="B102" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>126932450</v>
       </c>
       <c r="B103" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>126933326</v>
       </c>
       <c r="B104" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>126962844</v>
       </c>
       <c r="B105" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>126963368</v>
       </c>
       <c r="B106" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>126961591</v>
       </c>
       <c r="B107" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14008,7 +14008,7 @@
         <v>126963263</v>
       </c>
       <c r="B108" t="n">
-        <v>91541</v>
+        <v>91615</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>126962269</v>
       </c>
       <c r="B109" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>126963427</v>
       </c>
       <c r="B110" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>126962421</v>
       </c>
       <c r="B111" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>126963583</v>
       </c>
       <c r="B112" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -12185,7 +12185,7 @@
         <v>126936299</v>
       </c>
       <c r="B93" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12306,7 +12306,7 @@
         <v>126934586</v>
       </c>
       <c r="B94" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>126934603</v>
       </c>
       <c r="B95" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12551,7 +12551,7 @@
         <v>126934577</v>
       </c>
       <c r="B96" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>126934164</v>
       </c>
       <c r="B97" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         <v>126933611</v>
       </c>
       <c r="B98" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>126933275</v>
       </c>
       <c r="B99" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>126936539</v>
       </c>
       <c r="B100" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>126932846</v>
       </c>
       <c r="B101" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>126933692</v>
       </c>
       <c r="B102" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>126932450</v>
       </c>
       <c r="B103" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>126933326</v>
       </c>
       <c r="B104" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>126962844</v>
       </c>
       <c r="B105" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>126963368</v>
       </c>
       <c r="B106" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>126961591</v>
       </c>
       <c r="B107" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14008,7 +14008,7 @@
         <v>126963263</v>
       </c>
       <c r="B108" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>126962269</v>
       </c>
       <c r="B109" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>126963427</v>
       </c>
       <c r="B110" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>126962421</v>
       </c>
       <c r="B111" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>126963583</v>
       </c>
       <c r="B112" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -12185,7 +12185,7 @@
         <v>126936299</v>
       </c>
       <c r="B93" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12306,7 +12306,7 @@
         <v>126934586</v>
       </c>
       <c r="B94" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>126934603</v>
       </c>
       <c r="B95" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12551,7 +12551,7 @@
         <v>126934577</v>
       </c>
       <c r="B96" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>126934164</v>
       </c>
       <c r="B97" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         <v>126933611</v>
       </c>
       <c r="B98" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>126933275</v>
       </c>
       <c r="B99" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>126936539</v>
       </c>
       <c r="B100" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>126932846</v>
       </c>
       <c r="B101" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>126933692</v>
       </c>
       <c r="B102" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>126932450</v>
       </c>
       <c r="B103" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>126933326</v>
       </c>
       <c r="B104" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>126962844</v>
       </c>
       <c r="B105" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>126963368</v>
       </c>
       <c r="B106" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>126961591</v>
       </c>
       <c r="B107" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14008,7 +14008,7 @@
         <v>126963263</v>
       </c>
       <c r="B108" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>126962269</v>
       </c>
       <c r="B109" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>126963427</v>
       </c>
       <c r="B110" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>126962421</v>
       </c>
       <c r="B111" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>126963583</v>
       </c>
       <c r="B112" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -12185,7 +12185,7 @@
         <v>126936299</v>
       </c>
       <c r="B93" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12306,7 +12306,7 @@
         <v>126934586</v>
       </c>
       <c r="B94" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>126934603</v>
       </c>
       <c r="B95" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12551,7 +12551,7 @@
         <v>126934577</v>
       </c>
       <c r="B96" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>126934164</v>
       </c>
       <c r="B97" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         <v>126933611</v>
       </c>
       <c r="B98" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>126933275</v>
       </c>
       <c r="B99" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>126936539</v>
       </c>
       <c r="B100" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>126932846</v>
       </c>
       <c r="B101" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>126933692</v>
       </c>
       <c r="B102" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>126932450</v>
       </c>
       <c r="B103" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>126933326</v>
       </c>
       <c r="B104" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>126962844</v>
       </c>
       <c r="B105" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>126963368</v>
       </c>
       <c r="B106" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>126961591</v>
       </c>
       <c r="B107" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14008,7 +14008,7 @@
         <v>126963263</v>
       </c>
       <c r="B108" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>126962269</v>
       </c>
       <c r="B109" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>126963427</v>
       </c>
       <c r="B110" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>126962421</v>
       </c>
       <c r="B111" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>126963583</v>
       </c>
       <c r="B112" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -12185,7 +12185,7 @@
         <v>126936299</v>
       </c>
       <c r="B93" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12306,7 +12306,7 @@
         <v>126934586</v>
       </c>
       <c r="B94" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>126934603</v>
       </c>
       <c r="B95" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12551,7 +12551,7 @@
         <v>126934577</v>
       </c>
       <c r="B96" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>126934164</v>
       </c>
       <c r="B97" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         <v>126933611</v>
       </c>
       <c r="B98" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>126933275</v>
       </c>
       <c r="B99" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>126936539</v>
       </c>
       <c r="B100" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>126932846</v>
       </c>
       <c r="B101" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>126933692</v>
       </c>
       <c r="B102" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>126932450</v>
       </c>
       <c r="B103" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>126933326</v>
       </c>
       <c r="B104" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>126962844</v>
       </c>
       <c r="B105" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>126963368</v>
       </c>
       <c r="B106" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>126961591</v>
       </c>
       <c r="B107" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>126962269</v>
       </c>
       <c r="B109" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>126963427</v>
       </c>
       <c r="B110" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>126962421</v>
       </c>
       <c r="B111" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>126963583</v>
       </c>
       <c r="B112" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY112"/>
+  <dimension ref="A1:AY114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14618,6 +14618,238 @@
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>127727170</v>
+      </c>
+      <c r="B113" t="n">
+        <v>98448</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>524154</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6713653</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>127727173</v>
+      </c>
+      <c r="B114" t="n">
+        <v>98448</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>524154</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6713656</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -12185,7 +12185,7 @@
         <v>126936299</v>
       </c>
       <c r="B93" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12306,7 +12306,7 @@
         <v>126934586</v>
       </c>
       <c r="B94" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>126934603</v>
       </c>
       <c r="B95" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12551,7 +12551,7 @@
         <v>126934577</v>
       </c>
       <c r="B96" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>126934164</v>
       </c>
       <c r="B97" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         <v>126933611</v>
       </c>
       <c r="B98" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>126933275</v>
       </c>
       <c r="B99" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>126936539</v>
       </c>
       <c r="B100" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>126932846</v>
       </c>
       <c r="B101" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>126933692</v>
       </c>
       <c r="B102" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>126932450</v>
       </c>
       <c r="B103" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>126933326</v>
       </c>
       <c r="B104" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>126962844</v>
       </c>
       <c r="B105" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>126963368</v>
       </c>
       <c r="B106" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>126961591</v>
       </c>
       <c r="B107" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14008,7 +14008,7 @@
         <v>126963263</v>
       </c>
       <c r="B108" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>126962269</v>
       </c>
       <c r="B109" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>126963427</v>
       </c>
       <c r="B110" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>126962421</v>
       </c>
       <c r="B111" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>126963583</v>
       </c>
       <c r="B112" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>127727170</v>
       </c>
       <c r="B113" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>127727173</v>
       </c>
       <c r="B114" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -12427,7 +12427,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126934603</v>
+        <v>126934577</v>
       </c>
       <c r="B95" t="n">
         <v>98450</v>
@@ -12476,10 +12476,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>524034</v>
+        <v>524036</v>
       </c>
       <c r="R95" t="n">
-        <v>6713296</v>
+        <v>6713293</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12511,7 +12511,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12548,7 +12548,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126934577</v>
+        <v>126934603</v>
       </c>
       <c r="B96" t="n">
         <v>98450</v>
@@ -12597,10 +12597,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>524036</v>
+        <v>524034</v>
       </c>
       <c r="R96" t="n">
-        <v>6713293</v>
+        <v>6713296</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12632,7 +12632,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD96" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -14623,7 +14623,7 @@
         <v>127727170</v>
       </c>
       <c r="B113" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>127727173</v>
       </c>
       <c r="B114" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -14623,7 +14623,7 @@
         <v>127727170</v>
       </c>
       <c r="B113" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>127727173</v>
       </c>
       <c r="B114" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -14623,7 +14623,7 @@
         <v>127727170</v>
       </c>
       <c r="B113" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>127727173</v>
       </c>
       <c r="B114" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -14623,7 +14623,7 @@
         <v>127727170</v>
       </c>
       <c r="B113" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>127727173</v>
       </c>
       <c r="B114" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY114"/>
+  <dimension ref="A1:AY117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14850,6 +14850,341 @@
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>128217774</v>
+      </c>
+      <c r="B115" t="n">
+        <v>92652</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>524149</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6713406</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>128217698</v>
+      </c>
+      <c r="B116" t="n">
+        <v>92674</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>524146</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6713402</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Större antal runt gran.</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>128217134</v>
+      </c>
+      <c r="B117" t="n">
+        <v>57832</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Banvallen, Smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>524130</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6713667</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -14623,7 +14623,7 @@
         <v>127727170</v>
       </c>
       <c r="B113" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>127727173</v>
       </c>
       <c r="B114" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>128217774</v>
       </c>
       <c r="B115" t="n">
-        <v>92652</v>
+        <v>92653</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>128217698</v>
       </c>
       <c r="B116" t="n">
-        <v>92674</v>
+        <v>92675</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -14623,7 +14623,7 @@
         <v>127727170</v>
       </c>
       <c r="B113" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>127727173</v>
       </c>
       <c r="B114" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>128217774</v>
       </c>
       <c r="B115" t="n">
-        <v>92653</v>
+        <v>92654</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>128217698</v>
       </c>
       <c r="B116" t="n">
-        <v>92675</v>
+        <v>92676</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -14623,7 +14623,7 @@
         <v>127727170</v>
       </c>
       <c r="B113" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>127727173</v>
       </c>
       <c r="B114" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>128217774</v>
       </c>
       <c r="B115" t="n">
-        <v>92654</v>
+        <v>92662</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>128217698</v>
       </c>
       <c r="B116" t="n">
-        <v>92676</v>
+        <v>92684</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>128217134</v>
       </c>
       <c r="B117" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -14623,7 +14623,7 @@
         <v>127727170</v>
       </c>
       <c r="B113" t="n">
-        <v>98478</v>
+        <v>98490</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>127727173</v>
       </c>
       <c r="B114" t="n">
-        <v>98478</v>
+        <v>98490</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>128217774</v>
       </c>
       <c r="B115" t="n">
-        <v>92662</v>
+        <v>92754</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>128217698</v>
       </c>
       <c r="B116" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>128217134</v>
       </c>
       <c r="B117" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -14855,7 +14855,7 @@
         <v>128217774</v>
       </c>
       <c r="B115" t="n">
-        <v>92754</v>
+        <v>92766</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>128217698</v>
       </c>
       <c r="B116" t="n">
-        <v>92776</v>
+        <v>92788</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>128217134</v>
       </c>
       <c r="B117" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -14855,7 +14855,7 @@
         <v>128217774</v>
       </c>
       <c r="B115" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>128217698</v>
       </c>
       <c r="B116" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -14855,7 +14855,7 @@
         <v>128217774</v>
       </c>
       <c r="B115" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>128217698</v>
       </c>
       <c r="B116" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -14855,7 +14855,7 @@
         <v>128217774</v>
       </c>
       <c r="B115" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>128217698</v>
       </c>
       <c r="B116" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>128217134</v>
       </c>
       <c r="B117" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -15187,10 +15187,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129064961</v>
+        <v>129065356</v>
       </c>
       <c r="B118" t="n">
-        <v>92456</v>
+        <v>91293</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15198,43 +15198,43 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>524024</v>
+        <v>524081</v>
       </c>
       <c r="R118" t="n">
-        <v>6713938</v>
+        <v>6713859</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15266,7 +15266,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15276,7 +15276,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15303,45 +15303,54 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129065420</v>
+        <v>129064961</v>
       </c>
       <c r="B119" t="n">
-        <v>91520</v>
+        <v>92456</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524074</v>
+        <v>524024</v>
       </c>
       <c r="R119" t="n">
-        <v>6713878</v>
+        <v>6713938</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15373,7 +15382,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15383,12 +15392,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Längs hela stammen.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15415,54 +15419,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129065356</v>
+        <v>129065420</v>
       </c>
       <c r="B120" t="n">
-        <v>91293</v>
+        <v>91520</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524081</v>
+        <v>524074</v>
       </c>
       <c r="R120" t="n">
-        <v>6713859</v>
+        <v>6713878</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15494,7 +15489,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15504,7 +15499,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Längs hela stammen.</t>
         </is>
       </c>
       <c r="AD120" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -15187,54 +15187,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129065356</v>
+        <v>129065420</v>
       </c>
       <c r="B118" t="n">
-        <v>91293</v>
+        <v>91523</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>524081</v>
+        <v>524074</v>
       </c>
       <c r="R118" t="n">
-        <v>6713859</v>
+        <v>6713878</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15266,7 +15257,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15276,7 +15267,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Längs hela stammen.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15303,10 +15299,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129064961</v>
+        <v>129065356</v>
       </c>
       <c r="B119" t="n">
-        <v>92456</v>
+        <v>91296</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15314,43 +15310,43 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524024</v>
+        <v>524081</v>
       </c>
       <c r="R119" t="n">
-        <v>6713938</v>
+        <v>6713859</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15382,7 +15378,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15392,7 +15388,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15419,45 +15415,54 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129065420</v>
+        <v>129064961</v>
       </c>
       <c r="B120" t="n">
-        <v>91520</v>
+        <v>92461</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524074</v>
+        <v>524024</v>
       </c>
       <c r="R120" t="n">
-        <v>6713878</v>
+        <v>6713938</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15489,7 +15494,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15499,12 +15504,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Längs hela stammen.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15534,7 +15534,7 @@
         <v>129116978</v>
       </c>
       <c r="B121" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>129114973</v>
       </c>
       <c r="B122" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>129116918</v>
       </c>
       <c r="B123" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>129115572</v>
       </c>
       <c r="B124" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -15187,45 +15187,54 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129065420</v>
+        <v>129065356</v>
       </c>
       <c r="B118" t="n">
-        <v>91523</v>
+        <v>91299</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>524074</v>
+        <v>524081</v>
       </c>
       <c r="R118" t="n">
-        <v>6713878</v>
+        <v>6713859</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15257,7 +15266,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15267,12 +15276,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Längs hela stammen.</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15299,54 +15303,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129065356</v>
+        <v>129065420</v>
       </c>
       <c r="B119" t="n">
-        <v>91296</v>
+        <v>91526</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524081</v>
+        <v>524074</v>
       </c>
       <c r="R119" t="n">
-        <v>6713859</v>
+        <v>6713878</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15378,7 +15373,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15388,7 +15383,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Längs hela stammen.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15418,7 +15418,7 @@
         <v>129064961</v>
       </c>
       <c r="B120" t="n">
-        <v>92461</v>
+        <v>92464</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>129116978</v>
       </c>
       <c r="B121" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>129114973</v>
       </c>
       <c r="B122" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>129116918</v>
       </c>
       <c r="B123" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>129115572</v>
       </c>
       <c r="B124" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -15187,54 +15187,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129065356</v>
+        <v>129065420</v>
       </c>
       <c r="B118" t="n">
-        <v>91299</v>
+        <v>91526</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>524081</v>
+        <v>524074</v>
       </c>
       <c r="R118" t="n">
-        <v>6713859</v>
+        <v>6713878</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15266,7 +15257,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15276,7 +15267,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Längs hela stammen.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15303,45 +15299,54 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129065420</v>
+        <v>129064961</v>
       </c>
       <c r="B119" t="n">
-        <v>91526</v>
+        <v>92464</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524074</v>
+        <v>524024</v>
       </c>
       <c r="R119" t="n">
-        <v>6713878</v>
+        <v>6713938</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15373,7 +15378,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15383,12 +15388,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Längs hela stammen.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15415,10 +15415,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129064961</v>
+        <v>129065356</v>
       </c>
       <c r="B120" t="n">
-        <v>92464</v>
+        <v>91299</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15426,43 +15426,43 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524024</v>
+        <v>524081</v>
       </c>
       <c r="R120" t="n">
-        <v>6713938</v>
+        <v>6713859</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD120" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -15187,45 +15187,54 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129065420</v>
+        <v>129064961</v>
       </c>
       <c r="B118" t="n">
-        <v>91526</v>
+        <v>92464</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>524074</v>
+        <v>524024</v>
       </c>
       <c r="R118" t="n">
-        <v>6713878</v>
+        <v>6713938</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15257,7 +15266,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15267,12 +15276,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Längs hela stammen.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15299,54 +15303,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129064961</v>
+        <v>129065420</v>
       </c>
       <c r="B119" t="n">
-        <v>92464</v>
+        <v>91526</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524024</v>
+        <v>524074</v>
       </c>
       <c r="R119" t="n">
-        <v>6713938</v>
+        <v>6713878</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15378,7 +15373,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15388,7 +15383,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Längs hela stammen.</t>
         </is>
       </c>
       <c r="AD119" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -15187,54 +15187,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129064961</v>
+        <v>129065420</v>
       </c>
       <c r="B118" t="n">
-        <v>92464</v>
+        <v>91526</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>524024</v>
+        <v>524074</v>
       </c>
       <c r="R118" t="n">
-        <v>6713938</v>
+        <v>6713878</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15266,7 +15257,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15276,7 +15267,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Längs hela stammen.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15303,45 +15299,54 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129065420</v>
+        <v>129065356</v>
       </c>
       <c r="B119" t="n">
-        <v>91526</v>
+        <v>91299</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524074</v>
+        <v>524081</v>
       </c>
       <c r="R119" t="n">
-        <v>6713878</v>
+        <v>6713859</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15373,7 +15378,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15383,12 +15388,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Längs hela stammen.</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15415,10 +15415,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129065356</v>
+        <v>129064961</v>
       </c>
       <c r="B120" t="n">
-        <v>91299</v>
+        <v>92464</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15426,43 +15426,43 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524081</v>
+        <v>524024</v>
       </c>
       <c r="R120" t="n">
-        <v>6713859</v>
+        <v>6713938</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD120" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -15190,7 +15190,7 @@
         <v>129065420</v>
       </c>
       <c r="B118" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15299,10 +15299,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129065356</v>
+        <v>129064961</v>
       </c>
       <c r="B119" t="n">
-        <v>91299</v>
+        <v>92471</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15310,43 +15310,43 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524081</v>
+        <v>524024</v>
       </c>
       <c r="R119" t="n">
-        <v>6713859</v>
+        <v>6713938</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15378,7 +15378,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15388,7 +15388,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15415,10 +15415,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129064961</v>
+        <v>129065356</v>
       </c>
       <c r="B120" t="n">
-        <v>92464</v>
+        <v>91305</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15426,43 +15426,43 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524024</v>
+        <v>524081</v>
       </c>
       <c r="R120" t="n">
-        <v>6713938</v>
+        <v>6713859</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15534,7 +15534,7 @@
         <v>129116978</v>
       </c>
       <c r="B121" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>129114973</v>
       </c>
       <c r="B122" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>129116918</v>
       </c>
       <c r="B123" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>129115572</v>
       </c>
       <c r="B124" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -15190,7 +15190,7 @@
         <v>129065420</v>
       </c>
       <c r="B118" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15299,10 +15299,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129064961</v>
+        <v>129065356</v>
       </c>
       <c r="B119" t="n">
-        <v>92471</v>
+        <v>91312</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15310,43 +15310,43 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524024</v>
+        <v>524081</v>
       </c>
       <c r="R119" t="n">
-        <v>6713938</v>
+        <v>6713859</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15378,7 +15378,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15388,7 +15388,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15415,10 +15415,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129065356</v>
+        <v>129064961</v>
       </c>
       <c r="B120" t="n">
-        <v>91305</v>
+        <v>92478</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15426,43 +15426,43 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524081</v>
+        <v>524024</v>
       </c>
       <c r="R120" t="n">
-        <v>6713859</v>
+        <v>6713938</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15534,7 +15534,7 @@
         <v>129116978</v>
       </c>
       <c r="B121" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>129114973</v>
       </c>
       <c r="B122" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>129116918</v>
       </c>
       <c r="B123" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>129115572</v>
       </c>
       <c r="B124" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -15187,45 +15187,54 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129065420</v>
+        <v>129064961</v>
       </c>
       <c r="B118" t="n">
-        <v>91540</v>
+        <v>92480</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>524074</v>
+        <v>524024</v>
       </c>
       <c r="R118" t="n">
-        <v>6713878</v>
+        <v>6713938</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15257,7 +15266,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15267,12 +15276,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Längs hela stammen.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15299,54 +15303,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129065356</v>
+        <v>129065420</v>
       </c>
       <c r="B119" t="n">
-        <v>91312</v>
+        <v>91542</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524081</v>
+        <v>524074</v>
       </c>
       <c r="R119" t="n">
-        <v>6713859</v>
+        <v>6713878</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15378,7 +15373,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15388,7 +15383,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Längs hela stammen.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15415,10 +15415,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129064961</v>
+        <v>129065356</v>
       </c>
       <c r="B120" t="n">
-        <v>92478</v>
+        <v>91314</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15426,43 +15426,43 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524024</v>
+        <v>524081</v>
       </c>
       <c r="R120" t="n">
-        <v>6713938</v>
+        <v>6713859</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15534,7 +15534,7 @@
         <v>129116978</v>
       </c>
       <c r="B121" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>129114973</v>
       </c>
       <c r="B122" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>129116918</v>
       </c>
       <c r="B123" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>129115572</v>
       </c>
       <c r="B124" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -15187,10 +15187,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129064961</v>
+        <v>129065356</v>
       </c>
       <c r="B118" t="n">
-        <v>92480</v>
+        <v>91314</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15198,43 +15198,43 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>524024</v>
+        <v>524081</v>
       </c>
       <c r="R118" t="n">
-        <v>6713938</v>
+        <v>6713859</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15266,7 +15266,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15276,7 +15276,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15415,10 +15415,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129065356</v>
+        <v>129064961</v>
       </c>
       <c r="B120" t="n">
-        <v>91314</v>
+        <v>92480</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15426,43 +15426,43 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524081</v>
+        <v>524024</v>
       </c>
       <c r="R120" t="n">
-        <v>6713859</v>
+        <v>6713938</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD120" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -15187,54 +15187,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129065356</v>
+        <v>129065420</v>
       </c>
       <c r="B118" t="n">
-        <v>91314</v>
+        <v>91540</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>524081</v>
+        <v>524074</v>
       </c>
       <c r="R118" t="n">
-        <v>6713859</v>
+        <v>6713878</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15266,7 +15257,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15276,7 +15267,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Längs hela stammen.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15303,45 +15299,54 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129065420</v>
+        <v>129065356</v>
       </c>
       <c r="B119" t="n">
-        <v>91542</v>
+        <v>91313</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524074</v>
+        <v>524081</v>
       </c>
       <c r="R119" t="n">
-        <v>6713878</v>
+        <v>6713859</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15373,7 +15378,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15383,12 +15388,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Längs hela stammen.</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15418,7 +15418,7 @@
         <v>129064961</v>
       </c>
       <c r="B120" t="n">
-        <v>92480</v>
+        <v>92494</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>129116978</v>
       </c>
       <c r="B121" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>129114973</v>
       </c>
       <c r="B122" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>129116918</v>
       </c>
       <c r="B123" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>129115572</v>
       </c>
       <c r="B124" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -15187,45 +15187,54 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129065420</v>
+        <v>129064961</v>
       </c>
       <c r="B118" t="n">
-        <v>91540</v>
+        <v>92495</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>524074</v>
+        <v>524024</v>
       </c>
       <c r="R118" t="n">
-        <v>6713878</v>
+        <v>6713938</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15257,7 +15266,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15267,12 +15276,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Längs hela stammen.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15299,54 +15303,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129065356</v>
+        <v>129065420</v>
       </c>
       <c r="B119" t="n">
-        <v>91313</v>
+        <v>91540</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524081</v>
+        <v>524074</v>
       </c>
       <c r="R119" t="n">
-        <v>6713859</v>
+        <v>6713878</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15378,7 +15373,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15388,7 +15383,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Längs hela stammen.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15415,10 +15415,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129064961</v>
+        <v>129065356</v>
       </c>
       <c r="B120" t="n">
-        <v>92494</v>
+        <v>91313</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15426,43 +15426,43 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524024</v>
+        <v>524081</v>
       </c>
       <c r="R120" t="n">
-        <v>6713938</v>
+        <v>6713859</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15534,7 +15534,7 @@
         <v>129116978</v>
       </c>
       <c r="B121" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>129114973</v>
       </c>
       <c r="B122" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>129116918</v>
       </c>
       <c r="B123" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>129115572</v>
       </c>
       <c r="B124" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -15187,54 +15187,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129064961</v>
+        <v>129065420</v>
       </c>
       <c r="B118" t="n">
-        <v>92495</v>
+        <v>91540</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>524024</v>
+        <v>524074</v>
       </c>
       <c r="R118" t="n">
-        <v>6713938</v>
+        <v>6713878</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15266,7 +15257,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15276,7 +15267,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Längs hela stammen.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15303,45 +15299,54 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129065420</v>
+        <v>129064961</v>
       </c>
       <c r="B119" t="n">
-        <v>91540</v>
+        <v>92495</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524074</v>
+        <v>524024</v>
       </c>
       <c r="R119" t="n">
-        <v>6713878</v>
+        <v>6713938</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15373,7 +15378,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15383,12 +15388,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Längs hela stammen.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15655,7 +15655,7 @@
         <v>129114973</v>
       </c>
       <c r="B122" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>129115572</v>
       </c>
       <c r="B124" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -15187,45 +15187,54 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129065420</v>
+        <v>129064961</v>
       </c>
       <c r="B118" t="n">
-        <v>91540</v>
+        <v>92498</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>524074</v>
+        <v>524024</v>
       </c>
       <c r="R118" t="n">
-        <v>6713878</v>
+        <v>6713938</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15257,7 +15266,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15267,12 +15276,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Längs hela stammen.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15299,54 +15303,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129064961</v>
+        <v>129065420</v>
       </c>
       <c r="B119" t="n">
-        <v>92495</v>
+        <v>91543</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524024</v>
+        <v>524074</v>
       </c>
       <c r="R119" t="n">
-        <v>6713938</v>
+        <v>6713878</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15378,7 +15373,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15388,7 +15383,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Längs hela stammen.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15418,7 +15418,7 @@
         <v>129065356</v>
       </c>
       <c r="B120" t="n">
-        <v>91313</v>
+        <v>91316</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>129116978</v>
       </c>
       <c r="B121" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>129114973</v>
       </c>
       <c r="B122" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>129116918</v>
       </c>
       <c r="B123" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>129115572</v>
       </c>
       <c r="B124" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -15190,7 +15190,7 @@
         <v>129064961</v>
       </c>
       <c r="B118" t="n">
-        <v>92498</v>
+        <v>92500</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15303,45 +15303,54 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129065420</v>
+        <v>129065356</v>
       </c>
       <c r="B119" t="n">
-        <v>91543</v>
+        <v>91318</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524074</v>
+        <v>524081</v>
       </c>
       <c r="R119" t="n">
-        <v>6713878</v>
+        <v>6713859</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15373,7 +15382,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15383,12 +15392,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Längs hela stammen.</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15415,54 +15419,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129065356</v>
+        <v>129065420</v>
       </c>
       <c r="B120" t="n">
-        <v>91316</v>
+        <v>91545</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524081</v>
+        <v>524074</v>
       </c>
       <c r="R120" t="n">
-        <v>6713859</v>
+        <v>6713878</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15494,7 +15489,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15504,7 +15499,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Längs hela stammen.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15534,7 +15534,7 @@
         <v>129116978</v>
       </c>
       <c r="B121" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>129114973</v>
       </c>
       <c r="B122" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>129116918</v>
       </c>
       <c r="B123" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>129115572</v>
       </c>
       <c r="B124" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -15187,54 +15187,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129064961</v>
+        <v>129065420</v>
       </c>
       <c r="B118" t="n">
-        <v>92500</v>
+        <v>91549</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>524024</v>
+        <v>524074</v>
       </c>
       <c r="R118" t="n">
-        <v>6713938</v>
+        <v>6713878</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15266,7 +15257,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15276,7 +15267,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Längs hela stammen.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15306,7 +15302,7 @@
         <v>129065356</v>
       </c>
       <c r="B119" t="n">
-        <v>91318</v>
+        <v>91322</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15419,45 +15415,54 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129065420</v>
+        <v>129064961</v>
       </c>
       <c r="B120" t="n">
-        <v>91545</v>
+        <v>92504</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524074</v>
+        <v>524024</v>
       </c>
       <c r="R120" t="n">
-        <v>6713878</v>
+        <v>6713938</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15489,7 +15494,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15499,12 +15504,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Längs hela stammen.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15534,7 +15534,7 @@
         <v>129116978</v>
       </c>
       <c r="B121" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>129114973</v>
       </c>
       <c r="B122" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>129116918</v>
       </c>
       <c r="B123" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>129115572</v>
       </c>
       <c r="B124" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -15190,7 +15190,7 @@
         <v>129065420</v>
       </c>
       <c r="B118" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>129065356</v>
       </c>
       <c r="B119" t="n">
-        <v>91322</v>
+        <v>91323</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         <v>129064961</v>
       </c>
       <c r="B120" t="n">
-        <v>92504</v>
+        <v>92505</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>129116978</v>
       </c>
       <c r="B121" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>129114973</v>
       </c>
       <c r="B122" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>129116918</v>
       </c>
       <c r="B123" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>129115572</v>
       </c>
       <c r="B124" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -11963,7 +11963,7 @@
         <v>125899180</v>
       </c>
       <c r="B91" t="n">
-        <v>58134</v>
+        <v>58204</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -15190,7 +15190,7 @@
         <v>129065420</v>
       </c>
       <c r="B118" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>129065356</v>
       </c>
       <c r="B119" t="n">
-        <v>91323</v>
+        <v>91326</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         <v>129064961</v>
       </c>
       <c r="B120" t="n">
-        <v>92505</v>
+        <v>92508</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>129116978</v>
       </c>
       <c r="B121" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>129114973</v>
       </c>
       <c r="B122" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>129116918</v>
       </c>
       <c r="B123" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>129115572</v>
       </c>
       <c r="B124" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -15187,45 +15187,54 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129065420</v>
+        <v>129065356</v>
       </c>
       <c r="B118" t="n">
-        <v>91553</v>
+        <v>91326</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>524074</v>
+        <v>524081</v>
       </c>
       <c r="R118" t="n">
-        <v>6713878</v>
+        <v>6713859</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15257,7 +15266,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15267,12 +15276,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Längs hela stammen.</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15299,54 +15303,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129065356</v>
+        <v>129065420</v>
       </c>
       <c r="B119" t="n">
-        <v>91326</v>
+        <v>91553</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524081</v>
+        <v>524074</v>
       </c>
       <c r="R119" t="n">
-        <v>6713859</v>
+        <v>6713878</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15378,7 +15373,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15388,7 +15383,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Längs hela stammen.</t>
         </is>
       </c>
       <c r="AD119" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -15187,10 +15187,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129065356</v>
+        <v>129064961</v>
       </c>
       <c r="B118" t="n">
-        <v>91326</v>
+        <v>92508</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15198,43 +15198,43 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>524081</v>
+        <v>524024</v>
       </c>
       <c r="R118" t="n">
-        <v>6713859</v>
+        <v>6713938</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15266,7 +15266,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15276,7 +15276,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15303,45 +15303,54 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129065420</v>
+        <v>129065356</v>
       </c>
       <c r="B119" t="n">
-        <v>91553</v>
+        <v>91326</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524074</v>
+        <v>524081</v>
       </c>
       <c r="R119" t="n">
-        <v>6713878</v>
+        <v>6713859</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15373,7 +15382,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15383,12 +15392,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Längs hela stammen.</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15415,54 +15419,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129064961</v>
+        <v>129065420</v>
       </c>
       <c r="B120" t="n">
-        <v>92508</v>
+        <v>91553</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524024</v>
+        <v>524074</v>
       </c>
       <c r="R120" t="n">
-        <v>6713938</v>
+        <v>6713878</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15494,7 +15489,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15504,7 +15499,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Längs hela stammen.</t>
         </is>
       </c>
       <c r="AD120" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -15187,10 +15187,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129064961</v>
+        <v>129065356</v>
       </c>
       <c r="B118" t="n">
-        <v>92508</v>
+        <v>91326</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15198,43 +15198,43 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>524024</v>
+        <v>524081</v>
       </c>
       <c r="R118" t="n">
-        <v>6713938</v>
+        <v>6713859</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15266,7 +15266,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15276,7 +15276,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15303,10 +15303,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129065356</v>
+        <v>129064961</v>
       </c>
       <c r="B119" t="n">
-        <v>91326</v>
+        <v>92508</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15314,43 +15314,43 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524081</v>
+        <v>524024</v>
       </c>
       <c r="R119" t="n">
-        <v>6713859</v>
+        <v>6713938</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15382,7 +15382,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15392,7 +15392,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD119" t="b">

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -11963,7 +11963,7 @@
         <v>125899180</v>
       </c>
       <c r="B91" t="n">
-        <v>58204</v>
+        <v>58207</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -11963,7 +11963,7 @@
         <v>125899180</v>
       </c>
       <c r="B91" t="n">
-        <v>58207</v>
+        <v>58212</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -11963,7 +11963,7 @@
         <v>125899180</v>
       </c>
       <c r="B91" t="n">
-        <v>58212</v>
+        <v>58213</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -11963,7 +11963,7 @@
         <v>125899180</v>
       </c>
       <c r="B91" t="n">
-        <v>58213</v>
+        <v>58215</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -12185,7 +12185,7 @@
         <v>126936299</v>
       </c>
       <c r="B93" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12306,7 +12306,7 @@
         <v>126934586</v>
       </c>
       <c r="B94" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12427,10 +12427,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126934577</v>
+        <v>126934603</v>
       </c>
       <c r="B95" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12476,10 +12476,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>524036</v>
+        <v>524034</v>
       </c>
       <c r="R95" t="n">
-        <v>6713293</v>
+        <v>6713296</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12511,7 +12511,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12548,10 +12548,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126934603</v>
+        <v>126934577</v>
       </c>
       <c r="B96" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12597,10 +12597,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>524034</v>
+        <v>524036</v>
       </c>
       <c r="R96" t="n">
-        <v>6713296</v>
+        <v>6713293</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12632,7 +12632,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12672,7 +12672,7 @@
         <v>126934164</v>
       </c>
       <c r="B97" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         <v>126933611</v>
       </c>
       <c r="B98" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>126933275</v>
       </c>
       <c r="B99" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>126936539</v>
       </c>
       <c r="B100" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>126932846</v>
       </c>
       <c r="B101" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>126933692</v>
       </c>
       <c r="B102" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>126932450</v>
       </c>
       <c r="B103" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>126933326</v>
       </c>
       <c r="B104" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>126962844</v>
       </c>
       <c r="B105" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>126963368</v>
       </c>
       <c r="B106" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>126961591</v>
       </c>
       <c r="B107" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14008,7 +14008,7 @@
         <v>126963263</v>
       </c>
       <c r="B108" t="n">
-        <v>91628</v>
+        <v>91615</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>126962269</v>
       </c>
       <c r="B109" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>126963427</v>
       </c>
       <c r="B110" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>126962421</v>
       </c>
       <c r="B111" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>126963583</v>
       </c>
       <c r="B112" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY124"/>
+  <dimension ref="A1:AY125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16013,6 +16013,127 @@
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>130321255</v>
+      </c>
+      <c r="B125" t="n">
+        <v>101109</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>524148</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6713407</v>
+      </c>
+      <c r="S125" t="n">
+        <v>5</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -12185,7 +12185,7 @@
         <v>126936299</v>
       </c>
       <c r="B93" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12306,7 +12306,7 @@
         <v>126934586</v>
       </c>
       <c r="B94" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12427,10 +12427,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126934603</v>
+        <v>126934577</v>
       </c>
       <c r="B95" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12476,10 +12476,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>524034</v>
+        <v>524036</v>
       </c>
       <c r="R95" t="n">
-        <v>6713296</v>
+        <v>6713293</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12511,7 +12511,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12548,10 +12548,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126934577</v>
+        <v>126934603</v>
       </c>
       <c r="B96" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12597,10 +12597,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>524036</v>
+        <v>524034</v>
       </c>
       <c r="R96" t="n">
-        <v>6713293</v>
+        <v>6713296</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12632,7 +12632,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12672,7 +12672,7 @@
         <v>126934164</v>
       </c>
       <c r="B97" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         <v>126933611</v>
       </c>
       <c r="B98" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>126933275</v>
       </c>
       <c r="B99" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>126936539</v>
       </c>
       <c r="B100" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>126932846</v>
       </c>
       <c r="B101" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>126933692</v>
       </c>
       <c r="B102" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>126932450</v>
       </c>
       <c r="B103" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>126933326</v>
       </c>
       <c r="B104" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>126962844</v>
       </c>
       <c r="B105" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>126963368</v>
       </c>
       <c r="B106" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>126961591</v>
       </c>
       <c r="B107" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14008,7 +14008,7 @@
         <v>126963263</v>
       </c>
       <c r="B108" t="n">
-        <v>91615</v>
+        <v>91628</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>126962269</v>
       </c>
       <c r="B109" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>126963427</v>
       </c>
       <c r="B110" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>126962421</v>
       </c>
       <c r="B111" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>126963583</v>
       </c>
       <c r="B112" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -16018,7 +16018,7 @@
         <v>130321255</v>
       </c>
       <c r="B125" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -16018,7 +16018,7 @@
         <v>130321255</v>
       </c>
       <c r="B125" t="n">
-        <v>101112</v>
+        <v>101138</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -16018,7 +16018,7 @@
         <v>130321255</v>
       </c>
       <c r="B125" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -16018,7 +16018,7 @@
         <v>130321255</v>
       </c>
       <c r="B125" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -16018,7 +16018,7 @@
         <v>130321255</v>
       </c>
       <c r="B125" t="n">
-        <v>101140</v>
+        <v>101142</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -16018,7 +16018,7 @@
         <v>130321255</v>
       </c>
       <c r="B125" t="n">
-        <v>101142</v>
+        <v>101146</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -16018,7 +16018,7 @@
         <v>130321255</v>
       </c>
       <c r="B125" t="n">
-        <v>101146</v>
+        <v>101159</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -16018,7 +16018,7 @@
         <v>130321255</v>
       </c>
       <c r="B125" t="n">
-        <v>101159</v>
+        <v>101160</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -16018,7 +16018,7 @@
         <v>130321255</v>
       </c>
       <c r="B125" t="n">
-        <v>101160</v>
+        <v>101163</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY125"/>
+  <dimension ref="A1:AY127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16134,6 +16134,230 @@
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>131843813</v>
+      </c>
+      <c r="B126" t="n">
+        <v>58061</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Banvallen, Smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>524150</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6713670</v>
+      </c>
+      <c r="S126" t="n">
+        <v>5</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>131843634</v>
+      </c>
+      <c r="B127" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Banvallen, Smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>524145</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6713721</v>
+      </c>
+      <c r="S127" t="n">
+        <v>5</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -16139,7 +16139,7 @@
         <v>131843813</v>
       </c>
       <c r="B126" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>131843634</v>
       </c>
       <c r="B127" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -16139,7 +16139,7 @@
         <v>131843813</v>
       </c>
       <c r="B126" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY127"/>
+  <dimension ref="A1:AY129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16358,6 +16358,240 @@
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>133544380</v>
+      </c>
+      <c r="B128" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Banvallen, Smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>523932</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6713818</v>
+      </c>
+      <c r="S128" t="n">
+        <v>5</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>133546012</v>
+      </c>
+      <c r="B129" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>523990</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6713262</v>
+      </c>
+      <c r="S129" t="n">
+        <v>5</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Asp.</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -16363,7 +16363,7 @@
         <v>133544380</v>
       </c>
       <c r="B128" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>133546012</v>
       </c>
       <c r="B129" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -16363,7 +16363,7 @@
         <v>133544380</v>
       </c>
       <c r="B128" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>133546012</v>
       </c>
       <c r="B129" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY141"/>
+  <dimension ref="A1:AZ141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126963263</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122961337</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123562313</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1118,6 +1138,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123562349</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1225,6 +1250,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123565789</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123571398</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1439,6 +1474,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123572491</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1546,6 +1586,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126231015</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1658,6 +1703,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129065420</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1774,6 +1824,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129065356</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1881,6 +1936,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128217774</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1997,6 +2057,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129064961</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2113,6 +2178,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128217698</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2229,6 +2299,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129066471</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2350,6 +2425,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129116918</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2471,6 +2551,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129116978</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2613,6 +2698,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115538741</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2733,6 +2823,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114920743</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2845,6 +2940,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115551643</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2957,6 +3057,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123413633</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3069,6 +3174,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123526941</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3181,6 +3291,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123526961</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3293,6 +3408,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123528562</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3405,6 +3525,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123569917</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3517,6 +3642,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131843634</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3629,6 +3759,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133544380</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3751,6 +3886,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133546012</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3868,6 +4008,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944542</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3980,6 +4125,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944606</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4095,6 +4245,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125899180</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4223,6 +4378,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113739774</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4339,6 +4499,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122958842</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4455,6 +4620,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123562888</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4583,6 +4753,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113739771</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4695,6 +4870,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128217134</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4807,6 +4987,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131843813</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4924,6 +5109,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123563043</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5036,6 +5226,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123568031</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5148,6 +5343,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122915863</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5260,6 +5460,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122959354</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5372,6 +5577,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122959453</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5484,6 +5694,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123761045</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5596,6 +5811,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124434324</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5722,6 +5942,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680065</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5853,6 +6078,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680241</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5984,6 +6214,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680271</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6115,6 +6350,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680340</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6241,6 +6481,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680431</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6367,6 +6612,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680590</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6498,6 +6748,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680966</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6629,6 +6884,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122817980</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6760,6 +7020,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122821104</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6893,6 +7158,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122821198</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7024,6 +7294,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122821729</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7150,6 +7425,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122821745</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7276,6 +7556,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122821824</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7407,6 +7692,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122916997</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7538,6 +7828,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122917069</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7664,6 +7959,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122957710</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7795,6 +8095,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122958064</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7926,6 +8231,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122958244</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8052,6 +8362,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122958484</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8183,6 +8498,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122958550</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8314,6 +8634,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122958631</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8435,6 +8760,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122959503</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8556,6 +8886,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123412257</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8677,6 +9012,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123412326</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8798,6 +9138,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123412367</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8929,6 +9274,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123412439</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9055,6 +9405,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123412973</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9181,6 +9536,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123413078</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9314,6 +9674,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123413119</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9435,6 +9800,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123413726</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9556,6 +9926,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123413856</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9677,6 +10052,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123414270</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9798,6 +10178,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123414352</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9929,6 +10314,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123525488</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -10060,6 +10450,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123526406</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -10186,6 +10581,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123526470</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10307,6 +10707,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123527655</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10436,6 +10841,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123527741</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10565,6 +10975,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123528345</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10686,6 +11101,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123564666</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10807,6 +11227,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123564906</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10928,6 +11353,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123566656</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -11049,6 +11479,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123566767</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -11170,6 +11605,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123567299</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11291,6 +11731,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123567823</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11412,6 +11857,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123570699</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11533,6 +11983,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123760786</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11654,6 +12109,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123761091</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11780,6 +12240,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124431501</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11901,6 +12366,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124431841</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -12022,6 +12492,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124432135</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -12143,6 +12618,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124432412</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -12264,6 +12744,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124433963</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -12395,6 +12880,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124434100</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -12526,6 +13016,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124435133</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12647,6 +13142,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124711417</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12768,6 +13268,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125899247</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12889,6 +13394,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126932450</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -13010,6 +13520,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126932846</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -13131,6 +13646,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126933275</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -13252,6 +13772,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126933326</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -13373,6 +13898,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126933611</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -13494,6 +14024,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126933692</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -13615,6 +14150,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126934164</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -13736,6 +14276,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126934577</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13860,6 +14405,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126934586</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13981,6 +14531,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126934603</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -14102,6 +14657,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126935325</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -14223,6 +14783,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936299</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -14344,6 +14909,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936539</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -14470,6 +15040,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126961591</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -14591,6 +15166,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126962144</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -14712,6 +15292,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126962269</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -14833,6 +15418,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126962421</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14954,6 +15544,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126962844</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -15075,6 +15670,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126963368</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -15196,6 +15796,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126963427</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -15327,6 +15932,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126963583</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -15443,6 +16053,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127727170</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -15559,6 +16174,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127727173</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -15680,6 +16300,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129064197</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -15792,6 +16417,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129064260</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -15913,6 +16543,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129114973</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -16034,6 +16669,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115572</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -16146,6 +16786,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123569808</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -16275,6 +16920,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123569630</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -16408,6 +17058,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123762639</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -16529,6 +17184,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123768932</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -16641,6 +17301,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123768976</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -16753,6 +17418,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123768989</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -16865,6 +17535,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123768995</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -16977,6 +17652,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123769023</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -17098,6 +17778,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123769072</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -17219,6 +17904,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123769093</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -17331,6 +18021,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123769126</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -17452,6 +18147,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130321255</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -17573,8 +18273,155 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132755530</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -3897,7 +3897,7 @@
         <v>134944542</v>
       </c>
       <c r="B29" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>134944606</v>
       </c>
       <c r="B30" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
